--- a/VT_REG2_TRA_V12.xlsx
+++ b/VT_REG2_TRA_V12.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22730"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr showObjects="placeholders" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Training material\DemoS_012\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\veda-testing-model-private\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{917E9DCE-077D-4031-892E-D8C9566042AF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F11E3F78-B3CD-455B-AD79-15D6FE5572B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1905" yWindow="1905" windowWidth="21600" windowHeight="11385" tabRatio="901" activeTab="4"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="901" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EB2" sheetId="133" r:id="rId1"/>
@@ -27,12 +27,17 @@
   <definedNames>
     <definedName name="FID_1">[1]AGR_Fuels!$A$2</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -40,12 +45,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Maurizio Gargiulo</author>
   </authors>
   <commentList>
-    <comment ref="C8" authorId="0" shapeId="0">
+    <comment ref="C8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -63,14 +68,14 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Gary Goldstein</author>
     <author>Amit Kanudia</author>
     <author>Maurizio Gargiulo</author>
   </authors>
   <commentList>
-    <comment ref="J3" authorId="0" shapeId="0">
+    <comment ref="J3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
       <text>
         <r>
           <rPr>
@@ -184,7 +189,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O3" authorId="1" shapeId="0">
+    <comment ref="O3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
       <text>
         <r>
           <rPr>
@@ -210,7 +215,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P3" authorId="2" shapeId="0">
+    <comment ref="P3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000003000000}">
       <text>
         <r>
           <rPr>
@@ -283,7 +288,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q3" authorId="2" shapeId="0">
+    <comment ref="Q3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000004000000}">
       <text>
         <r>
           <rPr>
@@ -336,7 +341,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R3" authorId="2" shapeId="0">
+    <comment ref="R3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000005000000}">
       <text>
         <r>
           <rPr>
@@ -369,7 +374,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P13" authorId="2" shapeId="0">
+    <comment ref="P13" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000006000000}">
       <text>
         <r>
           <rPr>
@@ -462,7 +467,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q13" authorId="1" shapeId="0">
+    <comment ref="Q13" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000007000000}">
       <text>
         <r>
           <rPr>
@@ -487,7 +492,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R13" authorId="2" shapeId="0">
+    <comment ref="R13" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000008000000}">
       <text>
         <r>
           <rPr>
@@ -550,7 +555,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J14" authorId="2" shapeId="0">
+    <comment ref="J14" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000009000000}">
       <text>
         <r>
           <rPr>
@@ -798,14 +803,14 @@
 </file>
 
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Gary Goldstein</author>
     <author>Amit Kanudia</author>
     <author>Maurizio Gargiulo</author>
   </authors>
   <commentList>
-    <comment ref="O3" authorId="0" shapeId="0">
+    <comment ref="O3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
       <text>
         <r>
           <rPr>
@@ -919,7 +924,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T3" authorId="1" shapeId="0">
+    <comment ref="T3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000002000000}">
       <text>
         <r>
           <rPr>
@@ -945,7 +950,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U3" authorId="2" shapeId="0">
+    <comment ref="U3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0300-000003000000}">
       <text>
         <r>
           <rPr>
@@ -1018,7 +1023,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V3" authorId="2" shapeId="0">
+    <comment ref="V3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0300-000004000000}">
       <text>
         <r>
           <rPr>
@@ -1071,7 +1076,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W3" authorId="2" shapeId="0">
+    <comment ref="W3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0300-000005000000}">
       <text>
         <r>
           <rPr>
@@ -1104,7 +1109,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U10" authorId="2" shapeId="0">
+    <comment ref="U10" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0300-000006000000}">
       <text>
         <r>
           <rPr>
@@ -1197,7 +1202,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V10" authorId="1" shapeId="0">
+    <comment ref="V10" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0300-000007000000}">
       <text>
         <r>
           <rPr>
@@ -1222,7 +1227,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W10" authorId="2" shapeId="0">
+    <comment ref="W10" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0300-000008000000}">
       <text>
         <r>
           <rPr>
@@ -1285,7 +1290,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O11" authorId="2" shapeId="0">
+    <comment ref="O11" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0300-000009000000}">
       <text>
         <r>
           <rPr>
@@ -1533,7 +1538,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="194">
   <si>
     <t>CommName</t>
   </si>
@@ -2088,19 +2093,46 @@
   </si>
   <si>
     <t>Bpass*km</t>
+  </si>
+  <si>
+    <t>kj;</t>
+  </si>
+  <si>
+    <t>kl</t>
+  </si>
+  <si>
+    <t>l</t>
+  </si>
+  <si>
+    <t>kl;'</t>
+  </si>
+  <si>
+    <t>;'</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>;</t>
+  </si>
+  <si>
+    <t>k;l</t>
+  </si>
+  <si>
+    <t>;k</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="171" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="186" formatCode="0.000"/>
-    <numFmt numFmtId="187" formatCode="General_)"/>
-    <numFmt numFmtId="195" formatCode="\Te\x\t"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="General_)"/>
+    <numFmt numFmtId="167" formatCode="\Te\x\t"/>
   </numFmts>
-  <fonts count="32" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -2130,32 +2162,6 @@
       <sz val="10"/>
       <color indexed="12"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="8"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="8"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
       <family val="2"/>
     </font>
     <font>
@@ -2618,172 +2624,159 @@
   </borders>
   <cellStyleXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="148">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="13" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="13" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="13" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="13" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" xfId="5"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="8" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" xfId="8" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="5"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="8" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" xfId="8" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="10" applyFont="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" xfId="8" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" xfId="8" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="26" fillId="0" borderId="0" xfId="18" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="22" fillId="0" borderId="0" xfId="18" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="11"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="11" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="11" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="11" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="11" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="11" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="11" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="13" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="11" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="11" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="11" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="11" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="28" fillId="14" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="11" applyBorder="1"/>
+    <xf numFmtId="1" fontId="24" fillId="14" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="5" applyFill="1"/>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" xfId="8" quotePrefix="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="5" applyFill="1"/>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" xfId="8" quotePrefix="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="13" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" xfId="8" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" xfId="8" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="187" fontId="13" fillId="17" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="17" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="17" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="1" fontId="22" fillId="11" borderId="0" xfId="9" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="1" fontId="20" fillId="9" borderId="4" xfId="6" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="17" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="18" fillId="11" borderId="0" xfId="9" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="1" fontId="16" fillId="9" borderId="4" xfId="6" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="1" fontId="20" fillId="9" borderId="5" xfId="6" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="16" fillId="9" borderId="5" xfId="6" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="187" fontId="20" fillId="9" borderId="6" xfId="6" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="16" fillId="9" borderId="6" xfId="6" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="13" fillId="17" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="17" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="13" fillId="17" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="17" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="13" fillId="17" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="17" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="13" fillId="17" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="17" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="13" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="13" fillId="17" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="17" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="7" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -2792,40 +2785,38 @@
     <xf numFmtId="2" fontId="4" fillId="16" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="16" borderId="0" xfId="10" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="4" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="186" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="4" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="13" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="13" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" xfId="3"/>
-    <xf numFmtId="187" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="3"/>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="1" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="1" fontId="3" fillId="17" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="1" fontId="3" fillId="17" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="1" fontId="3" fillId="17" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="3" fillId="17" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2834,36 +2825,33 @@
     <xf numFmtId="0" fontId="3" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="13" fillId="17" borderId="10" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="9" fillId="17" borderId="10" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="13" fillId="17" borderId="1" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="9" fillId="17" borderId="1" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="13" fillId="17" borderId="11" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="9" fillId="17" borderId="11" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="13" fillId="17" borderId="2" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="9" fillId="17" borderId="2" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="22" fillId="11" borderId="1" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="22" fillId="11" borderId="2" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="18" fillId="11" borderId="1" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="18" fillId="11" borderId="2" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="22" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="4" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="186" fontId="0" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="28" fillId="14" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="24" fillId="14" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="11" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -2873,50 +2861,46 @@
     <xf numFmtId="0" fontId="3" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="11" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="11" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="19" borderId="0" xfId="11" applyFont="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="22" fillId="11" borderId="16" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="22" fillId="11" borderId="14" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="187" fontId="13" fillId="17" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="18" fillId="11" borderId="16" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="18" fillId="11" borderId="14" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="9" fillId="17" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="13" fillId="17" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="17" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="13" fillId="17" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="17" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="28" fillId="14" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="24" fillId="14" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="28" fillId="14" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="24" fillId="14" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="195" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="195" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="195" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="195" fontId="25" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="21" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="195" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="195" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="195" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="195" fontId="25" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="21" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="195" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="195" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="195" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="24">
     <cellStyle name="20% - Accent5" xfId="1" builtinId="46"/>
@@ -2925,24 +2909,24 @@
     <cellStyle name="Accent1" xfId="4" builtinId="29"/>
     <cellStyle name="Accent2" xfId="5" builtinId="33"/>
     <cellStyle name="Calculation" xfId="6" builtinId="22"/>
-    <cellStyle name="Comma 2" xfId="7"/>
+    <cellStyle name="Comma 2" xfId="7" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
     <cellStyle name="Good" xfId="8" builtinId="26"/>
     <cellStyle name="Input" xfId="9" builtinId="20"/>
     <cellStyle name="Neutral" xfId="10" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 10" xfId="11"/>
-    <cellStyle name="Normal 2" xfId="12"/>
-    <cellStyle name="Normal 4" xfId="13"/>
-    <cellStyle name="Normal 4 2" xfId="14"/>
-    <cellStyle name="Normal 8" xfId="15"/>
-    <cellStyle name="Normal 9 2" xfId="16"/>
-    <cellStyle name="Normale_B2020" xfId="17"/>
+    <cellStyle name="Normal 10" xfId="11" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
+    <cellStyle name="Normal 2" xfId="12" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
+    <cellStyle name="Normal 4" xfId="13" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
+    <cellStyle name="Normal 4 2" xfId="14" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
+    <cellStyle name="Normal 8" xfId="15" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
+    <cellStyle name="Normal 9 2" xfId="16" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
+    <cellStyle name="Normale_B2020" xfId="17" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
     <cellStyle name="Percent" xfId="18" builtinId="5"/>
-    <cellStyle name="Percent 2" xfId="19"/>
-    <cellStyle name="Percent 3" xfId="20"/>
-    <cellStyle name="Percent 4" xfId="21"/>
-    <cellStyle name="Percent 5" xfId="22"/>
-    <cellStyle name="Standard_Sce_D_Extraction" xfId="23"/>
+    <cellStyle name="Percent 2" xfId="19" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
+    <cellStyle name="Percent 3" xfId="20" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
+    <cellStyle name="Percent 4" xfId="21" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
+    <cellStyle name="Percent 5" xfId="22" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
+    <cellStyle name="Standard_Sce_D_Extraction" xfId="23" xr:uid="{00000000-0005-0000-0000-000017000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -3937,7 +3921,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="IEA Data"/>
@@ -4072,7 +4056,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="EnergyBalance"/>
@@ -4862,8 +4846,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AA31"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B1:AA31"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
@@ -4878,8 +4862,8 @@
     <col min="28" max="28" width="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="X1" s="24" t="s">
+    <row r="1" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="X1" s="20" t="s">
         <v>93</v>
       </c>
       <c r="Y1" s="1" t="s">
@@ -4892,1247 +4876,1208 @@
         <v>103</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C2" s="7"/>
-      <c r="D2" s="54" t="s">
+    <row r="2" spans="2:27" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D2" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="E2" s="54" t="s">
+      <c r="E2" s="41" t="s">
         <v>45</v>
       </c>
-      <c r="F2" s="54" t="s">
+      <c r="F2" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="G2" s="54" t="s">
+      <c r="G2" s="41" t="s">
         <v>129</v>
       </c>
-      <c r="H2" s="54" t="s">
+      <c r="H2" s="41" t="s">
         <v>130</v>
       </c>
-      <c r="I2" s="54" t="s">
+      <c r="I2" s="41" t="s">
         <v>131</v>
       </c>
-      <c r="J2" s="54" t="s">
+      <c r="J2" s="41" t="s">
         <v>132</v>
       </c>
-      <c r="K2" s="54" t="s">
+      <c r="K2" s="41" t="s">
         <v>133</v>
       </c>
-      <c r="L2" s="54" t="s">
+      <c r="L2" s="41" t="s">
         <v>134</v>
       </c>
-      <c r="M2" s="54" t="s">
+      <c r="M2" s="41" t="s">
         <v>135</v>
       </c>
-      <c r="N2" s="54" t="s">
+      <c r="N2" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="O2" s="54" t="s">
+      <c r="O2" s="41" t="s">
         <v>168</v>
       </c>
-      <c r="P2" s="54" t="s">
+      <c r="P2" s="41" t="s">
         <v>169</v>
       </c>
-      <c r="Q2" s="54" t="s">
+      <c r="Q2" s="41" t="s">
         <v>170</v>
       </c>
-      <c r="R2" s="54" t="s">
+      <c r="R2" s="41" t="s">
         <v>171</v>
       </c>
-      <c r="S2" s="54" t="s">
+      <c r="S2" s="41" t="s">
         <v>48</v>
       </c>
-      <c r="T2" s="54" t="s">
+      <c r="T2" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="U2" s="54" t="s">
+      <c r="U2" s="41" t="s">
         <v>50</v>
       </c>
-      <c r="V2" s="54" t="s">
+      <c r="V2" s="41" t="s">
         <v>166</v>
       </c>
-      <c r="X2" s="8"/>
-      <c r="Y2" s="53" t="s">
+      <c r="Y2" s="40" t="s">
         <v>156</v>
       </c>
-      <c r="Z2" s="14" t="s">
+      <c r="Z2" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="AA2" s="14" t="s">
+      <c r="AA2" s="10" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="C3" s="74" t="s">
+    <row r="3" spans="2:27" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="C3" s="61" t="s">
         <v>126</v>
       </c>
-      <c r="D3" s="55" t="s">
+      <c r="D3" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="E3" s="55" t="s">
+      <c r="E3" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="F3" s="55" t="s">
+      <c r="F3" s="42" t="s">
         <v>128</v>
       </c>
-      <c r="G3" s="55" t="s">
+      <c r="G3" s="42" t="s">
         <v>141</v>
       </c>
-      <c r="H3" s="55" t="s">
+      <c r="H3" s="42" t="s">
         <v>138</v>
       </c>
-      <c r="I3" s="55" t="s">
+      <c r="I3" s="42" t="s">
         <v>131</v>
       </c>
-      <c r="J3" s="55" t="s">
+      <c r="J3" s="42" t="s">
         <v>139</v>
       </c>
-      <c r="K3" s="55" t="s">
+      <c r="K3" s="42" t="s">
         <v>140</v>
       </c>
-      <c r="L3" s="55" t="s">
+      <c r="L3" s="42" t="s">
         <v>136</v>
       </c>
-      <c r="M3" s="55" t="s">
+      <c r="M3" s="42" t="s">
         <v>137</v>
       </c>
-      <c r="N3" s="55" t="s">
+      <c r="N3" s="42" t="s">
         <v>53</v>
       </c>
-      <c r="O3" s="55" t="s">
+      <c r="O3" s="42" t="s">
         <v>176</v>
       </c>
-      <c r="P3" s="55" t="s">
+      <c r="P3" s="42" t="s">
         <v>173</v>
       </c>
-      <c r="Q3" s="55" t="s">
+      <c r="Q3" s="42" t="s">
         <v>174</v>
       </c>
-      <c r="R3" s="55" t="s">
+      <c r="R3" s="42" t="s">
         <v>175</v>
       </c>
-      <c r="S3" s="55" t="s">
+      <c r="S3" s="42" t="s">
         <v>54</v>
       </c>
-      <c r="T3" s="55" t="s">
+      <c r="T3" s="42" t="s">
         <v>55</v>
       </c>
-      <c r="U3" s="55" t="s">
+      <c r="U3" s="42" t="s">
         <v>88</v>
       </c>
-      <c r="V3" s="55" t="s">
+      <c r="V3" s="42" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="B4" s="52"/>
-      <c r="C4" s="94" t="s">
+    <row r="4" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="B4" s="39"/>
+      <c r="C4" s="79" t="s">
         <v>57</v>
       </c>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="9"/>
-      <c r="O4" s="9"/>
-      <c r="P4" s="9"/>
-      <c r="Q4" s="9"/>
-      <c r="R4" s="9"/>
-      <c r="S4" s="9"/>
-      <c r="T4" s="9"/>
-      <c r="U4" s="9"/>
-      <c r="V4" s="95"/>
-    </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A5" s="6"/>
-      <c r="B5" s="56" t="s">
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6"/>
+      <c r="U4" s="6"/>
+      <c r="V4" s="80"/>
+    </row>
+    <row r="5" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="B5" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="C5" s="64" t="s">
+      <c r="C5" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="D5" s="96">
+      <c r="D5" s="81">
         <f>[2]EB2!D16</f>
         <v>124.79425000000001</v>
       </c>
-      <c r="E5" s="96">
+      <c r="E5" s="81">
         <f>[2]EB2!E16</f>
         <v>3095.8757999999998</v>
       </c>
-      <c r="F5" s="96">
+      <c r="F5" s="81">
         <f>[2]EB2!F16</f>
         <v>0</v>
       </c>
-      <c r="G5" s="96">
+      <c r="G5" s="81">
         <f>[2]EB2!G16</f>
         <v>862.053</v>
       </c>
-      <c r="H5" s="96">
+      <c r="H5" s="81">
         <f>[2]EB2!H16</f>
         <v>72.9495</v>
       </c>
-      <c r="I5" s="96">
+      <c r="I5" s="81">
         <f>[2]EB2!I16</f>
         <v>190.17599999999999</v>
       </c>
-      <c r="J5" s="96">
+      <c r="J5" s="81">
         <f>[2]EB2!J16</f>
         <v>3.1680000000000001</v>
       </c>
-      <c r="K5" s="96">
+      <c r="K5" s="81">
         <f>[2]EB2!K16</f>
         <v>0</v>
       </c>
-      <c r="L5" s="96">
+      <c r="L5" s="81">
         <f>[2]EB2!L16</f>
         <v>15.38</v>
       </c>
-      <c r="M5" s="96">
+      <c r="M5" s="81">
         <f>[2]EB2!M16</f>
         <v>0.92</v>
       </c>
-      <c r="N5" s="97">
+      <c r="N5" s="82">
         <f>[2]EB2!N16</f>
         <v>0</v>
       </c>
-      <c r="O5" s="96">
+      <c r="O5" s="81">
         <f>[2]EB2!O16</f>
         <v>298.48174999999992</v>
       </c>
-      <c r="P5" s="96">
+      <c r="P5" s="81">
         <f>[2]EB2!P16</f>
         <v>0</v>
       </c>
-      <c r="Q5" s="96">
+      <c r="Q5" s="81">
         <f>[2]EB2!Q16</f>
         <v>0</v>
       </c>
-      <c r="R5" s="96">
+      <c r="R5" s="81">
         <f>[2]EB2!R16</f>
         <v>50</v>
       </c>
-      <c r="S5" s="96">
+      <c r="S5" s="81">
         <f>[2]EB2!S16</f>
         <v>0</v>
       </c>
-      <c r="T5" s="96">
+      <c r="T5" s="81">
         <f>[2]EB2!T16</f>
         <v>432.74250000000001</v>
       </c>
-      <c r="U5" s="96">
+      <c r="U5" s="81">
         <f>[2]EB2!U16</f>
         <v>1435.8710000000001</v>
       </c>
-      <c r="V5" s="98">
+      <c r="V5" s="83">
         <f>SUM(D5:U5)</f>
         <v>6582.4117999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A6" s="6"/>
-      <c r="B6" s="56" t="s">
+    <row r="6" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="B6" s="43" t="s">
         <v>60</v>
       </c>
-      <c r="C6" s="65" t="s">
+      <c r="C6" s="52" t="s">
         <v>61</v>
       </c>
-      <c r="D6" s="96">
+      <c r="D6" s="81">
         <f>[2]EB2!D17</f>
         <v>19.923749999999998</v>
       </c>
-      <c r="E6" s="96">
+      <c r="E6" s="81">
         <f>[2]EB2!E17</f>
         <v>1051.038</v>
       </c>
-      <c r="F6" s="96">
+      <c r="F6" s="81">
         <f>[2]EB2!F17</f>
         <v>0</v>
       </c>
-      <c r="G6" s="96">
+      <c r="G6" s="81">
         <f>[2]EB2!G17</f>
         <v>368.84399999999999</v>
       </c>
-      <c r="H6" s="96">
+      <c r="H6" s="81">
         <f>[2]EB2!H17</f>
         <v>1.677</v>
       </c>
-      <c r="I6" s="96">
+      <c r="I6" s="81">
         <f>[2]EB2!I17</f>
         <v>31.602</v>
       </c>
-      <c r="J6" s="96">
+      <c r="J6" s="81">
         <f>[2]EB2!J17</f>
         <v>5.72</v>
       </c>
-      <c r="K6" s="96">
+      <c r="K6" s="81">
         <f>[2]EB2!K17</f>
         <v>0</v>
       </c>
-      <c r="L6" s="96">
+      <c r="L6" s="81">
         <f>[2]EB2!L17</f>
         <v>19.32</v>
       </c>
-      <c r="M6" s="96">
+      <c r="M6" s="81">
         <f>[2]EB2!M17</f>
         <v>0.24199999999999999</v>
       </c>
-      <c r="N6" s="97">
+      <c r="N6" s="82">
         <f>[2]EB2!N17</f>
         <v>0</v>
       </c>
-      <c r="O6" s="96">
+      <c r="O6" s="81">
         <f>[2]EB2!O17</f>
         <v>13</v>
       </c>
-      <c r="P6" s="96">
+      <c r="P6" s="81">
         <f>[2]EB2!P17</f>
         <v>0</v>
       </c>
-      <c r="Q6" s="96">
+      <c r="Q6" s="81">
         <f>[2]EB2!Q17</f>
         <v>0</v>
       </c>
-      <c r="R6" s="96">
+      <c r="R6" s="81">
         <f>[2]EB2!R17</f>
         <v>7.5</v>
       </c>
-      <c r="S6" s="96">
+      <c r="S6" s="81">
         <f>[2]EB2!S17</f>
         <v>0.60850000000000004</v>
       </c>
-      <c r="T6" s="96">
+      <c r="T6" s="81">
         <f>[2]EB2!T17</f>
         <v>127.32299999999999</v>
       </c>
-      <c r="U6" s="96">
+      <c r="U6" s="81">
         <f>[2]EB2!U17</f>
         <v>1263.6955</v>
       </c>
-      <c r="V6" s="98">
+      <c r="V6" s="83">
         <f t="shared" ref="V6:V12" si="0">SUM(D6:U6)</f>
         <v>2910.4937500000001</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A7" s="6"/>
-      <c r="B7" s="56" t="s">
+    <row r="7" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="B7" s="43" t="s">
         <v>62</v>
       </c>
-      <c r="C7" s="65" t="s">
+      <c r="C7" s="52" t="s">
         <v>63</v>
       </c>
-      <c r="D7" s="96">
+      <c r="D7" s="81">
         <f>[2]EB2!D18</f>
         <v>663.94509999999991</v>
       </c>
-      <c r="E7" s="96">
+      <c r="E7" s="81">
         <f>[2]EB2!E18</f>
         <v>2662.2965999999997</v>
       </c>
-      <c r="F7" s="96">
+      <c r="F7" s="81">
         <f>[2]EB2!F18</f>
         <v>0</v>
       </c>
-      <c r="G7" s="96">
+      <c r="G7" s="81">
         <f>[2]EB2!G18</f>
         <v>298.68</v>
       </c>
-      <c r="H7" s="96">
+      <c r="H7" s="81">
         <f>[2]EB2!H18</f>
         <v>36.356499999999997</v>
       </c>
-      <c r="I7" s="96">
+      <c r="I7" s="81">
         <f>[2]EB2!I18</f>
         <v>142.97149999999999</v>
       </c>
-      <c r="J7" s="96">
+      <c r="J7" s="81">
         <f>[2]EB2!J18</f>
         <v>7.766</v>
       </c>
-      <c r="K7" s="96">
+      <c r="K7" s="81">
         <f>[2]EB2!K18</f>
         <v>44.066000000000003</v>
       </c>
-      <c r="L7" s="96">
+      <c r="L7" s="81">
         <f>[2]EB2!L18</f>
         <v>286.0505</v>
       </c>
-      <c r="M7" s="96">
+      <c r="M7" s="81">
         <f>[2]EB2!M18</f>
         <v>191.57300000000001</v>
       </c>
-      <c r="N7" s="97">
+      <c r="N7" s="82">
         <f>[2]EB2!N18</f>
         <v>0</v>
       </c>
-      <c r="O7" s="96">
+      <c r="O7" s="81">
         <f>[2]EB2!O18</f>
         <v>180.41775000000007</v>
       </c>
-      <c r="P7" s="96">
+      <c r="P7" s="81">
         <f>[2]EB2!P18</f>
         <v>0</v>
       </c>
-      <c r="Q7" s="96">
+      <c r="Q7" s="81">
         <f>[2]EB2!Q18</f>
         <v>0</v>
       </c>
-      <c r="R7" s="96">
+      <c r="R7" s="81">
         <f>[2]EB2!R18</f>
         <v>0</v>
       </c>
-      <c r="S7" s="96">
+      <c r="S7" s="81">
         <f>[2]EB2!S18</f>
         <v>58.595999999999997</v>
       </c>
-      <c r="T7" s="96">
+      <c r="T7" s="81">
         <f>[2]EB2!T18</f>
         <v>316.79149999999998</v>
       </c>
-      <c r="U7" s="96">
+      <c r="U7" s="81">
         <f>[2]EB2!U18</f>
         <v>2044.222</v>
       </c>
-      <c r="V7" s="98">
+      <c r="V7" s="83">
         <f t="shared" si="0"/>
         <v>6933.7324499999986</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A8" s="6"/>
-      <c r="B8" s="56" t="s">
+    <row r="8" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="B8" s="43" t="s">
         <v>64</v>
       </c>
-      <c r="C8" s="65" t="s">
+      <c r="C8" s="52" t="s">
         <v>65</v>
       </c>
-      <c r="D8" s="96">
+      <c r="D8" s="81">
         <f>[2]EB2!D19</f>
         <v>15.434999999999999</v>
       </c>
-      <c r="E8" s="96">
+      <c r="E8" s="81">
         <f>[2]EB2!E19</f>
         <v>120.72359999999999</v>
       </c>
-      <c r="F8" s="96">
+      <c r="F8" s="81">
         <f>[2]EB2!F19</f>
         <v>0</v>
       </c>
-      <c r="G8" s="96">
+      <c r="G8" s="81">
         <f>[2]EB2!G19</f>
         <v>366.58800000000002</v>
       </c>
-      <c r="H8" s="96">
+      <c r="H8" s="81">
         <f>[2]EB2!H19</f>
         <v>0.47299999999999998</v>
       </c>
-      <c r="I8" s="96">
+      <c r="I8" s="81">
         <f>[2]EB2!I19</f>
         <v>16.169</v>
       </c>
-      <c r="J8" s="96">
+      <c r="J8" s="81">
         <f>[2]EB2!J19</f>
         <v>1.716</v>
       </c>
-      <c r="K8" s="96">
+      <c r="K8" s="81">
         <f>[2]EB2!K19</f>
         <v>0</v>
       </c>
-      <c r="L8" s="96">
+      <c r="L8" s="81">
         <f>[2]EB2!L19</f>
         <v>13.74</v>
       </c>
-      <c r="M8" s="96">
+      <c r="M8" s="81">
         <f>[2]EB2!M19</f>
         <v>0</v>
       </c>
-      <c r="N8" s="97">
+      <c r="N8" s="82">
         <f>[2]EB2!N19</f>
         <v>0</v>
       </c>
-      <c r="O8" s="96">
+      <c r="O8" s="81">
         <f>[2]EB2!O19</f>
         <v>15.771500000000003</v>
       </c>
-      <c r="P8" s="96">
+      <c r="P8" s="81">
         <f>[2]EB2!P19</f>
         <v>0</v>
       </c>
-      <c r="Q8" s="96">
+      <c r="Q8" s="81">
         <f>[2]EB2!Q19</f>
         <v>0</v>
       </c>
-      <c r="R8" s="96">
+      <c r="R8" s="81">
         <f>[2]EB2!R19</f>
         <v>0</v>
       </c>
-      <c r="S8" s="96">
+      <c r="S8" s="81">
         <f>[2]EB2!S19</f>
         <v>5.0000000000000001E-4</v>
       </c>
-      <c r="T8" s="96">
+      <c r="T8" s="81">
         <f>[2]EB2!T19</f>
         <v>7.7869999999999999</v>
       </c>
-      <c r="U8" s="96">
+      <c r="U8" s="81">
         <f>[2]EB2!U19</f>
         <v>9.6930000000000014</v>
       </c>
-      <c r="V8" s="98">
+      <c r="V8" s="83">
         <f t="shared" si="0"/>
         <v>568.09659999999997</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="15" x14ac:dyDescent="0.25">
-      <c r="A9" s="6"/>
-      <c r="B9" s="56" t="s">
+    <row r="9" spans="2:27" ht="15" x14ac:dyDescent="0.25">
+      <c r="B9" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="C9" s="65" t="s">
+      <c r="C9" s="52" t="s">
         <v>67</v>
       </c>
-      <c r="D9" s="96">
+      <c r="D9" s="81">
         <f>[2]EB2!D20</f>
         <v>0.1946</v>
       </c>
-      <c r="E9" s="60">
+      <c r="E9" s="47">
         <f>[2]EB2!E20</f>
         <v>12.7494</v>
       </c>
-      <c r="F9" s="96">
+      <c r="F9" s="81">
         <f>[2]EB2!F20</f>
         <v>0</v>
       </c>
-      <c r="G9" s="60">
+      <c r="G9" s="47">
         <f>[2]EB2!G20</f>
         <v>3856.2855</v>
       </c>
-      <c r="H9" s="96">
+      <c r="H9" s="81">
         <f>[2]EB2!H20</f>
         <v>1047.652</v>
       </c>
-      <c r="I9" s="60">
+      <c r="I9" s="47">
         <f>[2]EB2!I20</f>
         <v>94.230999999999995</v>
       </c>
-      <c r="J9" s="60">
+      <c r="J9" s="47">
         <f>[2]EB2!J20</f>
         <v>2394.2159999999999</v>
       </c>
-      <c r="K9" s="96">
+      <c r="K9" s="81">
         <f>[2]EB2!K20</f>
         <v>0</v>
       </c>
-      <c r="L9" s="96">
+      <c r="L9" s="81">
         <f>[2]EB2!L20</f>
         <v>33.24</v>
       </c>
-      <c r="M9" s="96">
+      <c r="M9" s="81">
         <f>[2]EB2!M20</f>
         <v>0</v>
       </c>
-      <c r="N9" s="96">
+      <c r="N9" s="81">
         <f>[2]EB2!N20</f>
         <v>0</v>
       </c>
-      <c r="O9" s="60">
+      <c r="O9" s="47">
         <f>[2]EB2!O20</f>
         <v>40.25</v>
       </c>
-      <c r="P9" s="96">
+      <c r="P9" s="81">
         <f>[2]EB2!P20</f>
         <v>0</v>
       </c>
-      <c r="Q9" s="96">
+      <c r="Q9" s="81">
         <f>[2]EB2!Q20</f>
         <v>0</v>
       </c>
-      <c r="R9" s="96">
+      <c r="R9" s="81">
         <f>[2]EB2!R20</f>
         <v>0</v>
       </c>
-      <c r="S9" s="96">
+      <c r="S9" s="81">
         <f>[2]EB2!S20</f>
         <v>0</v>
       </c>
-      <c r="T9" s="96">
+      <c r="T9" s="81">
         <f>[2]EB2!T20</f>
         <v>0</v>
       </c>
-      <c r="U9" s="60">
+      <c r="U9" s="47">
         <f>[2]EB2!U20</f>
         <v>132.98599999999999</v>
       </c>
-      <c r="V9" s="98">
+      <c r="V9" s="83">
         <f t="shared" si="0"/>
         <v>7611.8044999999993</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A10" s="6"/>
-      <c r="B10" s="56" t="s">
+    <row r="10" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="B10" s="43" t="s">
         <v>68</v>
       </c>
-      <c r="C10" s="66" t="s">
+      <c r="C10" s="53" t="s">
         <v>69</v>
       </c>
-      <c r="D10" s="59">
+      <c r="D10" s="46">
         <f>[2]EB2!D21</f>
         <v>416.23084999999924</v>
       </c>
-      <c r="E10" s="59">
+      <c r="E10" s="46">
         <f>[2]EB2!E21</f>
         <v>0</v>
       </c>
-      <c r="F10" s="59">
+      <c r="F10" s="46">
         <f>[2]EB2!F21</f>
         <v>0</v>
       </c>
-      <c r="G10" s="59">
+      <c r="G10" s="46">
         <f>[2]EB2!G21</f>
         <v>0</v>
       </c>
-      <c r="H10" s="59">
+      <c r="H10" s="46">
         <f>[2]EB2!H21</f>
         <v>0</v>
       </c>
-      <c r="I10" s="59">
+      <c r="I10" s="46">
         <f>[2]EB2!I21</f>
         <v>0</v>
       </c>
-      <c r="J10" s="59">
+      <c r="J10" s="46">
         <f>[2]EB2!J21</f>
         <v>0</v>
       </c>
-      <c r="K10" s="59">
+      <c r="K10" s="46">
         <f>[2]EB2!K21</f>
         <v>0</v>
       </c>
-      <c r="L10" s="59">
+      <c r="L10" s="46">
         <f>[2]EB2!L21</f>
         <v>0</v>
       </c>
-      <c r="M10" s="59">
+      <c r="M10" s="46">
         <f>[2]EB2!M21</f>
         <v>0</v>
       </c>
-      <c r="N10" s="59">
+      <c r="N10" s="46">
         <f>[2]EB2!N21</f>
         <v>0</v>
       </c>
-      <c r="O10" s="59">
+      <c r="O10" s="46">
         <f>[2]EB2!O21</f>
         <v>0</v>
       </c>
-      <c r="P10" s="59">
+      <c r="P10" s="46">
         <f>[2]EB2!P21</f>
         <v>0</v>
       </c>
-      <c r="Q10" s="59">
+      <c r="Q10" s="46">
         <f>[2]EB2!Q21</f>
         <v>0</v>
       </c>
-      <c r="R10" s="59">
+      <c r="R10" s="46">
         <f>[2]EB2!R21</f>
         <v>0</v>
       </c>
-      <c r="S10" s="59">
+      <c r="S10" s="46">
         <f>[2]EB2!S21</f>
         <v>0</v>
       </c>
-      <c r="T10" s="59">
+      <c r="T10" s="46">
         <f>[2]EB2!T21</f>
         <v>313.51900000000001</v>
       </c>
-      <c r="U10" s="59">
+      <c r="U10" s="46">
         <f>[2]EB2!U21</f>
         <v>325</v>
       </c>
-      <c r="V10" s="99">
+      <c r="V10" s="84">
         <f t="shared" si="0"/>
         <v>1054.7498499999992</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A11" s="6"/>
-      <c r="B11" s="56" t="s">
+    <row r="11" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="B11" s="43" t="s">
         <v>86</v>
       </c>
-      <c r="C11" s="65" t="s">
+      <c r="C11" s="52" t="s">
         <v>70</v>
       </c>
-      <c r="D11" s="96">
+      <c r="D11" s="81">
         <f>[2]EB2!D22</f>
         <v>18.358550000000001</v>
       </c>
-      <c r="E11" s="96">
+      <c r="E11" s="81">
         <f>[2]EB2!E22</f>
         <v>380.29379999999998</v>
       </c>
-      <c r="F11" s="96">
+      <c r="F11" s="81">
         <f>[2]EB2!F22</f>
         <v>0</v>
       </c>
-      <c r="G11" s="96">
+      <c r="G11" s="81">
         <f>[2]EB2!G22</f>
         <v>76.465000000000003</v>
       </c>
-      <c r="H11" s="96">
+      <c r="H11" s="81">
         <f>[2]EB2!H22</f>
         <v>4.7945000000000002</v>
       </c>
-      <c r="I11" s="96">
+      <c r="I11" s="81">
         <f>[2]EB2!I22</f>
         <v>199.87350000000001</v>
       </c>
-      <c r="J11" s="96">
+      <c r="J11" s="81">
         <f>[2]EB2!J22</f>
         <v>3.1459999999999999</v>
       </c>
-      <c r="K11" s="96">
+      <c r="K11" s="81">
         <f>[2]EB2!K22</f>
         <v>899.20600000000002</v>
       </c>
-      <c r="L11" s="96">
+      <c r="L11" s="81">
         <f>[2]EB2!L22</f>
         <v>52.04</v>
       </c>
-      <c r="M11" s="96">
+      <c r="M11" s="81">
         <f>[2]EB2!M22</f>
         <v>800.72900000000004</v>
       </c>
-      <c r="N11" s="97">
+      <c r="N11" s="82">
         <f>[2]EB2!N22</f>
         <v>0</v>
       </c>
-      <c r="O11" s="96">
+      <c r="O11" s="81">
         <f>[2]EB2!O22</f>
         <v>0</v>
       </c>
-      <c r="P11" s="96">
+      <c r="P11" s="81">
         <f>[2]EB2!P22</f>
         <v>0</v>
       </c>
-      <c r="Q11" s="96">
+      <c r="Q11" s="81">
         <f>[2]EB2!Q22</f>
         <v>0</v>
       </c>
-      <c r="R11" s="96">
+      <c r="R11" s="81">
         <f>[2]EB2!R22</f>
         <v>0</v>
       </c>
-      <c r="S11" s="96">
+      <c r="S11" s="81">
         <f>[2]EB2!S22</f>
         <v>0</v>
       </c>
-      <c r="T11" s="96">
+      <c r="T11" s="81">
         <f>[2]EB2!T22</f>
         <v>0</v>
       </c>
-      <c r="U11" s="96">
+      <c r="U11" s="81">
         <f>[2]EB2!U22</f>
         <v>0</v>
       </c>
-      <c r="V11" s="98">
+      <c r="V11" s="83">
         <f t="shared" si="0"/>
         <v>2434.9063500000002</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A12" s="6"/>
-      <c r="B12" s="56" t="s">
+    <row r="12" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="B12" s="43" t="s">
         <v>87</v>
       </c>
-      <c r="C12" s="65" t="s">
+      <c r="C12" s="52" t="s">
         <v>71</v>
       </c>
-      <c r="D12" s="96">
+      <c r="D12" s="81">
         <f>[2]EB2!D23</f>
         <v>0</v>
       </c>
-      <c r="E12" s="96">
+      <c r="E12" s="81">
         <f>[2]EB2!E23</f>
         <v>0</v>
       </c>
-      <c r="F12" s="96">
+      <c r="F12" s="81">
         <f>[2]EB2!F23</f>
         <v>0</v>
       </c>
-      <c r="G12" s="96">
+      <c r="G12" s="81">
         <f>[2]EB2!G23</f>
         <v>146.90600000000001</v>
       </c>
-      <c r="H12" s="96">
+      <c r="H12" s="81">
         <f>[2]EB2!H23</f>
         <v>0</v>
       </c>
-      <c r="I12" s="96">
+      <c r="I12" s="81">
         <f>[2]EB2!I23</f>
         <v>0</v>
       </c>
-      <c r="J12" s="96">
+      <c r="J12" s="81">
         <f>[2]EB2!J23</f>
         <v>0</v>
       </c>
-      <c r="K12" s="96">
+      <c r="K12" s="81">
         <f>[2]EB2!K23</f>
         <v>0</v>
       </c>
-      <c r="L12" s="96">
+      <c r="L12" s="81">
         <f>[2]EB2!L23</f>
         <v>902.14</v>
       </c>
-      <c r="M12" s="96">
+      <c r="M12" s="81">
         <f>[2]EB2!M23</f>
         <v>6.5</v>
       </c>
-      <c r="N12" s="97">
+      <c r="N12" s="82">
         <f>[2]EB2!N23</f>
         <v>0</v>
       </c>
-      <c r="O12" s="59">
+      <c r="O12" s="46">
         <f>[2]EB2!O23</f>
         <v>0</v>
       </c>
-      <c r="P12" s="59">
+      <c r="P12" s="46">
         <f>[2]EB2!P23</f>
         <v>0</v>
       </c>
-      <c r="Q12" s="59">
+      <c r="Q12" s="46">
         <f>[2]EB2!Q23</f>
         <v>0</v>
       </c>
-      <c r="R12" s="59">
+      <c r="R12" s="46">
         <f>[2]EB2!R23</f>
         <v>0</v>
       </c>
-      <c r="S12" s="96">
+      <c r="S12" s="81">
         <f>[2]EB2!S23</f>
         <v>0</v>
       </c>
-      <c r="T12" s="96">
+      <c r="T12" s="81">
         <f>[2]EB2!T23</f>
         <v>0</v>
       </c>
-      <c r="U12" s="96">
+      <c r="U12" s="81">
         <f>[2]EB2!U23</f>
         <v>0</v>
       </c>
-      <c r="V12" s="98">
+      <c r="V12" s="83">
         <f t="shared" si="0"/>
         <v>1055.546</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="15" x14ac:dyDescent="0.25">
-      <c r="A13" s="6"/>
-      <c r="B13" s="93" t="s">
+    <row r="13" spans="2:27" ht="15" x14ac:dyDescent="0.25">
+      <c r="B13" s="78" t="s">
         <v>89</v>
       </c>
-      <c r="C13" s="63" t="s">
+      <c r="C13" s="50" t="s">
         <v>162</v>
       </c>
-      <c r="D13" s="61">
+      <c r="D13" s="48">
         <f t="shared" ref="D13:V13" si="1">SUM(D5:D12)</f>
         <v>1258.8820999999991</v>
       </c>
-      <c r="E13" s="61">
+      <c r="E13" s="48">
         <f t="shared" si="1"/>
         <v>7322.9772000000003</v>
       </c>
-      <c r="F13" s="61">
+      <c r="F13" s="48">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G13" s="61">
+      <c r="G13" s="48">
         <f t="shared" si="1"/>
         <v>5975.8215</v>
       </c>
-      <c r="H13" s="61">
+      <c r="H13" s="48">
         <f t="shared" si="1"/>
         <v>1163.9024999999999</v>
       </c>
-      <c r="I13" s="61">
+      <c r="I13" s="48">
         <f t="shared" si="1"/>
         <v>675.02300000000002</v>
       </c>
-      <c r="J13" s="61">
+      <c r="J13" s="48">
         <f t="shared" si="1"/>
         <v>2415.732</v>
       </c>
-      <c r="K13" s="61">
+      <c r="K13" s="48">
         <f t="shared" si="1"/>
         <v>943.27200000000005</v>
       </c>
-      <c r="L13" s="61">
+      <c r="L13" s="48">
         <f t="shared" si="1"/>
         <v>1321.9105</v>
       </c>
-      <c r="M13" s="61">
+      <c r="M13" s="48">
         <f t="shared" si="1"/>
         <v>999.96400000000006</v>
       </c>
-      <c r="N13" s="61">
+      <c r="N13" s="48">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O13" s="61">
+      <c r="O13" s="48">
         <f t="shared" si="1"/>
         <v>547.92100000000005</v>
       </c>
-      <c r="P13" s="61"/>
-      <c r="Q13" s="61"/>
-      <c r="R13" s="61"/>
-      <c r="S13" s="61">
+      <c r="P13" s="48"/>
+      <c r="Q13" s="48"/>
+      <c r="R13" s="48"/>
+      <c r="S13" s="48">
         <f t="shared" si="1"/>
         <v>59.204999999999998</v>
       </c>
-      <c r="T13" s="61">
+      <c r="T13" s="48">
         <f t="shared" si="1"/>
         <v>1198.163</v>
       </c>
-      <c r="U13" s="61">
+      <c r="U13" s="48">
         <f>SUM(U5:U12)</f>
         <v>5211.4674999999997</v>
       </c>
-      <c r="V13" s="62">
+      <c r="V13" s="49">
         <f t="shared" si="1"/>
         <v>29151.741299999998</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A14" s="6"/>
-      <c r="D14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="10"/>
-      <c r="M14" s="10"/>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A15" s="6"/>
-      <c r="D15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
-      <c r="L15" s="10"/>
-      <c r="M15" s="10"/>
-    </row>
-    <row r="16" spans="1:27" ht="15" x14ac:dyDescent="0.25">
-      <c r="A16" s="6"/>
-      <c r="C16" s="60" t="s">
+    <row r="14" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="D14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="7"/>
+    </row>
+    <row r="15" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="D15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7"/>
+    </row>
+    <row r="16" spans="2:27" ht="15" x14ac:dyDescent="0.25">
+      <c r="C16" s="47" t="s">
         <v>157</v>
       </c>
-      <c r="D16" s="60"/>
-      <c r="E16" s="60"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="10"/>
-      <c r="K16" s="10"/>
-      <c r="L16" s="10"/>
-      <c r="M16" s="10"/>
-    </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A17" s="6"/>
-      <c r="D17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="10"/>
-      <c r="K17" s="10"/>
-      <c r="L17" s="10"/>
-      <c r="M17" s="10"/>
-    </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A18" s="6"/>
-      <c r="D18" s="10"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="10"/>
-      <c r="K18" s="10"/>
-      <c r="L18" s="10"/>
-      <c r="M18" s="10"/>
-    </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A19" s="6"/>
-      <c r="D19" s="10"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10"/>
-      <c r="I19" s="10"/>
-      <c r="J19" s="10"/>
-      <c r="K19" s="10"/>
-      <c r="L19" s="10"/>
-      <c r="M19" s="10"/>
-    </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A20" s="6"/>
-      <c r="D20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="10"/>
-      <c r="K20" s="10"/>
-      <c r="L20" s="10"/>
-      <c r="M20" s="10"/>
-    </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A21" s="6"/>
-      <c r="D21" s="10"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
-      <c r="I21" s="10"/>
-      <c r="J21" s="10"/>
-      <c r="K21" s="10"/>
-      <c r="L21" s="10"/>
-      <c r="M21" s="10"/>
-    </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A22" s="6"/>
-      <c r="D22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="10"/>
-      <c r="K22" s="10"/>
-      <c r="L22" s="10"/>
-      <c r="M22" s="10"/>
-    </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A23" s="6"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="26"/>
-      <c r="O23" s="27"/>
-      <c r="P23" s="27"/>
-      <c r="Q23" s="27"/>
-      <c r="R23" s="27"/>
-    </row>
-    <row r="24" spans="1:24" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A24" s="6"/>
-      <c r="B24" s="28" t="s">
+      <c r="D16" s="47"/>
+      <c r="E16" s="47"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="7"/>
+      <c r="M16" s="7"/>
+    </row>
+    <row r="17" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="D17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="7"/>
+      <c r="M17" s="7"/>
+    </row>
+    <row r="18" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="D18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="7"/>
+      <c r="M18" s="7"/>
+    </row>
+    <row r="19" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="D19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="7"/>
+      <c r="M19" s="7"/>
+    </row>
+    <row r="20" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="D20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="7"/>
+      <c r="K20" s="7"/>
+      <c r="L20" s="7"/>
+      <c r="M20" s="7"/>
+    </row>
+    <row r="21" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="D21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="7"/>
+      <c r="J21" s="7"/>
+      <c r="K21" s="7"/>
+      <c r="L21" s="7"/>
+      <c r="M21" s="7"/>
+    </row>
+    <row r="22" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="D22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="7"/>
+      <c r="J22" s="7"/>
+      <c r="K22" s="7"/>
+      <c r="L22" s="7"/>
+      <c r="M22" s="7"/>
+    </row>
+    <row r="23" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="C23" s="1"/>
+      <c r="D23" s="21"/>
+      <c r="O23" s="6"/>
+      <c r="P23" s="6"/>
+      <c r="Q23" s="6"/>
+      <c r="R23" s="6"/>
+    </row>
+    <row r="24" spans="2:24" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="B24" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="C24" s="70" t="s">
+      <c r="C24" s="57" t="s">
         <v>116</v>
       </c>
-      <c r="D24" s="121" t="s">
+      <c r="D24" s="103" t="s">
         <v>51</v>
       </c>
-      <c r="E24" s="122" t="s">
+      <c r="E24" s="104" t="s">
         <v>52</v>
       </c>
-      <c r="F24" s="122" t="s">
+      <c r="F24" s="104" t="s">
         <v>128</v>
       </c>
-      <c r="G24" s="122" t="s">
+      <c r="G24" s="104" t="s">
         <v>141</v>
       </c>
-      <c r="H24" s="122" t="s">
+      <c r="H24" s="104" t="s">
         <v>138</v>
       </c>
-      <c r="I24" s="122" t="s">
+      <c r="I24" s="104" t="s">
         <v>131</v>
       </c>
-      <c r="J24" s="122" t="s">
+      <c r="J24" s="104" t="s">
         <v>139</v>
       </c>
-      <c r="K24" s="122" t="s">
+      <c r="K24" s="104" t="s">
         <v>140</v>
       </c>
-      <c r="L24" s="122" t="s">
+      <c r="L24" s="104" t="s">
         <v>136</v>
       </c>
-      <c r="M24" s="122" t="s">
+      <c r="M24" s="104" t="s">
         <v>137</v>
       </c>
-      <c r="N24" s="122" t="s">
+      <c r="N24" s="104" t="s">
         <v>53</v>
       </c>
-      <c r="O24" s="55" t="s">
+      <c r="O24" s="42" t="s">
         <v>172</v>
       </c>
-      <c r="P24" s="55" t="s">
+      <c r="P24" s="42" t="s">
         <v>173</v>
       </c>
-      <c r="Q24" s="55" t="s">
+      <c r="Q24" s="42" t="s">
         <v>174</v>
       </c>
-      <c r="R24" s="55" t="s">
+      <c r="R24" s="42" t="s">
         <v>175</v>
       </c>
-      <c r="S24" s="122" t="s">
+      <c r="S24" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="T24" s="122" t="s">
+      <c r="T24" s="104" t="s">
         <v>55</v>
       </c>
-      <c r="U24" s="123" t="s">
+      <c r="U24" s="105" t="s">
         <v>88</v>
       </c>
-      <c r="V24" s="55" t="s">
+      <c r="V24" s="42" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="25" spans="1:24" ht="15" x14ac:dyDescent="0.25">
-      <c r="A25" s="6"/>
-      <c r="B25" s="103" t="s">
+    <row r="25" spans="2:24" ht="15" x14ac:dyDescent="0.25">
+      <c r="B25" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="C25" s="67" t="s">
+      <c r="C25" s="54" t="s">
         <v>164</v>
       </c>
-      <c r="D25" s="104"/>
-      <c r="E25" s="108">
+      <c r="D25" s="88"/>
+      <c r="E25" s="92">
         <v>1</v>
       </c>
-      <c r="F25" s="105"/>
-      <c r="G25" s="108">
+      <c r="F25" s="89"/>
+      <c r="G25" s="92">
         <v>0.9</v>
       </c>
-      <c r="H25" s="105"/>
-      <c r="I25" s="108">
+      <c r="H25" s="89"/>
+      <c r="I25" s="92">
         <v>1</v>
       </c>
-      <c r="J25" s="108">
+      <c r="J25" s="92">
         <v>1</v>
       </c>
-      <c r="K25" s="105"/>
-      <c r="L25" s="105"/>
-      <c r="M25" s="105"/>
-      <c r="N25" s="105"/>
-      <c r="O25" s="108">
+      <c r="K25" s="89"/>
+      <c r="L25" s="89"/>
+      <c r="M25" s="89"/>
+      <c r="N25" s="89"/>
+      <c r="O25" s="92">
         <v>0.5</v>
       </c>
-      <c r="P25" s="105"/>
-      <c r="Q25" s="105"/>
-      <c r="R25" s="105"/>
-      <c r="S25" s="105"/>
-      <c r="T25" s="105"/>
-      <c r="U25" s="126">
-        <v>0</v>
-      </c>
-      <c r="V25" s="68"/>
-      <c r="W25" s="8"/>
-      <c r="X25" s="64" t="s">
+      <c r="P25" s="89"/>
+      <c r="Q25" s="89"/>
+      <c r="R25" s="89"/>
+      <c r="S25" s="89"/>
+      <c r="T25" s="89"/>
+      <c r="U25" s="108">
+        <v>0</v>
+      </c>
+      <c r="V25" s="55"/>
+      <c r="X25" s="51" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="26" spans="1:24" ht="15" x14ac:dyDescent="0.25">
-      <c r="A26" s="6"/>
-      <c r="B26" s="103" t="s">
+    <row r="26" spans="2:24" ht="15" x14ac:dyDescent="0.25">
+      <c r="B26" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="C26" s="69" t="s">
+      <c r="C26" s="56" t="s">
         <v>165</v>
       </c>
-      <c r="D26" s="106"/>
-      <c r="E26" s="109">
+      <c r="D26" s="90"/>
+      <c r="E26" s="93">
         <f>1-E25</f>
         <v>0</v>
       </c>
-      <c r="F26" s="107"/>
-      <c r="G26" s="109">
+      <c r="F26" s="91"/>
+      <c r="G26" s="93">
         <f>1-G25</f>
         <v>9.9999999999999978E-2</v>
       </c>
-      <c r="H26" s="107"/>
-      <c r="I26" s="109">
+      <c r="H26" s="91"/>
+      <c r="I26" s="93">
         <f>1-I25</f>
         <v>0</v>
       </c>
-      <c r="J26" s="109">
+      <c r="J26" s="93">
         <f>1-J25</f>
         <v>0</v>
       </c>
-      <c r="K26" s="107"/>
-      <c r="L26" s="107"/>
-      <c r="M26" s="107"/>
-      <c r="N26" s="107"/>
-      <c r="O26" s="109">
+      <c r="K26" s="91"/>
+      <c r="L26" s="91"/>
+      <c r="M26" s="91"/>
+      <c r="N26" s="91"/>
+      <c r="O26" s="93">
         <f>1-O25</f>
         <v>0.5</v>
       </c>
-      <c r="P26" s="107"/>
-      <c r="Q26" s="107"/>
-      <c r="R26" s="107"/>
-      <c r="S26" s="107"/>
-      <c r="T26" s="107"/>
-      <c r="U26" s="127">
+      <c r="P26" s="91"/>
+      <c r="Q26" s="91"/>
+      <c r="R26" s="91"/>
+      <c r="S26" s="91"/>
+      <c r="T26" s="91"/>
+      <c r="U26" s="109">
         <f>1-U25</f>
         <v>1</v>
       </c>
-      <c r="V26" s="58"/>
-      <c r="W26" s="8"/>
-      <c r="X26" s="66" t="s">
+      <c r="V26" s="45"/>
+      <c r="X26" s="53" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A27" s="6"/>
-      <c r="V27" s="8"/>
-    </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A28" s="6"/>
-      <c r="V28" s="8"/>
-    </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A29" s="6"/>
-      <c r="C29" s="71" t="s">
+    <row r="29" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="C29" s="58" t="s">
         <v>106</v>
       </c>
-      <c r="D29" s="73" t="s">
+      <c r="D29" s="60" t="s">
         <v>107</v>
       </c>
-      <c r="E29" s="72" t="s">
+      <c r="E29" s="59" t="s">
         <v>108</v>
       </c>
-      <c r="V29" s="8"/>
-    </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A30" s="6"/>
-      <c r="B30" s="24" t="s">
+    </row>
+    <row r="30" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B30" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="C30" s="101" t="s">
+      <c r="C30" s="86" t="s">
         <v>109</v>
       </c>
-      <c r="D30" s="101" t="s">
+      <c r="D30" s="86" t="s">
         <v>110</v>
       </c>
-      <c r="E30" s="102" t="s">
+      <c r="E30" s="87" t="s">
         <v>108</v>
       </c>
-      <c r="V30" s="8"/>
-    </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A31" s="6"/>
-      <c r="B31" s="56" t="s">
+    </row>
+    <row r="31" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B31" s="43" t="s">
         <v>66</v>
       </c>
-      <c r="C31" s="128">
+      <c r="C31" s="110">
         <v>1</v>
       </c>
-      <c r="D31" s="129"/>
-      <c r="E31" s="130"/>
+      <c r="D31" s="111"/>
+      <c r="E31" s="112"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6142,28 +6087,28 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B3:G5"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="1.85546875" style="29" customWidth="1"/>
-    <col min="2" max="2" width="7.7109375" style="29" customWidth="1"/>
-    <col min="3" max="3" width="6.85546875" style="29" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" width="1.85546875" style="23" customWidth="1"/>
+    <col min="2" max="2" width="7.7109375" style="23" customWidth="1"/>
+    <col min="3" max="3" width="6.85546875" style="23" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="23"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:7" ht="18" x14ac:dyDescent="0.25">
-      <c r="B3" s="124" t="s">
+      <c r="B3" s="106" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="D5" s="125" t="s">
+      <c r="D5" s="107" t="s">
         <v>167</v>
       </c>
-      <c r="E5" s="125"/>
-      <c r="F5" s="125"/>
-      <c r="G5" s="125"/>
+      <c r="E5" s="107"/>
+      <c r="F5" s="107"/>
+      <c r="G5" s="107"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6173,7 +6118,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:R36"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
@@ -6198,296 +6143,278 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:18" ht="15" x14ac:dyDescent="0.25">
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="H1" s="43"/>
+      <c r="H1" s="30"/>
     </row>
     <row r="2" spans="2:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B2" s="14" t="str">
+      <c r="B2" s="10" t="str">
         <f>'EB2'!B9</f>
         <v>TRA</v>
       </c>
-      <c r="C2" s="14" t="str">
+      <c r="C2" s="10" t="str">
         <f>'EB2'!C9</f>
         <v>Transport</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="D2" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="E2" s="14" t="str">
+      <c r="E2" s="10" t="str">
         <f>'EB2'!Z2</f>
         <v>PJ</v>
       </c>
-      <c r="F2" s="14" t="str">
+      <c r="F2" s="10" t="str">
         <f>'EB2'!Y2</f>
         <v>M€2005</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="G2" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="H2" s="13"/>
-      <c r="J2" s="133" t="s">
+      <c r="H2" s="9"/>
+      <c r="J2" s="115" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="133"/>
-      <c r="L2" s="134"/>
-      <c r="M2" s="134"/>
-      <c r="N2" s="134"/>
-      <c r="O2" s="134"/>
-      <c r="P2" s="134"/>
-      <c r="Q2" s="134"/>
-      <c r="R2" s="134"/>
+      <c r="K2" s="115"/>
+      <c r="L2" s="116"/>
+      <c r="M2" s="116"/>
+      <c r="N2" s="116"/>
+      <c r="O2" s="116"/>
+      <c r="P2" s="116"/>
+      <c r="Q2" s="116"/>
+      <c r="R2" s="116"/>
     </row>
     <row r="3" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="J3" s="135" t="s">
+      <c r="J3" s="117" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="136" t="s">
+      <c r="K3" s="118" t="s">
         <v>30</v>
       </c>
-      <c r="L3" s="135" t="s">
-        <v>0</v>
-      </c>
-      <c r="M3" s="135" t="s">
+      <c r="L3" s="117" t="s">
+        <v>0</v>
+      </c>
+      <c r="M3" s="117" t="s">
         <v>3</v>
       </c>
-      <c r="N3" s="135" t="s">
+      <c r="N3" s="117" t="s">
         <v>4</v>
       </c>
-      <c r="O3" s="135" t="s">
+      <c r="O3" s="117" t="s">
         <v>8</v>
       </c>
-      <c r="P3" s="135" t="s">
+      <c r="P3" s="117" t="s">
         <v>9</v>
       </c>
-      <c r="Q3" s="135" t="s">
+      <c r="Q3" s="117" t="s">
         <v>10</v>
       </c>
-      <c r="R3" s="135" t="s">
+      <c r="R3" s="117" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:18" s="6" customFormat="1" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="J4" s="137" t="s">
+    <row r="4" spans="2:18" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="J4" s="119" t="s">
         <v>37</v>
       </c>
-      <c r="K4" s="137" t="s">
+      <c r="K4" s="119" t="s">
         <v>31</v>
       </c>
-      <c r="L4" s="137" t="s">
+      <c r="L4" s="119" t="s">
         <v>26</v>
       </c>
-      <c r="M4" s="137" t="s">
+      <c r="M4" s="119" t="s">
         <v>27</v>
       </c>
-      <c r="N4" s="137" t="s">
+      <c r="N4" s="119" t="s">
         <v>4</v>
       </c>
-      <c r="O4" s="137" t="s">
+      <c r="O4" s="119" t="s">
         <v>40</v>
       </c>
-      <c r="P4" s="137" t="s">
+      <c r="P4" s="119" t="s">
         <v>41</v>
       </c>
-      <c r="Q4" s="137" t="s">
+      <c r="Q4" s="119" t="s">
         <v>28</v>
       </c>
-      <c r="R4" s="137" t="s">
+      <c r="R4" s="119" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="85"/>
-      <c r="H5" s="15"/>
-      <c r="J5" s="138" t="s">
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="70"/>
+      <c r="H5" s="11"/>
+      <c r="J5" s="120" t="s">
         <v>72</v>
       </c>
-      <c r="K5" s="138"/>
-      <c r="L5" s="138" t="str">
+      <c r="K5" s="120"/>
+      <c r="L5" s="120" t="str">
         <f>$B$2&amp;'EB2'!$E$2</f>
         <v>TRAGAS</v>
       </c>
-      <c r="M5" s="139" t="str">
+      <c r="M5" s="121" t="str">
         <f>$C$2&amp;" "&amp;'EB2'!$E$3</f>
         <v>Transport Natural Gas</v>
       </c>
-      <c r="N5" s="138" t="str">
+      <c r="N5" s="120" t="str">
         <f t="shared" ref="N5:N10" si="0">$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="O5" s="138"/>
-      <c r="P5" s="138"/>
-      <c r="Q5" s="138"/>
-      <c r="R5" s="138"/>
+      <c r="O5" s="120"/>
+      <c r="P5" s="120"/>
+      <c r="Q5" s="120"/>
+      <c r="R5" s="120"/>
     </row>
     <row r="6" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="85"/>
-      <c r="H6" s="15"/>
-      <c r="J6" s="138"/>
-      <c r="K6" s="138"/>
-      <c r="L6" s="138" t="str">
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="70"/>
+      <c r="H6" s="11"/>
+      <c r="J6" s="120"/>
+      <c r="K6" s="120"/>
+      <c r="L6" s="120" t="str">
         <f>$B$2&amp;'EB2'!$G$2</f>
         <v>TRADSL</v>
       </c>
-      <c r="M6" s="139" t="str">
+      <c r="M6" s="121" t="str">
         <f>$C$2&amp;" "&amp;'EB2'!$G$3</f>
         <v>Transport Diesel oil</v>
       </c>
-      <c r="N6" s="138" t="str">
+      <c r="N6" s="120" t="str">
         <f t="shared" si="0"/>
         <v>PJ</v>
       </c>
-      <c r="O6" s="138"/>
-      <c r="P6" s="138"/>
-      <c r="Q6" s="138"/>
-      <c r="R6" s="138"/>
+      <c r="O6" s="120"/>
+      <c r="P6" s="120"/>
+      <c r="Q6" s="120"/>
+      <c r="R6" s="120"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="85"/>
-      <c r="H7" s="15"/>
-      <c r="J7" s="138"/>
-      <c r="K7" s="138"/>
-      <c r="L7" s="138" t="str">
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="70"/>
+      <c r="H7" s="11"/>
+      <c r="J7" s="120"/>
+      <c r="K7" s="120"/>
+      <c r="L7" s="120" t="str">
         <f>$B$2&amp;'EB2'!$I$2</f>
         <v>TRALPG</v>
       </c>
-      <c r="M7" s="139" t="str">
+      <c r="M7" s="121" t="str">
         <f>$C$2&amp;" "&amp;'EB2'!$I$3</f>
         <v>Transport LPG</v>
       </c>
-      <c r="N7" s="138" t="str">
+      <c r="N7" s="120" t="str">
         <f t="shared" si="0"/>
         <v>PJ</v>
       </c>
-      <c r="O7" s="138"/>
-      <c r="P7" s="138"/>
-      <c r="Q7" s="138"/>
-      <c r="R7" s="138"/>
+      <c r="O7" s="120"/>
+      <c r="P7" s="120"/>
+      <c r="Q7" s="120"/>
+      <c r="R7" s="120"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="85"/>
-      <c r="H8" s="15"/>
-      <c r="J8" s="138"/>
-      <c r="K8" s="138"/>
-      <c r="L8" s="138" t="str">
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="70"/>
+      <c r="H8" s="11"/>
+      <c r="J8" s="120"/>
+      <c r="K8" s="120"/>
+      <c r="L8" s="120" t="str">
         <f>$B$2&amp;'EB2'!$J$2</f>
         <v>TRAGSL</v>
       </c>
-      <c r="M8" s="139" t="str">
+      <c r="M8" s="121" t="str">
         <f>$C$2&amp;" "&amp;'EB2'!$J$3</f>
         <v>Transport Motor spirit</v>
       </c>
-      <c r="N8" s="138" t="str">
+      <c r="N8" s="120" t="str">
         <f t="shared" si="0"/>
         <v>PJ</v>
       </c>
-      <c r="O8" s="138"/>
-      <c r="P8" s="138"/>
-      <c r="Q8" s="138"/>
-      <c r="R8" s="138"/>
+      <c r="O8" s="120"/>
+      <c r="P8" s="120"/>
+      <c r="Q8" s="120"/>
+      <c r="R8" s="120"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="85"/>
-      <c r="H9" s="15"/>
-      <c r="J9" s="138"/>
-      <c r="K9" s="138"/>
-      <c r="L9" s="138" t="str">
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="70"/>
+      <c r="H9" s="11"/>
+      <c r="J9" s="120"/>
+      <c r="K9" s="120"/>
+      <c r="L9" s="120" t="str">
         <f>$B$2&amp;'EB2'!$O$2</f>
         <v>TRABIO</v>
       </c>
-      <c r="M9" s="139" t="str">
+      <c r="M9" s="121" t="str">
         <f>$C$2&amp;" "&amp;'EB2'!$O$3</f>
         <v>Transport Biofuels</v>
       </c>
-      <c r="N9" s="138" t="str">
+      <c r="N9" s="120" t="str">
         <f t="shared" si="0"/>
         <v>PJ</v>
       </c>
-      <c r="O9" s="140"/>
-      <c r="P9" s="140"/>
-      <c r="Q9" s="140"/>
-      <c r="R9" s="140"/>
+      <c r="O9" s="120"/>
+      <c r="P9" s="120"/>
+      <c r="Q9" s="120"/>
+      <c r="R9" s="120"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="85"/>
-      <c r="H10" s="15"/>
-      <c r="J10" s="138"/>
-      <c r="K10" s="138"/>
-      <c r="L10" s="138" t="str">
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="70"/>
+      <c r="H10" s="11"/>
+      <c r="J10" s="120"/>
+      <c r="K10" s="120"/>
+      <c r="L10" s="120" t="str">
         <f>$B$2&amp;'EB2'!$U$2</f>
         <v>TRAELC</v>
       </c>
-      <c r="M10" s="139" t="str">
+      <c r="M10" s="121" t="str">
         <f>$C$2&amp;" "&amp;'EB2'!$U$3</f>
         <v>Transport Electricity</v>
       </c>
-      <c r="N10" s="138" t="str">
+      <c r="N10" s="120" t="str">
         <f t="shared" si="0"/>
         <v>PJ</v>
       </c>
-      <c r="O10" s="138"/>
-      <c r="P10" s="138" t="s">
+      <c r="O10" s="120"/>
+      <c r="P10" s="120" t="s">
         <v>125</v>
       </c>
-      <c r="Q10" s="138"/>
-      <c r="R10" s="138" t="s">
+      <c r="Q10" s="120"/>
+      <c r="R10" s="120" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="L11" s="32"/>
-      <c r="M11" s="34"/>
+      <c r="L11" s="23"/>
+      <c r="M11" s="24"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.2">
       <c r="D12" s="5" t="s">
@@ -6495,144 +6422,144 @@
       </c>
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
-      <c r="J12" s="133" t="s">
+      <c r="J12" s="115" t="s">
         <v>15</v>
       </c>
-      <c r="K12" s="133"/>
-      <c r="L12" s="140"/>
-      <c r="M12" s="140"/>
-      <c r="N12" s="140"/>
-      <c r="O12" s="140"/>
-      <c r="P12" s="140"/>
-      <c r="Q12" s="140"/>
-      <c r="R12" s="140"/>
+      <c r="K12" s="115"/>
+      <c r="L12" s="120"/>
+      <c r="M12" s="120"/>
+      <c r="N12" s="120"/>
+      <c r="O12" s="120"/>
+      <c r="P12" s="120"/>
+      <c r="Q12" s="120"/>
+      <c r="R12" s="120"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B13" s="21" t="s">
+      <c r="B13" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="21" t="s">
+      <c r="C13" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="D13" s="21" t="s">
+      <c r="D13" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="E13" s="89" t="s">
+      <c r="E13" s="74" t="s">
         <v>155</v>
       </c>
-      <c r="F13" s="86" t="s">
+      <c r="F13" s="71" t="s">
         <v>127</v>
       </c>
-      <c r="G13" s="86" t="s">
+      <c r="G13" s="71" t="s">
         <v>85</v>
       </c>
-      <c r="H13" s="86" t="s">
+      <c r="H13" s="71" t="s">
         <v>79</v>
       </c>
-      <c r="J13" s="135" t="s">
+      <c r="J13" s="117" t="s">
         <v>11</v>
       </c>
-      <c r="K13" s="136" t="s">
+      <c r="K13" s="118" t="s">
         <v>30</v>
       </c>
-      <c r="L13" s="135" t="s">
+      <c r="L13" s="117" t="s">
         <v>1</v>
       </c>
-      <c r="M13" s="135" t="s">
+      <c r="M13" s="117" t="s">
         <v>2</v>
       </c>
-      <c r="N13" s="135" t="s">
+      <c r="N13" s="117" t="s">
         <v>16</v>
       </c>
-      <c r="O13" s="135" t="s">
+      <c r="O13" s="117" t="s">
         <v>17</v>
       </c>
-      <c r="P13" s="135" t="s">
+      <c r="P13" s="117" t="s">
         <v>18</v>
       </c>
-      <c r="Q13" s="135" t="s">
+      <c r="Q13" s="117" t="s">
         <v>19</v>
       </c>
-      <c r="R13" s="135" t="s">
+      <c r="R13" s="117" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="14" spans="2:18" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="20" t="s">
+      <c r="B14" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="C14" s="20" t="s">
+      <c r="C14" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="D14" s="20" t="s">
+      <c r="D14" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="E14" s="20" t="s">
+      <c r="E14" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="F14" s="20" t="s">
+      <c r="F14" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="G14" s="20" t="s">
+      <c r="G14" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="H14" s="20" t="s">
+      <c r="H14" s="16" t="s">
         <v>177</v>
       </c>
-      <c r="J14" s="137" t="s">
+      <c r="J14" s="119" t="s">
         <v>38</v>
       </c>
-      <c r="K14" s="137" t="s">
+      <c r="K14" s="119" t="s">
         <v>31</v>
       </c>
-      <c r="L14" s="137" t="s">
+      <c r="L14" s="119" t="s">
         <v>21</v>
       </c>
-      <c r="M14" s="137" t="s">
+      <c r="M14" s="119" t="s">
         <v>22</v>
       </c>
-      <c r="N14" s="137" t="s">
+      <c r="N14" s="119" t="s">
         <v>23</v>
       </c>
-      <c r="O14" s="137" t="s">
+      <c r="O14" s="119" t="s">
         <v>24</v>
       </c>
-      <c r="P14" s="137" t="s">
+      <c r="P14" s="119" t="s">
         <v>43</v>
       </c>
-      <c r="Q14" s="137" t="s">
+      <c r="Q14" s="119" t="s">
         <v>42</v>
       </c>
-      <c r="R14" s="137" t="s">
+      <c r="R14" s="119" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="15" spans="2:18" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17" t="str">
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13" t="str">
         <f>E2&amp;"a"</f>
         <v>PJa</v>
       </c>
-      <c r="G15" s="17"/>
-      <c r="H15" s="17" t="s">
+      <c r="G15" s="13"/>
+      <c r="H15" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="J15" s="137" t="s">
+      <c r="J15" s="119" t="s">
         <v>81</v>
       </c>
-      <c r="K15" s="141"/>
-      <c r="L15" s="141"/>
-      <c r="M15" s="141"/>
-      <c r="N15" s="141"/>
-      <c r="O15" s="141"/>
-      <c r="P15" s="141"/>
-      <c r="Q15" s="141"/>
-      <c r="R15" s="141"/>
+      <c r="K15" s="122"/>
+      <c r="L15" s="122"/>
+      <c r="M15" s="122"/>
+      <c r="N15" s="122"/>
+      <c r="O15" s="122"/>
+      <c r="P15" s="122"/>
+      <c r="Q15" s="122"/>
+      <c r="R15" s="122"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B16" t="str">
@@ -6647,37 +6574,37 @@
         <f t="shared" ref="D16:D21" si="3">L5</f>
         <v>TRAGAS</v>
       </c>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="78">
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="65">
         <v>1</v>
       </c>
-      <c r="H16" s="79">
+      <c r="H16" s="66">
         <v>50</v>
       </c>
-      <c r="J16" s="142" t="s">
+      <c r="J16" s="116" t="s">
         <v>112</v>
       </c>
-      <c r="K16" s="138"/>
-      <c r="L16" s="138" t="str">
+      <c r="K16" s="120"/>
+      <c r="L16" s="120" t="str">
         <f t="shared" ref="L16:L21" si="4">"FT"&amp;$G$2&amp;"-"&amp;L5</f>
         <v>FTE-TRAGAS</v>
       </c>
-      <c r="M16" s="139" t="str">
+      <c r="M16" s="121" t="str">
         <f t="shared" ref="M16:M21" si="5">$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M5</f>
         <v>Sector Fuel Technology Existing Transport Natural Gas</v>
       </c>
-      <c r="N16" s="138" t="str">
+      <c r="N16" s="120" t="str">
         <f t="shared" ref="N16:N21" si="6">$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="O16" s="138" t="str">
+      <c r="O16" s="120" t="str">
         <f t="shared" ref="O16:O21" si="7">$E$2&amp;"a"</f>
         <v>PJa</v>
       </c>
-      <c r="P16" s="138"/>
-      <c r="Q16" s="138"/>
-      <c r="R16" s="138"/>
+      <c r="P16" s="120"/>
+      <c r="Q16" s="120"/>
+      <c r="R16" s="120"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B17" t="str">
@@ -6692,35 +6619,35 @@
         <f t="shared" si="3"/>
         <v>TRADSL</v>
       </c>
-      <c r="E17" s="16"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="78">
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="65">
         <v>1</v>
       </c>
-      <c r="H17" s="79">
+      <c r="H17" s="66">
         <v>50</v>
       </c>
-      <c r="J17" s="142"/>
-      <c r="K17" s="138"/>
-      <c r="L17" s="138" t="str">
+      <c r="J17" s="116"/>
+      <c r="K17" s="120"/>
+      <c r="L17" s="120" t="str">
         <f t="shared" si="4"/>
         <v>FTE-TRADSL</v>
       </c>
-      <c r="M17" s="139" t="str">
+      <c r="M17" s="121" t="str">
         <f t="shared" si="5"/>
         <v>Sector Fuel Technology Existing Transport Diesel oil</v>
       </c>
-      <c r="N17" s="138" t="str">
+      <c r="N17" s="120" t="str">
         <f t="shared" si="6"/>
         <v>PJ</v>
       </c>
-      <c r="O17" s="138" t="str">
+      <c r="O17" s="120" t="str">
         <f t="shared" si="7"/>
         <v>PJa</v>
       </c>
-      <c r="P17" s="138"/>
-      <c r="Q17" s="138"/>
-      <c r="R17" s="138"/>
+      <c r="P17" s="120"/>
+      <c r="Q17" s="120"/>
+      <c r="R17" s="120"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B18" t="str">
@@ -6735,35 +6662,35 @@
         <f t="shared" si="3"/>
         <v>TRALPG</v>
       </c>
-      <c r="E18" s="16"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="78">
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="65">
         <v>1</v>
       </c>
-      <c r="H18" s="79">
+      <c r="H18" s="66">
         <v>50</v>
       </c>
-      <c r="J18" s="138"/>
-      <c r="K18" s="138"/>
-      <c r="L18" s="138" t="str">
+      <c r="J18" s="120"/>
+      <c r="K18" s="120"/>
+      <c r="L18" s="120" t="str">
         <f t="shared" si="4"/>
         <v>FTE-TRALPG</v>
       </c>
-      <c r="M18" s="139" t="str">
+      <c r="M18" s="121" t="str">
         <f t="shared" si="5"/>
         <v>Sector Fuel Technology Existing Transport LPG</v>
       </c>
-      <c r="N18" s="138" t="str">
+      <c r="N18" s="120" t="str">
         <f t="shared" si="6"/>
         <v>PJ</v>
       </c>
-      <c r="O18" s="138" t="str">
+      <c r="O18" s="120" t="str">
         <f t="shared" si="7"/>
         <v>PJa</v>
       </c>
-      <c r="P18" s="138"/>
-      <c r="Q18" s="138"/>
-      <c r="R18" s="138"/>
+      <c r="P18" s="120"/>
+      <c r="Q18" s="120"/>
+      <c r="R18" s="120"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B19" t="str">
@@ -6778,35 +6705,35 @@
         <f t="shared" si="3"/>
         <v>TRAGSL</v>
       </c>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="78">
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="65">
         <v>1</v>
       </c>
-      <c r="H19" s="79">
+      <c r="H19" s="66">
         <v>50</v>
       </c>
-      <c r="J19" s="138"/>
-      <c r="K19" s="138"/>
-      <c r="L19" s="138" t="str">
+      <c r="J19" s="120"/>
+      <c r="K19" s="120"/>
+      <c r="L19" s="120" t="str">
         <f t="shared" si="4"/>
         <v>FTE-TRAGSL</v>
       </c>
-      <c r="M19" s="139" t="str">
+      <c r="M19" s="121" t="str">
         <f t="shared" si="5"/>
         <v>Sector Fuel Technology Existing Transport Motor spirit</v>
       </c>
-      <c r="N19" s="138" t="str">
+      <c r="N19" s="120" t="str">
         <f t="shared" si="6"/>
         <v>PJ</v>
       </c>
-      <c r="O19" s="138" t="str">
+      <c r="O19" s="120" t="str">
         <f t="shared" si="7"/>
         <v>PJa</v>
       </c>
-      <c r="P19" s="138"/>
-      <c r="Q19" s="138"/>
-      <c r="R19" s="138"/>
+      <c r="P19" s="120"/>
+      <c r="Q19" s="120"/>
+      <c r="R19" s="120"/>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B20" t="str">
@@ -6821,35 +6748,35 @@
         <f t="shared" si="3"/>
         <v>TRABIO</v>
       </c>
-      <c r="E20" s="16"/>
-      <c r="F20" s="16"/>
-      <c r="G20" s="78">
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="65">
         <v>1</v>
       </c>
-      <c r="H20" s="79">
+      <c r="H20" s="66">
         <v>50</v>
       </c>
-      <c r="J20" s="138"/>
-      <c r="K20" s="138"/>
-      <c r="L20" s="138" t="str">
+      <c r="J20" s="120"/>
+      <c r="K20" s="120"/>
+      <c r="L20" s="120" t="str">
         <f t="shared" si="4"/>
         <v>FTE-TRABIO</v>
       </c>
-      <c r="M20" s="139" t="str">
+      <c r="M20" s="121" t="str">
         <f t="shared" si="5"/>
         <v>Sector Fuel Technology Existing Transport Biofuels</v>
       </c>
-      <c r="N20" s="138" t="str">
+      <c r="N20" s="120" t="str">
         <f t="shared" si="6"/>
         <v>PJ</v>
       </c>
-      <c r="O20" s="138" t="str">
+      <c r="O20" s="120" t="str">
         <f t="shared" si="7"/>
         <v>PJa</v>
       </c>
-      <c r="P20" s="138"/>
-      <c r="Q20" s="138"/>
-      <c r="R20" s="138"/>
+      <c r="P20" s="120"/>
+      <c r="Q20" s="120"/>
+      <c r="R20" s="120"/>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B21" t="str">
@@ -6864,208 +6791,135 @@
         <f t="shared" si="3"/>
         <v>TRAELC</v>
       </c>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="78">
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="65">
         <v>1</v>
       </c>
-      <c r="H21" s="79">
+      <c r="H21" s="66">
         <v>50</v>
       </c>
-      <c r="J21" s="138"/>
-      <c r="K21" s="138"/>
-      <c r="L21" s="138" t="str">
+      <c r="J21" s="120"/>
+      <c r="K21" s="120"/>
+      <c r="L21" s="120" t="str">
         <f t="shared" si="4"/>
         <v>FTE-TRAELC</v>
       </c>
-      <c r="M21" s="139" t="str">
+      <c r="M21" s="121" t="str">
         <f t="shared" si="5"/>
         <v>Sector Fuel Technology Existing Transport Electricity</v>
       </c>
-      <c r="N21" s="138" t="str">
+      <c r="N21" s="120" t="str">
         <f t="shared" si="6"/>
         <v>PJ</v>
       </c>
-      <c r="O21" s="138" t="str">
+      <c r="O21" s="120" t="str">
         <f t="shared" si="7"/>
         <v>PJa</v>
       </c>
-      <c r="P21" s="138" t="s">
+      <c r="P21" s="120" t="s">
         <v>125</v>
       </c>
-      <c r="Q21" s="138"/>
-      <c r="R21" s="138"/>
+      <c r="Q21" s="120"/>
+      <c r="R21" s="120"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="85"/>
-      <c r="H22" s="15"/>
-      <c r="J22" s="6"/>
-      <c r="K22" s="6"/>
-      <c r="L22" s="6"/>
-      <c r="M22" s="23"/>
-      <c r="N22" s="6"/>
-      <c r="O22" s="6"/>
-      <c r="P22" s="6"/>
-      <c r="Q22" s="6"/>
-      <c r="R22" s="6"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="11"/>
+      <c r="M22" s="19"/>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B23" s="38"/>
-      <c r="C23" s="38"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="85"/>
-      <c r="H23" s="15"/>
-      <c r="J23" s="6"/>
-      <c r="K23" s="6"/>
-      <c r="L23" s="6"/>
-      <c r="M23" s="23"/>
-      <c r="N23" s="6"/>
-      <c r="O23" s="6"/>
-      <c r="P23" s="6"/>
-      <c r="Q23" s="6"/>
-      <c r="R23" s="6"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="11"/>
+      <c r="M23" s="19"/>
     </row>
     <row r="24" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B24" s="31"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="31"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="85"/>
-      <c r="H24" s="15"/>
-      <c r="J24" s="6"/>
-      <c r="K24" s="6"/>
-      <c r="L24" s="6"/>
-      <c r="M24" s="23"/>
-      <c r="N24" s="6"/>
-      <c r="O24" s="6"/>
-      <c r="P24" s="6"/>
-      <c r="Q24" s="6"/>
-      <c r="R24" s="6"/>
+      <c r="B24" s="23"/>
+      <c r="D24" s="23"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="70"/>
+      <c r="H24" s="11"/>
+      <c r="M24" s="19"/>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B25" s="31"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="31"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="85"/>
-      <c r="H25" s="15"/>
-      <c r="J25" s="30"/>
-      <c r="K25" s="29"/>
-      <c r="L25" s="6"/>
-      <c r="M25" s="23"/>
-      <c r="N25" s="6"/>
-      <c r="O25" s="6"/>
-      <c r="P25" s="6"/>
-      <c r="Q25" s="6"/>
-      <c r="R25" s="6"/>
+      <c r="B25" s="23"/>
+      <c r="D25" s="23"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="70"/>
+      <c r="H25" s="11"/>
+      <c r="J25" s="23"/>
+      <c r="K25" s="23"/>
+      <c r="M25" s="19"/>
     </row>
     <row r="26" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B26" s="31"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="31"/>
-      <c r="E26" s="110"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="85"/>
-      <c r="H26" s="15"/>
-      <c r="J26" s="29"/>
-      <c r="K26" s="29"/>
-      <c r="L26" s="6"/>
-      <c r="M26" s="23"/>
-      <c r="N26" s="6"/>
-      <c r="O26" s="6"/>
-      <c r="P26" s="6"/>
-      <c r="Q26" s="6"/>
-      <c r="R26" s="6"/>
+      <c r="B26" s="23"/>
+      <c r="D26" s="23"/>
+      <c r="E26" s="94"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="70"/>
+      <c r="H26" s="11"/>
+      <c r="J26" s="23"/>
+      <c r="K26" s="23"/>
+      <c r="M26" s="19"/>
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B27" s="31"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="31"/>
-      <c r="E27" s="110"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="85"/>
-      <c r="H27" s="15"/>
-      <c r="J27" s="37"/>
-      <c r="K27" s="33"/>
-      <c r="L27" s="6"/>
-      <c r="M27" s="23"/>
-      <c r="N27" s="6"/>
-      <c r="O27" s="6"/>
-      <c r="P27" s="6"/>
-      <c r="Q27" s="6"/>
-      <c r="R27" s="6"/>
+      <c r="B27" s="23"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="94"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="70"/>
+      <c r="H27" s="11"/>
+      <c r="J27" s="23"/>
+      <c r="K27" s="23"/>
+      <c r="M27" s="19"/>
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B28" s="31"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="110"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="85"/>
-      <c r="H28" s="15"/>
-      <c r="J28" s="38"/>
-      <c r="K28" s="38"/>
-      <c r="L28" s="6"/>
-      <c r="M28" s="23"/>
-      <c r="N28" s="6"/>
-      <c r="O28" s="6"/>
-      <c r="P28" s="38"/>
-      <c r="Q28" s="38"/>
-      <c r="R28" s="6"/>
+      <c r="B28" s="23"/>
+      <c r="D28" s="23"/>
+      <c r="E28" s="94"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="70"/>
+      <c r="H28" s="11"/>
+      <c r="M28" s="19"/>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B29" s="31"/>
-      <c r="C29" s="6"/>
-      <c r="D29" s="31"/>
-      <c r="E29" s="110"/>
-      <c r="F29" s="16"/>
-      <c r="G29" s="85"/>
-      <c r="H29" s="15"/>
-      <c r="J29" s="6"/>
-      <c r="K29" s="6"/>
-      <c r="L29" s="6"/>
-      <c r="M29" s="6"/>
-      <c r="N29" s="6"/>
-      <c r="O29" s="6"/>
-      <c r="P29" s="6"/>
-      <c r="Q29" s="6"/>
-      <c r="R29" s="6"/>
+      <c r="B29" s="23"/>
+      <c r="D29" s="23"/>
+      <c r="E29" s="94"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="70"/>
+      <c r="H29" s="11"/>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B30" s="32"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="31"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="16"/>
-      <c r="G30" s="85"/>
-      <c r="H30" s="15"/>
+      <c r="B30" s="23"/>
+      <c r="D30" s="23"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="70"/>
+      <c r="H30" s="11"/>
     </row>
     <row r="31" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B31" s="32"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="31"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="85"/>
-      <c r="H31" s="15"/>
+      <c r="B31" s="23"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="70"/>
+      <c r="H31" s="11"/>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B35" s="57"/>
+      <c r="B35" s="44"/>
       <c r="C35" s="1" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B36" s="77"/>
+      <c r="B36" s="64"/>
       <c r="C36" s="1" t="s">
         <v>160</v>
       </c>
@@ -7079,8 +6933,8 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:W32"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="B1:W32"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -7094,7 +6948,7 @@
     <col min="9" max="9" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8.85546875" customWidth="1"/>
     <col min="11" max="11" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="2" style="38" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="2" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13.85546875" customWidth="1"/>
     <col min="14" max="14" width="2" customWidth="1"/>
     <col min="15" max="15" width="12.42578125" customWidth="1"/>
@@ -7109,205 +6963,202 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:23" ht="15" x14ac:dyDescent="0.25">
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="I1" s="43"/>
+      <c r="I1" s="30"/>
     </row>
     <row r="2" spans="2:23" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="14" t="str">
+      <c r="B2" s="10" t="str">
         <f>'EB2'!B9</f>
         <v>TRA</v>
       </c>
-      <c r="C2" s="14" t="str">
+      <c r="C2" s="10" t="str">
         <f>'EB2'!C9</f>
         <v>Transport</v>
       </c>
-      <c r="D2" s="22" t="s">
+      <c r="D2" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="E2" s="14" t="str">
+      <c r="E2" s="10" t="str">
         <f>'EB2'!Z2</f>
         <v>PJ</v>
       </c>
-      <c r="F2" s="14" t="str">
+      <c r="F2" s="10" t="str">
         <f>'EB2'!Y2</f>
         <v>M€2005</v>
       </c>
-      <c r="G2" s="44" t="s">
+      <c r="G2" s="31" t="s">
         <v>144</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="H2" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="I2" s="13"/>
-      <c r="O2" s="133" t="s">
+      <c r="I2" s="9"/>
+      <c r="O2" s="115" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="133"/>
-      <c r="Q2" s="134"/>
-      <c r="R2" s="134"/>
-      <c r="S2" s="134"/>
-      <c r="T2" s="134"/>
-      <c r="U2" s="134"/>
-      <c r="V2" s="134"/>
-      <c r="W2" s="134"/>
+      <c r="P2" s="115"/>
+      <c r="Q2" s="116"/>
+      <c r="R2" s="116"/>
+      <c r="S2" s="116"/>
+      <c r="T2" s="116"/>
+      <c r="U2" s="116"/>
+      <c r="V2" s="116"/>
+      <c r="W2" s="116"/>
     </row>
     <row r="3" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="O3" s="135" t="s">
+      <c r="O3" s="117" t="s">
         <v>7</v>
       </c>
-      <c r="P3" s="136" t="s">
+      <c r="P3" s="118" t="s">
         <v>30</v>
       </c>
-      <c r="Q3" s="135" t="s">
-        <v>0</v>
-      </c>
-      <c r="R3" s="135" t="s">
+      <c r="Q3" s="117" t="s">
+        <v>0</v>
+      </c>
+      <c r="R3" s="117" t="s">
         <v>3</v>
       </c>
-      <c r="S3" s="135" t="s">
+      <c r="S3" s="117" t="s">
         <v>4</v>
       </c>
-      <c r="T3" s="135" t="s">
+      <c r="T3" s="117" t="s">
         <v>8</v>
       </c>
-      <c r="U3" s="135" t="s">
+      <c r="U3" s="117" t="s">
         <v>9</v>
       </c>
-      <c r="V3" s="135" t="s">
+      <c r="V3" s="117" t="s">
         <v>10</v>
       </c>
-      <c r="W3" s="135" t="s">
+      <c r="W3" s="117" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:23" s="6" customFormat="1" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="L4" s="38"/>
-      <c r="O4" s="137" t="s">
+    <row r="4" spans="2:23" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="O4" s="119" t="s">
         <v>37</v>
       </c>
-      <c r="P4" s="137" t="s">
+      <c r="P4" s="119" t="s">
         <v>31</v>
       </c>
-      <c r="Q4" s="137" t="s">
+      <c r="Q4" s="119" t="s">
         <v>26</v>
       </c>
-      <c r="R4" s="137" t="s">
+      <c r="R4" s="119" t="s">
         <v>27</v>
       </c>
-      <c r="S4" s="137" t="s">
+      <c r="S4" s="119" t="s">
         <v>4</v>
       </c>
-      <c r="T4" s="137" t="s">
+      <c r="T4" s="119" t="s">
         <v>40</v>
       </c>
-      <c r="U4" s="137" t="s">
+      <c r="U4" s="119" t="s">
         <v>41</v>
       </c>
-      <c r="V4" s="137" t="s">
+      <c r="V4" s="119" t="s">
         <v>28</v>
       </c>
-      <c r="W4" s="137" t="s">
+      <c r="W4" s="119" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="2:23" s="6" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="L5" s="38"/>
-      <c r="O5" s="142" t="s">
+    <row r="5" spans="2:23" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="O5" s="116" t="s">
         <v>83</v>
       </c>
-      <c r="P5" s="138"/>
-      <c r="Q5" s="142" t="str">
+      <c r="P5" s="120"/>
+      <c r="Q5" s="116" t="str">
         <f>LEFT($O$5,1)&amp;LEFT($B$2,1)&amp;'EB2'!$C$25</f>
         <v>DTCAR</v>
       </c>
-      <c r="R5" s="142" t="str">
+      <c r="R5" s="116" t="str">
         <f>LEFT($D$2,6)&amp;" "&amp;$C$2&amp; " Sector - "&amp;'EB2'!$X$25</f>
         <v>Demand Transport Sector - Cars</v>
       </c>
-      <c r="S5" s="147" t="s">
+      <c r="S5" s="116" t="s">
         <v>183</v>
       </c>
-      <c r="T5" s="142"/>
-      <c r="U5" s="142"/>
-      <c r="V5" s="142"/>
-      <c r="W5" s="142"/>
-    </row>
-    <row r="6" spans="2:23" s="6" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="L6" s="38"/>
-      <c r="O6" s="142"/>
-      <c r="P6" s="138"/>
-      <c r="Q6" s="142" t="str">
+      <c r="T5" s="116"/>
+      <c r="U5" s="116"/>
+      <c r="V5" s="116"/>
+      <c r="W5" s="116"/>
+    </row>
+    <row r="6" spans="2:23" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="O6" s="116"/>
+      <c r="P6" s="120"/>
+      <c r="Q6" s="116" t="str">
         <f>LEFT($O$5,1)&amp;LEFT($B$2,1)&amp;'EB2'!$C$26</f>
         <v>DTPUB</v>
       </c>
-      <c r="R6" s="142" t="str">
+      <c r="R6" s="116" t="str">
         <f>LEFT($D$2,6)&amp;" "&amp;$C$2&amp; " Sector - "&amp;'EB2'!$X$26</f>
         <v>Demand Transport Sector - Pub</v>
       </c>
-      <c r="S6" s="147" t="s">
+      <c r="S6" s="116" t="s">
         <v>183</v>
       </c>
-      <c r="T6" s="142"/>
-      <c r="U6" s="142"/>
-      <c r="V6" s="142"/>
-      <c r="W6" s="142"/>
+      <c r="T6" s="116"/>
+      <c r="U6" s="116"/>
+      <c r="V6" s="116"/>
+      <c r="W6" s="116"/>
     </row>
     <row r="7" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="O7" s="140" t="s">
+      <c r="O7" s="120" t="s">
         <v>105</v>
       </c>
-      <c r="P7" s="140"/>
-      <c r="Q7" s="140" t="str">
+      <c r="P7" s="120"/>
+      <c r="Q7" s="120" t="str">
         <f>$B$2&amp;'EB2'!$C$29</f>
         <v>TRACO2</v>
       </c>
-      <c r="R7" s="140" t="str">
+      <c r="R7" s="120" t="str">
         <f>$C$2&amp;" "&amp;'EB2'!$C$30</f>
         <v>Transport Carbon dioxide</v>
       </c>
-      <c r="S7" s="140" t="str">
+      <c r="S7" s="120" t="str">
         <f>'EB2'!$AA$2</f>
         <v>kt</v>
       </c>
-      <c r="T7" s="140"/>
-      <c r="U7" s="140"/>
-      <c r="V7" s="140"/>
-      <c r="W7" s="140"/>
+      <c r="T7" s="120"/>
+      <c r="U7" s="120"/>
+      <c r="V7" s="120"/>
+      <c r="W7" s="120"/>
     </row>
     <row r="9" spans="2:23" x14ac:dyDescent="0.2">
       <c r="D9" s="5" t="s">
@@ -7316,189 +7167,189 @@
       <c r="E9" s="5"/>
       <c r="G9" s="5"/>
       <c r="I9" s="4"/>
-      <c r="J9" s="18"/>
-      <c r="O9" s="133" t="s">
+      <c r="J9" s="14"/>
+      <c r="O9" s="115" t="s">
         <v>15</v>
       </c>
-      <c r="P9" s="133"/>
-      <c r="Q9" s="140"/>
-      <c r="R9" s="140"/>
-      <c r="S9" s="140"/>
-      <c r="T9" s="140"/>
-      <c r="U9" s="140"/>
-      <c r="V9" s="140"/>
-      <c r="W9" s="140"/>
+      <c r="P9" s="115"/>
+      <c r="Q9" s="120"/>
+      <c r="R9" s="120"/>
+      <c r="S9" s="120"/>
+      <c r="T9" s="120"/>
+      <c r="U9" s="120"/>
+      <c r="V9" s="120"/>
+      <c r="W9" s="120"/>
     </row>
     <row r="10" spans="2:23" x14ac:dyDescent="0.2">
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="21" t="s">
+      <c r="D10" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="E10" s="86" t="s">
+      <c r="E10" s="71" t="s">
         <v>127</v>
       </c>
-      <c r="F10" s="86" t="s">
+      <c r="F10" s="71" t="s">
         <v>85</v>
       </c>
-      <c r="G10" s="86" t="s">
+      <c r="G10" s="71" t="s">
         <v>98</v>
       </c>
-      <c r="H10" s="86" t="s">
+      <c r="H10" s="71" t="s">
         <v>146</v>
       </c>
-      <c r="I10" s="86" t="s">
+      <c r="I10" s="71" t="s">
         <v>84</v>
       </c>
-      <c r="J10" s="86" t="s">
+      <c r="J10" s="71" t="s">
         <v>79</v>
       </c>
-      <c r="K10" s="86" t="s">
+      <c r="K10" s="71" t="s">
         <v>178</v>
       </c>
-      <c r="L10" s="35"/>
-      <c r="M10" s="42" t="s">
+      <c r="L10" s="25"/>
+      <c r="M10" s="29" t="s">
         <v>118</v>
       </c>
-      <c r="O10" s="135" t="s">
+      <c r="O10" s="117" t="s">
         <v>11</v>
       </c>
-      <c r="P10" s="136" t="s">
+      <c r="P10" s="118" t="s">
         <v>30</v>
       </c>
-      <c r="Q10" s="135" t="s">
+      <c r="Q10" s="117" t="s">
         <v>1</v>
       </c>
-      <c r="R10" s="135" t="s">
+      <c r="R10" s="117" t="s">
         <v>2</v>
       </c>
-      <c r="S10" s="135" t="s">
+      <c r="S10" s="117" t="s">
         <v>16</v>
       </c>
-      <c r="T10" s="135" t="s">
+      <c r="T10" s="117" t="s">
         <v>17</v>
       </c>
-      <c r="U10" s="135" t="s">
+      <c r="U10" s="117" t="s">
         <v>18</v>
       </c>
-      <c r="V10" s="135" t="s">
+      <c r="V10" s="117" t="s">
         <v>19</v>
       </c>
-      <c r="W10" s="135" t="s">
+      <c r="W10" s="117" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="11" spans="2:23" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="20" t="s">
+      <c r="B11" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="20" t="s">
+      <c r="C11" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="20" t="s">
+      <c r="D11" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="E11" s="20" t="s">
+      <c r="E11" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F11" s="20" t="s">
+      <c r="F11" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="G11" s="100" t="s">
+      <c r="G11" s="85" t="s">
         <v>99</v>
       </c>
-      <c r="H11" s="100" t="s">
+      <c r="H11" s="85" t="s">
         <v>148</v>
       </c>
-      <c r="I11" s="20" t="s">
+      <c r="I11" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="J11" s="20" t="s">
+      <c r="J11" s="16" t="s">
         <v>177</v>
       </c>
-      <c r="K11" s="20" t="s">
+      <c r="K11" s="16" t="s">
         <v>179</v>
       </c>
-      <c r="L11" s="45"/>
-      <c r="M11" s="131" t="s">
+      <c r="L11" s="32"/>
+      <c r="M11" s="113" t="s">
         <v>35</v>
       </c>
-      <c r="O11" s="137" t="s">
+      <c r="O11" s="119" t="s">
         <v>38</v>
       </c>
-      <c r="P11" s="137" t="s">
+      <c r="P11" s="119" t="s">
         <v>31</v>
       </c>
-      <c r="Q11" s="137" t="s">
+      <c r="Q11" s="119" t="s">
         <v>21</v>
       </c>
-      <c r="R11" s="137" t="s">
+      <c r="R11" s="119" t="s">
         <v>22</v>
       </c>
-      <c r="S11" s="137" t="s">
+      <c r="S11" s="119" t="s">
         <v>23</v>
       </c>
-      <c r="T11" s="137" t="s">
+      <c r="T11" s="119" t="s">
         <v>24</v>
       </c>
-      <c r="U11" s="137" t="s">
+      <c r="U11" s="119" t="s">
         <v>43</v>
       </c>
-      <c r="V11" s="137" t="s">
+      <c r="V11" s="119" t="s">
         <v>42</v>
       </c>
-      <c r="W11" s="137" t="s">
+      <c r="W11" s="119" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="12" spans="2:23" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="17" t="str">
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="13" t="str">
         <f>G2</f>
         <v>000_Units</v>
       </c>
-      <c r="F12" s="17" t="s">
+      <c r="F12" s="13" t="s">
         <v>180</v>
       </c>
-      <c r="G12" s="90" t="s">
+      <c r="G12" s="75" t="s">
         <v>151</v>
       </c>
-      <c r="H12" s="88" t="s">
+      <c r="H12" s="73" t="s">
         <v>147</v>
       </c>
-      <c r="I12" s="17" t="str">
+      <c r="I12" s="13" t="str">
         <f>$F$2&amp;"/"&amp;G2&amp;"a"</f>
         <v>M€2005/000_Unitsa</v>
       </c>
-      <c r="J12" s="17" t="s">
+      <c r="J12" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="K12" s="17" t="s">
+      <c r="K12" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="L12" s="45"/>
-      <c r="M12" s="132" t="s">
+      <c r="L12" s="32"/>
+      <c r="M12" s="114" t="s">
         <v>182</v>
       </c>
-      <c r="O12" s="137" t="s">
+      <c r="O12" s="119" t="s">
         <v>81</v>
       </c>
-      <c r="P12" s="137"/>
-      <c r="Q12" s="137"/>
-      <c r="R12" s="137"/>
-      <c r="S12" s="137"/>
-      <c r="T12" s="137"/>
-      <c r="U12" s="137"/>
-      <c r="V12" s="137"/>
-      <c r="W12" s="137"/>
+      <c r="P12" s="119"/>
+      <c r="Q12" s="119"/>
+      <c r="R12" s="119"/>
+      <c r="S12" s="119"/>
+      <c r="T12" s="119"/>
+      <c r="U12" s="119"/>
+      <c r="V12" s="119"/>
+      <c r="W12" s="119"/>
     </row>
     <row r="13" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B13" t="str">
@@ -7513,56 +7364,56 @@
         <f t="shared" ref="D13:D18" si="2">$Q$5</f>
         <v>DTCAR</v>
       </c>
-      <c r="E13" s="76">
+      <c r="E13" s="63">
         <f>('EB2'!E$9*'EB2'!$E$25*F13/(K13*G13))*1.01</f>
         <v>349.51569428571423</v>
       </c>
-      <c r="F13" s="57">
+      <c r="F13" s="44">
         <v>0.38</v>
       </c>
-      <c r="G13" s="57">
+      <c r="G13" s="44">
         <v>14</v>
       </c>
-      <c r="H13" s="80">
+      <c r="H13" s="67">
         <v>1.25</v>
       </c>
-      <c r="I13" s="80">
+      <c r="I13" s="67">
         <v>0.16</v>
       </c>
-      <c r="J13" s="57">
+      <c r="J13" s="44">
         <v>10</v>
       </c>
-      <c r="K13" s="83">
+      <c r="K13" s="69">
         <v>1E-3</v>
       </c>
-      <c r="M13" s="42">
+      <c r="M13" s="29">
         <f>E13*G13*K13*H13</f>
         <v>6.1165246499999988</v>
       </c>
-      <c r="O13" s="142" t="s">
+      <c r="O13" s="116" t="s">
         <v>97</v>
       </c>
-      <c r="P13" s="138"/>
-      <c r="Q13" s="138" t="str">
+      <c r="P13" s="120"/>
+      <c r="Q13" s="120" t="str">
         <f>LEFT($B$2)&amp;'EB2'!$C$25&amp;$H$2&amp;'EB2'!$E$2</f>
         <v>TCAREGAS</v>
       </c>
-      <c r="R13" s="139" t="str">
+      <c r="R13" s="121" t="str">
         <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB2'!$X$25&amp;" - "&amp;'EB2'!$E$3</f>
         <v>Demand Technologies Transport Sector - Existing Cars - Natural Gas</v>
       </c>
-      <c r="S13" s="142" t="s">
+      <c r="S13" s="116" t="s">
         <v>183</v>
       </c>
-      <c r="T13" s="142" t="str">
+      <c r="T13" s="116" t="str">
         <f t="shared" ref="T13:T24" si="3">$G$2</f>
         <v>000_Units</v>
       </c>
-      <c r="U13" s="138"/>
-      <c r="V13" s="142" t="s">
+      <c r="U13" s="120"/>
+      <c r="V13" s="116" t="s">
         <v>145</v>
       </c>
-      <c r="W13" s="138"/>
+      <c r="W13" s="120"/>
     </row>
     <row r="14" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B14" t="str">
@@ -7577,54 +7428,54 @@
         <f t="shared" si="2"/>
         <v>DTCAR</v>
       </c>
-      <c r="E14" s="76">
+      <c r="E14" s="63">
         <f>('EB2'!G$9*'EB2'!$G$25*F14/(K14*G14))*1.01</f>
         <v>87102.97230272727</v>
       </c>
-      <c r="F14" s="80">
+      <c r="F14" s="67">
         <v>0.41</v>
       </c>
-      <c r="G14" s="75">
+      <c r="G14" s="62">
         <v>16.5</v>
       </c>
-      <c r="H14" s="80">
+      <c r="H14" s="67">
         <v>1.25</v>
       </c>
-      <c r="I14" s="80">
+      <c r="I14" s="67">
         <v>0.16</v>
       </c>
-      <c r="J14" s="57">
+      <c r="J14" s="44">
         <v>10</v>
       </c>
-      <c r="K14" s="83">
+      <c r="K14" s="69">
         <v>1E-3</v>
       </c>
-      <c r="M14" s="42">
+      <c r="M14" s="29">
         <f t="shared" ref="M14:M22" si="4">E14*G14*K14*H14</f>
         <v>1796.4988037437502</v>
       </c>
-      <c r="O14" s="138"/>
-      <c r="P14" s="138"/>
-      <c r="Q14" s="138" t="str">
+      <c r="O14" s="120"/>
+      <c r="P14" s="120"/>
+      <c r="Q14" s="120" t="str">
         <f>LEFT($B$2)&amp;'EB2'!$C$25&amp;$H$2&amp;'EB2'!$G$2</f>
         <v>TCAREDSL</v>
       </c>
-      <c r="R14" s="139" t="str">
+      <c r="R14" s="121" t="str">
         <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB2'!$X$25&amp;" - "&amp;'EB2'!$G$3</f>
         <v>Demand Technologies Transport Sector - Existing Cars - Diesel oil</v>
       </c>
-      <c r="S14" s="147" t="s">
+      <c r="S14" s="116" t="s">
         <v>183</v>
       </c>
-      <c r="T14" s="142" t="str">
+      <c r="T14" s="116" t="str">
         <f t="shared" si="3"/>
         <v>000_Units</v>
       </c>
-      <c r="U14" s="138"/>
-      <c r="V14" s="142" t="s">
+      <c r="U14" s="120"/>
+      <c r="V14" s="116" t="s">
         <v>145</v>
       </c>
-      <c r="W14" s="138"/>
+      <c r="W14" s="120"/>
     </row>
     <row r="15" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B15" t="str">
@@ -7639,54 +7490,54 @@
         <f t="shared" si="2"/>
         <v>DTCAR</v>
       </c>
-      <c r="E15" s="76">
+      <c r="E15" s="63">
         <f>('EB2'!I$9*'EB2'!$I$25*F15/(K15*G15))*1.01</f>
         <v>2583.2755571428575</v>
       </c>
-      <c r="F15" s="80">
+      <c r="F15" s="67">
         <v>0.38</v>
       </c>
-      <c r="G15" s="75">
+      <c r="G15" s="62">
         <v>14</v>
       </c>
-      <c r="H15" s="80">
+      <c r="H15" s="67">
         <v>1.25</v>
       </c>
-      <c r="I15" s="84">
+      <c r="I15" s="68">
         <v>0.16</v>
       </c>
-      <c r="J15" s="57">
+      <c r="J15" s="44">
         <v>10</v>
       </c>
-      <c r="K15" s="83">
+      <c r="K15" s="69">
         <v>1E-3</v>
       </c>
-      <c r="M15" s="42">
+      <c r="M15" s="29">
         <f t="shared" si="4"/>
         <v>45.207322250000004</v>
       </c>
-      <c r="O15" s="138"/>
-      <c r="P15" s="138"/>
-      <c r="Q15" s="138" t="str">
+      <c r="O15" s="120"/>
+      <c r="P15" s="120"/>
+      <c r="Q15" s="120" t="str">
         <f>LEFT($B$2)&amp;'EB2'!$C$25&amp;$H$2&amp;'EB2'!$I$2</f>
         <v>TCARELPG</v>
       </c>
-      <c r="R15" s="139" t="str">
+      <c r="R15" s="121" t="str">
         <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB2'!$X$25&amp;" - "&amp;'EB2'!$I$3</f>
         <v>Demand Technologies Transport Sector - Existing Cars - LPG</v>
       </c>
-      <c r="S15" s="147" t="s">
+      <c r="S15" s="116" t="s">
         <v>183</v>
       </c>
-      <c r="T15" s="142" t="str">
+      <c r="T15" s="116" t="str">
         <f t="shared" si="3"/>
         <v>000_Units</v>
       </c>
-      <c r="U15" s="138"/>
-      <c r="V15" s="142" t="s">
+      <c r="U15" s="120"/>
+      <c r="V15" s="116" t="s">
         <v>145</v>
       </c>
-      <c r="W15" s="138"/>
+      <c r="W15" s="120"/>
     </row>
     <row r="16" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B16" t="str">
@@ -7701,56 +7552,56 @@
         <f t="shared" si="2"/>
         <v>DTCAR</v>
       </c>
-      <c r="E16" s="76">
+      <c r="E16" s="63">
         <f>('EB2'!J$9*'EB2'!$J$25*F16/(K16*G16))*1.01</f>
         <v>84109.849043478273</v>
       </c>
-      <c r="F16" s="81">
+      <c r="F16" s="68">
         <v>0.4</v>
       </c>
-      <c r="G16" s="82">
+      <c r="G16" s="62">
         <v>11.5</v>
       </c>
-      <c r="H16" s="80">
+      <c r="H16" s="67">
         <v>1.25</v>
       </c>
-      <c r="I16" s="80">
+      <c r="I16" s="67">
         <v>0.15</v>
       </c>
-      <c r="J16" s="57">
+      <c r="J16" s="44">
         <v>10</v>
       </c>
-      <c r="K16" s="83">
+      <c r="K16" s="69">
         <v>1E-3</v>
       </c>
-      <c r="M16" s="42">
+      <c r="M16" s="29">
         <f t="shared" si="4"/>
         <v>1209.07908</v>
       </c>
-      <c r="O16" s="138"/>
-      <c r="P16" s="138"/>
-      <c r="Q16" s="138" t="str">
+      <c r="O16" s="120"/>
+      <c r="P16" s="120"/>
+      <c r="Q16" s="120" t="str">
         <f>LEFT($B$2)&amp;'EB2'!$C$25&amp;$H$2&amp;'EB2'!$J$2</f>
         <v>TCAREGSL</v>
       </c>
-      <c r="R16" s="143" t="str">
+      <c r="R16" s="120" t="str">
         <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB2'!$X$25&amp;" - "&amp;'EB2'!$J$3</f>
         <v>Demand Technologies Transport Sector - Existing Cars - Motor spirit</v>
       </c>
-      <c r="S16" s="147" t="s">
+      <c r="S16" s="116" t="s">
         <v>183</v>
       </c>
-      <c r="T16" s="142" t="str">
+      <c r="T16" s="116" t="str">
         <f t="shared" si="3"/>
         <v>000_Units</v>
       </c>
-      <c r="U16" s="138"/>
-      <c r="V16" s="142" t="s">
+      <c r="U16" s="120"/>
+      <c r="V16" s="116" t="s">
         <v>145</v>
       </c>
-      <c r="W16" s="138"/>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="W16" s="120"/>
+    </row>
+    <row r="17" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B17" t="str">
         <f>Q17</f>
         <v>TCAREBIO</v>
@@ -7763,119 +7614,119 @@
         <f t="shared" si="2"/>
         <v>DTCAR</v>
       </c>
-      <c r="E17" s="76">
+      <c r="E17" s="63">
         <f>('EB2'!O$9*'EB2'!$O$25*F17/(K17*G17))*1.01</f>
         <v>707.00000000000011</v>
       </c>
-      <c r="F17" s="81">
+      <c r="F17" s="68">
         <v>0.4</v>
       </c>
-      <c r="G17" s="82">
+      <c r="G17" s="62">
         <v>11.5</v>
       </c>
-      <c r="H17" s="80">
+      <c r="H17" s="67">
         <v>1.25</v>
       </c>
-      <c r="I17" s="80">
+      <c r="I17" s="67">
         <v>0.15</v>
       </c>
-      <c r="J17" s="57">
+      <c r="J17" s="44">
         <v>10</v>
       </c>
-      <c r="K17" s="83">
+      <c r="K17" s="69">
         <v>1E-3</v>
       </c>
-      <c r="M17" s="42">
+      <c r="M17" s="29">
         <f>E17*G17*K17*H17</f>
         <v>10.163125000000001</v>
       </c>
-      <c r="O17" s="138"/>
-      <c r="P17" s="138"/>
-      <c r="Q17" s="138" t="str">
+      <c r="O17" s="120"/>
+      <c r="P17" s="120"/>
+      <c r="Q17" s="120" t="str">
         <f>LEFT($B$2)&amp;'EB2'!$C$25&amp;$H$2&amp;'EB2'!$O$2</f>
         <v>TCAREBIO</v>
       </c>
-      <c r="R17" s="143" t="str">
+      <c r="R17" s="120" t="str">
         <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB2'!$X$25&amp;" - "&amp;'EB2'!$O$3</f>
         <v>Demand Technologies Transport Sector - Existing Cars - Biofuels</v>
       </c>
-      <c r="S17" s="147" t="s">
+      <c r="S17" s="116" t="s">
         <v>183</v>
       </c>
-      <c r="T17" s="142" t="str">
+      <c r="T17" s="116" t="str">
         <f t="shared" si="3"/>
         <v>000_Units</v>
       </c>
-      <c r="U17" s="138"/>
-      <c r="V17" s="142" t="s">
+      <c r="U17" s="120"/>
+      <c r="V17" s="116" t="s">
         <v>145</v>
       </c>
-      <c r="W17" s="138"/>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="B18" s="27" t="str">
+      <c r="W17" s="120"/>
+    </row>
+    <row r="18" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B18" s="6" t="str">
         <f t="shared" si="0"/>
         <v>TCAREELC</v>
       </c>
-      <c r="C18" s="27" t="str">
+      <c r="C18" s="6" t="str">
         <f t="shared" si="1"/>
         <v>TRAELC</v>
       </c>
-      <c r="D18" s="27" t="str">
+      <c r="D18" s="6" t="str">
         <f t="shared" si="2"/>
         <v>DTCAR</v>
       </c>
-      <c r="E18" s="92">
+      <c r="E18" s="77">
         <f>('EB2'!U$9*'EB2'!$U$25*F18/(K18*G18))*1.01</f>
         <v>0</v>
       </c>
-      <c r="F18" s="111">
+      <c r="F18" s="95">
         <v>0.4</v>
       </c>
-      <c r="G18" s="112">
+      <c r="G18" s="96">
         <v>11.5</v>
       </c>
-      <c r="H18" s="113">
+      <c r="H18" s="97">
         <v>1.25</v>
       </c>
-      <c r="I18" s="113">
+      <c r="I18" s="97">
         <v>0.15</v>
       </c>
-      <c r="J18" s="114">
+      <c r="J18" s="98">
         <v>10</v>
       </c>
-      <c r="K18" s="115">
+      <c r="K18" s="99">
         <v>1E-3</v>
       </c>
-      <c r="L18" s="116"/>
-      <c r="M18" s="117">
+      <c r="L18" s="6"/>
+      <c r="M18" s="100">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O18" s="144"/>
-      <c r="P18" s="144"/>
-      <c r="Q18" s="144" t="str">
+      <c r="O18" s="123"/>
+      <c r="P18" s="123"/>
+      <c r="Q18" s="123" t="str">
         <f>LEFT($B$2)&amp;'EB2'!$C$25&amp;$H$2&amp;'EB2'!$U$2</f>
         <v>TCAREELC</v>
       </c>
-      <c r="R18" s="145" t="str">
+      <c r="R18" s="123" t="str">
         <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB2'!$X$25&amp;" - "&amp;'EB2'!$U$3</f>
         <v>Demand Technologies Transport Sector - Existing Cars - Electricity</v>
       </c>
-      <c r="S18" s="146" t="s">
+      <c r="S18" s="124" t="s">
         <v>183</v>
       </c>
-      <c r="T18" s="146" t="str">
+      <c r="T18" s="124" t="str">
         <f t="shared" si="3"/>
         <v>000_Units</v>
       </c>
-      <c r="U18" s="144"/>
-      <c r="V18" s="146" t="s">
+      <c r="U18" s="123"/>
+      <c r="V18" s="124" t="s">
         <v>145</v>
       </c>
-      <c r="W18" s="144"/>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="W18" s="123"/>
+    </row>
+    <row r="19" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B19" t="str">
         <f t="shared" si="0"/>
         <v>TPUBEGAS</v>
@@ -7888,56 +7739,56 @@
         <f t="shared" ref="D19:D24" si="5">$Q$6</f>
         <v>DTPUB</v>
       </c>
-      <c r="E19" s="76">
+      <c r="E19" s="63">
         <f>('EB2'!E$9*'EB2'!$E$26*F19/(K19*G19))*1.01</f>
         <v>0</v>
       </c>
-      <c r="F19" s="80">
+      <c r="F19" s="67">
         <v>0.1</v>
       </c>
-      <c r="G19" s="57">
+      <c r="G19" s="44">
         <v>50</v>
       </c>
-      <c r="H19" s="80">
+      <c r="H19" s="67">
         <v>15</v>
       </c>
-      <c r="I19" s="80">
+      <c r="I19" s="67">
         <v>0.24</v>
       </c>
-      <c r="J19" s="57">
+      <c r="J19" s="44">
         <v>30</v>
       </c>
-      <c r="K19" s="83">
+      <c r="K19" s="69">
         <v>1E-3</v>
       </c>
-      <c r="M19" s="42">
+      <c r="M19" s="29">
         <f>E19*G19*K19*H19</f>
         <v>0</v>
       </c>
-      <c r="O19" s="138"/>
-      <c r="P19" s="138"/>
-      <c r="Q19" s="138" t="str">
+      <c r="O19" s="120"/>
+      <c r="P19" s="120"/>
+      <c r="Q19" s="120" t="str">
         <f>LEFT($B$2)&amp;'EB2'!$C$26&amp;$H$2&amp;'EB2'!$E$2</f>
         <v>TPUBEGAS</v>
       </c>
-      <c r="R19" s="139" t="str">
+      <c r="R19" s="121" t="str">
         <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB2'!$X$26&amp;" - "&amp;'EB2'!$E$3</f>
         <v>Demand Technologies Transport Sector - Existing Pub - Natural Gas</v>
       </c>
-      <c r="S19" s="147" t="s">
+      <c r="S19" s="116" t="s">
         <v>183</v>
       </c>
-      <c r="T19" s="142" t="str">
+      <c r="T19" s="116" t="str">
         <f t="shared" si="3"/>
         <v>000_Units</v>
       </c>
-      <c r="U19" s="138"/>
-      <c r="V19" s="142" t="s">
+      <c r="U19" s="120"/>
+      <c r="V19" s="116" t="s">
         <v>145</v>
       </c>
-      <c r="W19" s="138"/>
-    </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="W19" s="120"/>
+    </row>
+    <row r="20" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B20" t="str">
         <f t="shared" si="0"/>
         <v>TPUBEDSL</v>
@@ -7950,56 +7801,56 @@
         <f t="shared" si="5"/>
         <v>DTPUB</v>
       </c>
-      <c r="E20" s="76">
+      <c r="E20" s="63">
         <f>('EB2'!G$9*'EB2'!$G$26*F20/(K20*G20))*1.01</f>
         <v>1168.4545064999998</v>
       </c>
-      <c r="F20" s="80">
+      <c r="F20" s="67">
         <v>0.15</v>
       </c>
-      <c r="G20" s="75">
+      <c r="G20" s="62">
         <v>50</v>
       </c>
-      <c r="H20" s="80">
+      <c r="H20" s="67">
         <v>15</v>
       </c>
-      <c r="I20" s="80">
+      <c r="I20" s="67">
         <v>0.24</v>
       </c>
-      <c r="J20" s="57">
+      <c r="J20" s="44">
         <v>30</v>
       </c>
-      <c r="K20" s="83">
+      <c r="K20" s="69">
         <v>1E-3</v>
       </c>
-      <c r="M20" s="42">
+      <c r="M20" s="29">
         <f>E20*G20*K20*H20</f>
         <v>876.34087987499981</v>
       </c>
-      <c r="O20" s="138"/>
-      <c r="P20" s="138"/>
-      <c r="Q20" s="138" t="str">
+      <c r="O20" s="120"/>
+      <c r="P20" s="120"/>
+      <c r="Q20" s="120" t="str">
         <f>LEFT($B$2)&amp;'EB2'!$C$26&amp;$H$2&amp;'EB2'!$G$2</f>
         <v>TPUBEDSL</v>
       </c>
-      <c r="R20" s="139" t="str">
+      <c r="R20" s="121" t="str">
         <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB2'!$X$26&amp;" - "&amp;'EB2'!$G$3</f>
         <v>Demand Technologies Transport Sector - Existing Pub - Diesel oil</v>
       </c>
-      <c r="S20" s="147" t="s">
+      <c r="S20" s="116" t="s">
         <v>183</v>
       </c>
-      <c r="T20" s="142" t="str">
+      <c r="T20" s="116" t="str">
         <f t="shared" si="3"/>
         <v>000_Units</v>
       </c>
-      <c r="U20" s="138"/>
-      <c r="V20" s="142" t="s">
+      <c r="U20" s="120"/>
+      <c r="V20" s="116" t="s">
         <v>145</v>
       </c>
-      <c r="W20" s="138"/>
-    </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="W20" s="120"/>
+    </row>
+    <row r="21" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B21" t="str">
         <f t="shared" si="0"/>
         <v>TPUBELPG</v>
@@ -8012,56 +7863,56 @@
         <f t="shared" si="5"/>
         <v>DTPUB</v>
       </c>
-      <c r="E21" s="76">
+      <c r="E21" s="63">
         <f>('EB2'!I$9*'EB2'!$I$26*F21/(K21*G21))*1.01</f>
         <v>0</v>
       </c>
-      <c r="F21" s="80">
+      <c r="F21" s="67">
         <v>0.1</v>
       </c>
-      <c r="G21" s="75">
+      <c r="G21" s="62">
         <v>50</v>
       </c>
-      <c r="H21" s="80">
+      <c r="H21" s="67">
         <v>15</v>
       </c>
-      <c r="I21" s="84">
+      <c r="I21" s="68">
         <v>0.24</v>
       </c>
-      <c r="J21" s="57">
+      <c r="J21" s="44">
         <v>30</v>
       </c>
-      <c r="K21" s="83">
+      <c r="K21" s="69">
         <v>1E-3</v>
       </c>
-      <c r="M21" s="42">
+      <c r="M21" s="29">
         <f>E21*G21*K21*H21</f>
         <v>0</v>
       </c>
-      <c r="O21" s="138"/>
-      <c r="P21" s="138"/>
-      <c r="Q21" s="138" t="str">
+      <c r="O21" s="120"/>
+      <c r="P21" s="120"/>
+      <c r="Q21" s="120" t="str">
         <f>LEFT($B$2)&amp;'EB2'!$C$26&amp;$H$2&amp;'EB2'!$I$2</f>
         <v>TPUBELPG</v>
       </c>
-      <c r="R21" s="139" t="str">
+      <c r="R21" s="121" t="str">
         <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB2'!$X$26&amp;" - "&amp;'EB2'!$I$3</f>
         <v>Demand Technologies Transport Sector - Existing Pub - LPG</v>
       </c>
-      <c r="S21" s="147" t="s">
+      <c r="S21" s="116" t="s">
         <v>183</v>
       </c>
-      <c r="T21" s="142" t="str">
+      <c r="T21" s="116" t="str">
         <f t="shared" si="3"/>
         <v>000_Units</v>
       </c>
-      <c r="U21" s="138"/>
-      <c r="V21" s="142" t="s">
+      <c r="U21" s="120"/>
+      <c r="V21" s="116" t="s">
         <v>145</v>
       </c>
-      <c r="W21" s="138"/>
-    </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="W21" s="120"/>
+    </row>
+    <row r="22" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B22" t="str">
         <f t="shared" si="0"/>
         <v>TPUBEGSL</v>
@@ -8074,56 +7925,56 @@
         <f t="shared" si="5"/>
         <v>DTPUB</v>
       </c>
-      <c r="E22" s="76">
+      <c r="E22" s="63">
         <f>('EB2'!J$9*'EB2'!$J$26*F22/(K22*G22))*1.01</f>
         <v>0</v>
       </c>
-      <c r="F22" s="81">
+      <c r="F22" s="68">
         <v>0.15</v>
       </c>
-      <c r="G22" s="82">
+      <c r="G22" s="62">
         <v>20</v>
       </c>
-      <c r="H22" s="80">
+      <c r="H22" s="67">
         <v>15</v>
       </c>
-      <c r="I22" s="80">
+      <c r="I22" s="67">
         <v>0.22499999999999998</v>
       </c>
-      <c r="J22" s="57">
+      <c r="J22" s="44">
         <v>30</v>
       </c>
-      <c r="K22" s="83">
+      <c r="K22" s="69">
         <v>1E-3</v>
       </c>
-      <c r="M22" s="42">
+      <c r="M22" s="29">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O22" s="138"/>
-      <c r="P22" s="138"/>
-      <c r="Q22" s="138" t="str">
+      <c r="O22" s="120"/>
+      <c r="P22" s="120"/>
+      <c r="Q22" s="120" t="str">
         <f>LEFT($B$2)&amp;'EB2'!$C$26&amp;$H$2&amp;'EB2'!$J$2</f>
         <v>TPUBEGSL</v>
       </c>
-      <c r="R22" s="143" t="str">
+      <c r="R22" s="120" t="str">
         <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB2'!$X$26&amp;" - "&amp;'EB2'!$J$3</f>
         <v>Demand Technologies Transport Sector - Existing Pub - Motor spirit</v>
       </c>
-      <c r="S22" s="147" t="s">
+      <c r="S22" s="116" t="s">
         <v>183</v>
       </c>
-      <c r="T22" s="142" t="str">
+      <c r="T22" s="116" t="str">
         <f t="shared" si="3"/>
         <v>000_Units</v>
       </c>
-      <c r="U22" s="138"/>
-      <c r="V22" s="142" t="s">
+      <c r="U22" s="120"/>
+      <c r="V22" s="116" t="s">
         <v>145</v>
       </c>
-      <c r="W22" s="138"/>
-    </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="W22" s="120"/>
+    </row>
+    <row r="23" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B23" t="str">
         <f>Q23</f>
         <v>TPUBEBIO</v>
@@ -8136,184 +7987,153 @@
         <f t="shared" si="5"/>
         <v>DTPUB</v>
       </c>
-      <c r="E23" s="76">
+      <c r="E23" s="63">
         <f>('EB2'!O$9*'EB2'!$O$26*F23/(K23*G23))*1.01</f>
         <v>152.44687500000001</v>
       </c>
-      <c r="F23" s="81">
+      <c r="F23" s="68">
         <v>0.15</v>
       </c>
-      <c r="G23" s="82">
+      <c r="G23" s="62">
         <v>20</v>
       </c>
-      <c r="H23" s="80">
+      <c r="H23" s="67">
         <v>15</v>
       </c>
-      <c r="I23" s="80">
+      <c r="I23" s="67">
         <v>0.22499999999999998</v>
       </c>
-      <c r="J23" s="57">
+      <c r="J23" s="44">
         <v>30</v>
       </c>
-      <c r="K23" s="83">
+      <c r="K23" s="69">
         <v>1E-3</v>
       </c>
-      <c r="M23" s="42">
+      <c r="M23" s="29">
         <f>E23*G23*K23*H23</f>
         <v>45.7340625</v>
       </c>
-      <c r="O23" s="138"/>
-      <c r="P23" s="138"/>
-      <c r="Q23" s="138" t="str">
+      <c r="O23" s="120"/>
+      <c r="P23" s="120"/>
+      <c r="Q23" s="120" t="str">
         <f>LEFT($B$2)&amp;'EB2'!$C$26&amp;$H$2&amp;'EB2'!$O$2</f>
         <v>TPUBEBIO</v>
       </c>
-      <c r="R23" s="143" t="str">
+      <c r="R23" s="120" t="str">
         <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB2'!$X$26&amp;" - "&amp;'EB2'!$O$3</f>
         <v>Demand Technologies Transport Sector - Existing Pub - Biofuels</v>
       </c>
-      <c r="S23" s="147" t="s">
+      <c r="S23" s="116" t="s">
         <v>183</v>
       </c>
-      <c r="T23" s="142" t="str">
+      <c r="T23" s="116" t="str">
         <f t="shared" si="3"/>
         <v>000_Units</v>
       </c>
-      <c r="U23" s="138"/>
-      <c r="V23" s="142" t="s">
+      <c r="U23" s="120"/>
+      <c r="V23" s="116" t="s">
         <v>145</v>
       </c>
-      <c r="W23" s="138"/>
-    </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="B24" s="27" t="str">
+      <c r="W23" s="120"/>
+    </row>
+    <row r="24" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B24" s="6" t="str">
         <f t="shared" si="0"/>
         <v>TPUBEELC</v>
       </c>
-      <c r="C24" s="27" t="str">
+      <c r="C24" s="6" t="str">
         <f t="shared" si="1"/>
         <v>TRAELC</v>
       </c>
-      <c r="D24" s="27" t="str">
+      <c r="D24" s="6" t="str">
         <f t="shared" si="5"/>
         <v>DTPUB</v>
       </c>
-      <c r="E24" s="92">
+      <c r="E24" s="77">
         <f>('EB2'!U$9*'EB2'!$U$26*F24/(K24*G24))*1.01</f>
         <v>40.294757999999995</v>
       </c>
-      <c r="F24" s="111">
+      <c r="F24" s="95">
         <v>0.03</v>
       </c>
-      <c r="G24" s="112">
+      <c r="G24" s="96">
         <v>100</v>
       </c>
-      <c r="H24" s="113">
+      <c r="H24" s="97">
         <v>200</v>
       </c>
-      <c r="I24" s="113">
+      <c r="I24" s="97">
         <v>0.22499999999999998</v>
       </c>
-      <c r="J24" s="114">
+      <c r="J24" s="98">
         <v>30</v>
       </c>
-      <c r="K24" s="115">
+      <c r="K24" s="99">
         <v>1E-3</v>
       </c>
-      <c r="M24" s="117">
+      <c r="M24" s="100">
         <f>E24*G24*K24*H24</f>
         <v>805.89515999999981</v>
       </c>
-      <c r="O24" s="144"/>
-      <c r="P24" s="144"/>
-      <c r="Q24" s="144" t="str">
+      <c r="O24" s="123"/>
+      <c r="P24" s="123"/>
+      <c r="Q24" s="123" t="str">
         <f>LEFT($B$2)&amp;'EB2'!$C$26&amp;$H$2&amp;'EB2'!$U$2</f>
         <v>TPUBEELC</v>
       </c>
-      <c r="R24" s="145" t="str">
+      <c r="R24" s="123" t="str">
         <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB2'!$X$26&amp;" - "&amp;'EB2'!$U$3</f>
         <v>Demand Technologies Transport Sector - Existing Pub - Electricity</v>
       </c>
-      <c r="S24" s="146" t="s">
+      <c r="S24" s="124" t="s">
         <v>183</v>
       </c>
-      <c r="T24" s="146" t="str">
+      <c r="T24" s="124" t="str">
         <f t="shared" si="3"/>
         <v>000_Units</v>
       </c>
-      <c r="U24" s="144"/>
-      <c r="V24" s="146" t="s">
+      <c r="U24" s="123"/>
+      <c r="V24" s="124" t="s">
         <v>145</v>
       </c>
-      <c r="W24" s="144"/>
-    </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="O25" s="6"/>
-      <c r="P25" s="6"/>
-      <c r="Q25" s="6"/>
-      <c r="R25" s="6"/>
-      <c r="S25" s="6"/>
-      <c r="T25" s="6"/>
-      <c r="U25" s="6"/>
-      <c r="V25" s="6"/>
-      <c r="W25" s="6"/>
-    </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="B27" s="57"/>
+      <c r="W24" s="123"/>
+    </row>
+    <row r="27" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B27" s="44"/>
       <c r="C27" s="1" t="s">
         <v>159</v>
       </c>
       <c r="K27" s="1"/>
-      <c r="L27" s="11"/>
+      <c r="L27" s="1"/>
       <c r="M27" s="1"/>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="B28" s="77"/>
+    <row r="28" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="B28" s="64"/>
       <c r="C28" s="1" t="s">
         <v>160</v>
       </c>
       <c r="K28" s="1"/>
-      <c r="L28" s="11"/>
+      <c r="L28" s="1"/>
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A29" s="8"/>
+    <row r="29" spans="2:23" x14ac:dyDescent="0.2">
       <c r="K29" s="1"/>
-      <c r="L29" s="11"/>
+      <c r="L29" s="1"/>
       <c r="M29" s="1"/>
       <c r="N29" s="1"/>
     </row>
-    <row r="30" spans="1:23" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A30"/>
-      <c r="B30"/>
-      <c r="C30"/>
-      <c r="D30"/>
-      <c r="E30"/>
-      <c r="F30"/>
-      <c r="G30"/>
-      <c r="H30"/>
-      <c r="I30"/>
-      <c r="J30"/>
+    <row r="30" spans="2:23" x14ac:dyDescent="0.2">
       <c r="K30" s="1"/>
-      <c r="L30" s="11"/>
+      <c r="L30" s="1"/>
       <c r="M30" s="1"/>
       <c r="N30" s="1"/>
-      <c r="O30"/>
-      <c r="P30"/>
-      <c r="Q30"/>
-      <c r="R30"/>
-      <c r="S30"/>
-      <c r="T30"/>
-      <c r="U30"/>
-      <c r="V30"/>
-      <c r="W30"/>
-    </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="31" spans="2:23" x14ac:dyDescent="0.2">
       <c r="E31" s="1"/>
       <c r="N31" s="1"/>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:23" x14ac:dyDescent="0.2">
       <c r="E32" s="1"/>
     </row>
   </sheetData>
@@ -8324,7 +8144,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B1:J24"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
@@ -8340,33 +8160,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="15" x14ac:dyDescent="0.25">
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="8" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="2" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14" t="str">
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10" t="str">
         <f>DemTechs_TRA!S5</f>
         <v>BPkm</v>
       </c>
-      <c r="G2" s="14" t="str">
+      <c r="G2" s="10" t="str">
         <f>'EB2'!Y2</f>
         <v>M€2005</v>
       </c>
@@ -8392,7 +8212,7 @@
       <c r="D6" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="E6" s="91">
+      <c r="E6" s="76">
         <v>2005</v>
       </c>
       <c r="G6" s="2" t="s">
@@ -8409,99 +8229,99 @@
       </c>
     </row>
     <row r="7" spans="2:10" ht="22.5" x14ac:dyDescent="0.2">
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="D7" s="20" t="s">
+      <c r="D7" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="E7" s="87" t="s">
+      <c r="E7" s="72" t="s">
         <v>36</v>
       </c>
-      <c r="G7" s="20" t="s">
+      <c r="G7" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="H7" s="20" t="s">
+      <c r="H7" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="I7" s="20"/>
-      <c r="J7" s="20"/>
+      <c r="I7" s="16"/>
+      <c r="J7" s="16"/>
     </row>
     <row r="8" spans="2:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="17" t="str">
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="13" t="str">
         <f>E2</f>
         <v>BPkm</v>
       </c>
-      <c r="G8" s="19" t="s">
+      <c r="G8" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="H8" s="19"/>
-      <c r="I8" s="19"/>
-      <c r="J8" s="19"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="15"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B9" s="8" t="s">
+      <c r="B9" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="8" t="str">
+      <c r="C9" t="str">
         <f>DemTechs_TRA!$Q$5</f>
         <v>DTCAR</v>
       </c>
-      <c r="D9" s="25" t="s">
+      <c r="D9" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E9" s="75">
+      <c r="E9" s="62">
         <f>SUM(DemTechs_TRA!M13:M18)</f>
         <v>3067.06485564375</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="H9" s="8" t="str">
+      <c r="H9" t="str">
         <f>DemTechs_TRA!$Q$5</f>
         <v>DTCAR</v>
       </c>
-      <c r="I9" s="39" t="s">
+      <c r="I9" s="23" t="s">
         <v>121</v>
       </c>
-      <c r="J9" s="80">
+      <c r="J9" s="67">
         <v>0.25</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B10" s="8" t="s">
+      <c r="B10" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="8" t="str">
+      <c r="C10" t="str">
         <f>DemTechs_TRA!$Q$6</f>
         <v>DTPUB</v>
       </c>
-      <c r="D10" s="25" t="s">
+      <c r="D10" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E10" s="75">
+      <c r="E10" s="62">
         <f>SUM(DemTechs_TRA!M19:M24)</f>
         <v>1727.9701023749997</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="H10" s="8" t="str">
+      <c r="H10" t="str">
         <f>DemTechs_TRA!$Q$5</f>
         <v>DTCAR</v>
       </c>
-      <c r="I10" s="39" t="s">
+      <c r="I10" s="23" t="s">
         <v>122</v>
       </c>
-      <c r="J10" s="80">
+      <c r="J10" s="67">
         <v>0.25</v>
       </c>
     </row>
@@ -8509,46 +8329,46 @@
       <c r="G11" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="H11" s="8" t="str">
+      <c r="H11" t="str">
         <f>DemTechs_TRA!$Q$5</f>
         <v>DTCAR</v>
       </c>
-      <c r="I11" s="39" t="s">
+      <c r="I11" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="J11" s="80">
+      <c r="J11" s="67">
         <v>0.25</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="E12" s="36"/>
-      <c r="G12" s="40" t="s">
+      <c r="E12" s="26"/>
+      <c r="G12" s="27" t="s">
         <v>120</v>
       </c>
-      <c r="H12" s="27" t="str">
+      <c r="H12" s="6" t="str">
         <f>DemTechs_TRA!$Q$5</f>
         <v>DTCAR</v>
       </c>
-      <c r="I12" s="41" t="s">
+      <c r="I12" s="28" t="s">
         <v>124</v>
       </c>
-      <c r="J12" s="113">
+      <c r="J12" s="97">
         <v>0.25</v>
       </c>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="E13" s="10"/>
+      <c r="E13" s="7"/>
       <c r="G13" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="H13" s="8" t="str">
+      <c r="H13" t="str">
         <f>DemTechs_TRA!$Q$6</f>
         <v>DTPUB</v>
       </c>
-      <c r="I13" s="39" t="s">
+      <c r="I13" s="23" t="s">
         <v>121</v>
       </c>
-      <c r="J13" s="80">
+      <c r="J13" s="67">
         <v>0.25</v>
       </c>
     </row>
@@ -8556,30 +8376,30 @@
       <c r="G14" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="H14" s="8" t="str">
+      <c r="H14" t="str">
         <f>DemTechs_TRA!$Q$6</f>
         <v>DTPUB</v>
       </c>
-      <c r="I14" s="39" t="s">
+      <c r="I14" s="23" t="s">
         <v>122</v>
       </c>
-      <c r="J14" s="80">
+      <c r="J14" s="67">
         <v>0.25</v>
       </c>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="E15" s="10"/>
+      <c r="E15" s="7"/>
       <c r="G15" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="H15" s="8" t="str">
+      <c r="H15" t="str">
         <f>DemTechs_TRA!$Q$6</f>
         <v>DTPUB</v>
       </c>
-      <c r="I15" s="39" t="s">
+      <c r="I15" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="J15" s="80">
+      <c r="J15" s="67">
         <v>0.25</v>
       </c>
     </row>
@@ -8587,25 +8407,25 @@
       <c r="G16" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="H16" s="8" t="str">
+      <c r="H16" t="str">
         <f>DemTechs_TRA!$Q$6</f>
         <v>DTPUB</v>
       </c>
-      <c r="I16" s="118" t="s">
+      <c r="I16" s="23" t="s">
         <v>124</v>
       </c>
-      <c r="J16" s="80">
+      <c r="J16" s="67">
         <v>0.25</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B23" s="57"/>
+      <c r="B23" s="44"/>
       <c r="C23" s="1" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B24" s="77"/>
+      <c r="B24" s="64"/>
       <c r="C24" s="1" t="s">
         <v>160</v>
       </c>
@@ -8617,123 +8437,183 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:I24"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="B3:Q35"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:9" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="48" t="s">
+    <row r="3" spans="2:15" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="35" t="s">
         <v>149</v>
       </c>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-    </row>
-    <row r="4" spans="2:9" s="6" customFormat="1" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="49"/>
-      <c r="C4" s="49"/>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="49"/>
-      <c r="G4" s="49"/>
-    </row>
-    <row r="5" spans="2:9" ht="18" x14ac:dyDescent="0.25">
-      <c r="B5" s="46" t="s">
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+    </row>
+    <row r="4" spans="2:15" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
+    </row>
+    <row r="5" spans="2:15" ht="18" x14ac:dyDescent="0.25">
+      <c r="B5" s="33" t="s">
         <v>150</v>
       </c>
-      <c r="C5" s="47"/>
-      <c r="G5" s="38"/>
-      <c r="H5" s="38"/>
-    </row>
-    <row r="6" spans="2:9" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="C6" s="51" t="str">
+      <c r="C5" s="34"/>
+    </row>
+    <row r="6" spans="2:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="38" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="38" t="str">
         <f>Sector_Fuels_TRA!L5</f>
         <v>TRAGAS</v>
       </c>
-      <c r="D6" s="51" t="str">
+      <c r="D6" s="38" t="str">
         <f>Sector_Fuels_TRA!L6</f>
         <v>TRADSL</v>
       </c>
-      <c r="E6" s="51" t="str">
+      <c r="E6" s="38" t="str">
         <f>Sector_Fuels_TRA!L7</f>
         <v>TRALPG</v>
       </c>
-      <c r="F6" s="51" t="str">
+      <c r="F6" s="38" t="str">
         <f>Sector_Fuels_TRA!L8</f>
         <v>TRAGSL</v>
       </c>
-      <c r="G6" s="50"/>
-      <c r="H6" s="50"/>
+      <c r="G6" s="37"/>
+      <c r="H6" s="37"/>
       <c r="I6" s="1"/>
     </row>
-    <row r="7" spans="2:9" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="19" t="s">
+    <row r="7" spans="2:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="G7" s="119"/>
-      <c r="H7" s="119"/>
+      <c r="G7" s="101"/>
+      <c r="H7" s="101"/>
       <c r="I7" s="1"/>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B8" s="50" t="str">
+    <row r="8" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B8" s="37" t="str">
         <f>DemTechs_TRA!Q7</f>
         <v>TRACO2</v>
       </c>
-      <c r="C8" s="80">
+      <c r="C8" s="67">
         <v>56.1</v>
       </c>
-      <c r="D8" s="80">
+      <c r="D8" s="67">
         <v>75</v>
       </c>
-      <c r="E8" s="80">
+      <c r="E8" s="67">
         <v>64</v>
       </c>
-      <c r="F8" s="80">
+      <c r="F8" s="67">
         <v>73</v>
       </c>
-      <c r="G8" s="120"/>
-      <c r="H8" s="120"/>
+      <c r="G8" s="102"/>
+      <c r="H8" s="102"/>
       <c r="I8" s="1"/>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="G9" s="38"/>
-      <c r="H9" s="38"/>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="G10" s="38"/>
-      <c r="H10" s="38"/>
-    </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B23" s="57"/>
+    <row r="9" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="L9" t="s">
+        <v>188</v>
+      </c>
+      <c r="M9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="11" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="K11" t="s">
+        <v>187</v>
+      </c>
+      <c r="O11" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="14" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="M14" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="17" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="O17" s="125" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="18" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="K18" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="21" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="J21" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="22" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="K22" t="s">
+        <v>189</v>
+      </c>
+      <c r="N22" s="125" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="23" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B23" s="44"/>
       <c r="C23" s="1" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B24" s="77"/>
+      <c r="N23" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="24" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B24" s="64"/>
       <c r="C24" s="1" t="s">
         <v>160</v>
+      </c>
+    </row>
+    <row r="25" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="P25" s="125" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="26" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="K26" s="125" t="s">
+        <v>193</v>
+      </c>
+      <c r="L26" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="29" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="125" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="35" spans="10:10" x14ac:dyDescent="0.2">
+      <c r="J35" s="125" t="s">
+        <v>192</v>
       </c>
     </row>
   </sheetData>

--- a/VT_REG2_TRA_V12.xlsx
+++ b/VT_REG2_TRA_V12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\veda-testing-model-private\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F11E3F78-B3CD-455B-AD79-15D6FE5572B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{576C7C28-0A36-4EA0-9AE0-AD8F6A51F51D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="901" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1538,7 +1538,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="207">
   <si>
     <t>CommName</t>
   </si>
@@ -2120,6 +2120,45 @@
   </si>
   <si>
     <t>;k</t>
+  </si>
+  <si>
+    <t>v</t>
+  </si>
+  <si>
+    <t>fds</t>
+  </si>
+  <si>
+    <t>fd</t>
+  </si>
+  <si>
+    <t>ddfs</t>
+  </si>
+  <si>
+    <t>ds</t>
+  </si>
+  <si>
+    <t>f</t>
+  </si>
+  <si>
+    <t>df</t>
+  </si>
+  <si>
+    <t>sfd</t>
+  </si>
+  <si>
+    <t>fdf</t>
+  </si>
+  <si>
+    <t>d</t>
+  </si>
+  <si>
+    <t>sdfs</t>
+  </si>
+  <si>
+    <t>fsdf</t>
+  </si>
+  <si>
+    <t>sf</t>
   </si>
 </sst>
 </file>
@@ -8444,7 +8483,7 @@
     <col min="2" max="2" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:15" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="35" t="s">
         <v>149</v>
       </c>
@@ -8454,22 +8493,37 @@
       <c r="F3" s="35"/>
       <c r="G3" s="35"/>
       <c r="H3" s="35"/>
-    </row>
-    <row r="4" spans="2:15" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J3" t="s">
+        <v>202</v>
+      </c>
+      <c r="M3" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="4" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="36"/>
       <c r="C4" s="36"/>
       <c r="D4" s="36"/>
       <c r="E4" s="36"/>
       <c r="F4" s="36"/>
       <c r="G4" s="36"/>
-    </row>
-    <row r="5" spans="2:15" ht="18" x14ac:dyDescent="0.25">
+      <c r="L4" t="s">
+        <v>200</v>
+      </c>
+      <c r="N4" t="s">
+        <v>205</v>
+      </c>
+      <c r="P4" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="5" spans="2:16" ht="18" x14ac:dyDescent="0.25">
       <c r="B5" s="33" t="s">
         <v>150</v>
       </c>
       <c r="C5" s="34"/>
     </row>
-    <row r="6" spans="2:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:16" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B6" s="38" t="s">
         <v>0</v>
       </c>
@@ -8491,9 +8545,14 @@
       </c>
       <c r="G6" s="37"/>
       <c r="H6" s="37"/>
-      <c r="I6" s="1"/>
-    </row>
-    <row r="7" spans="2:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="I6" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="M6" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="7" spans="2:16" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B7" s="15" t="s">
         <v>91</v>
       </c>
@@ -8513,7 +8572,7 @@
       <c r="H7" s="101"/>
       <c r="I7" s="1"/>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B8" s="37" t="str">
         <f>DemTechs_TRA!Q7</f>
         <v>TRACO2</v>
@@ -8531,10 +8590,15 @@
         <v>73</v>
       </c>
       <c r="G8" s="102"/>
-      <c r="H8" s="102"/>
+      <c r="H8" s="102" t="s">
+        <v>206</v>
+      </c>
       <c r="I8" s="1"/>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="I9" t="s">
+        <v>201</v>
+      </c>
       <c r="L9" t="s">
         <v>188</v>
       </c>
@@ -8542,7 +8606,10 @@
         <v>187</v>
       </c>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="I11" t="s">
+        <v>199</v>
+      </c>
       <c r="K11" t="s">
         <v>187</v>
       </c>
@@ -8550,12 +8617,15 @@
         <v>186</v>
       </c>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:16" x14ac:dyDescent="0.2">
       <c r="M14" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="17" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="I17" t="s">
+        <v>199</v>
+      </c>
       <c r="O17" s="125" t="s">
         <v>189</v>
       </c>
@@ -8566,6 +8636,9 @@
       </c>
     </row>
     <row r="21" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="I21" t="s">
+        <v>200</v>
+      </c>
       <c r="J21" t="s">
         <v>189</v>
       </c>
@@ -8594,11 +8667,17 @@
       </c>
     </row>
     <row r="25" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="H25" t="s">
+        <v>196</v>
+      </c>
       <c r="P25" s="125" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="26" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="G26" t="s">
+        <v>199</v>
+      </c>
       <c r="K26" s="125" t="s">
         <v>193</v>
       </c>
@@ -8606,12 +8685,33 @@
         <v>189</v>
       </c>
     </row>
+    <row r="27" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="E27" t="s">
+        <v>198</v>
+      </c>
+    </row>
     <row r="29" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="C29" t="s">
+        <v>197</v>
+      </c>
       <c r="Q29" s="125" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="35" spans="10:10" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B33" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="F34" t="s">
+        <v>195</v>
+      </c>
+      <c r="L34" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J35" s="125" t="s">
         <v>192</v>
       </c>

--- a/VT_REG2_TRA_V12.xlsx
+++ b/VT_REG2_TRA_V12.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr showObjects="placeholders" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\veda-testing-model-private\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{576C7C28-0A36-4EA0-9AE0-AD8F6A51F51D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09821A44-7A95-4717-A262-757D6EA23794}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="901" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1538,7 +1538,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="213">
   <si>
     <t>CommName</t>
   </si>
@@ -2159,6 +2159,24 @@
   </si>
   <si>
     <t>sf</t>
+  </si>
+  <si>
+    <t>kijopiop</t>
+  </si>
+  <si>
+    <t>iui</t>
+  </si>
+  <si>
+    <t>uipoui</t>
+  </si>
+  <si>
+    <t>ipo</t>
+  </si>
+  <si>
+    <t>oou</t>
+  </si>
+  <si>
+    <t>opuipo</t>
   </si>
 </sst>
 </file>
@@ -8477,13 +8495,18 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="B3:Q35"/>
+  <dimension ref="B2:V35"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="S2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="3" spans="2:22" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="35" t="s">
         <v>149</v>
       </c>
@@ -8500,7 +8523,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="4" spans="2:16" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:22" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="36"/>
       <c r="C4" s="36"/>
       <c r="D4" s="36"/>
@@ -8517,13 +8540,19 @@
         <v>203</v>
       </c>
     </row>
-    <row r="5" spans="2:16" ht="18" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:22" ht="18" x14ac:dyDescent="0.25">
       <c r="B5" s="33" t="s">
         <v>150</v>
       </c>
       <c r="C5" s="34"/>
-    </row>
-    <row r="6" spans="2:16" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="Q5" t="s">
+        <v>210</v>
+      </c>
+      <c r="V5" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="6" spans="2:22" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B6" s="38" t="s">
         <v>0</v>
       </c>
@@ -8552,7 +8581,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="7" spans="2:16" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:22" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B7" s="15" t="s">
         <v>91</v>
       </c>
@@ -8572,7 +8601,7 @@
       <c r="H7" s="101"/>
       <c r="I7" s="1"/>
     </row>
-    <row r="8" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B8" s="37" t="str">
         <f>DemTechs_TRA!Q7</f>
         <v>TRACO2</v>
@@ -8594,8 +8623,11 @@
         <v>206</v>
       </c>
       <c r="I8" s="1"/>
-    </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="S8" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="9" spans="2:22" x14ac:dyDescent="0.2">
       <c r="I9" t="s">
         <v>201</v>
       </c>
@@ -8606,7 +8638,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="11" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:22" x14ac:dyDescent="0.2">
       <c r="I11" t="s">
         <v>199</v>
       </c>
@@ -8617,7 +8649,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="14" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:22" x14ac:dyDescent="0.2">
       <c r="M14" t="s">
         <v>185</v>
       </c>
@@ -8628,6 +8660,9 @@
       </c>
       <c r="O17" s="125" t="s">
         <v>189</v>
+      </c>
+      <c r="P17" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="18" spans="2:17" x14ac:dyDescent="0.2">
@@ -8696,6 +8731,11 @@
       </c>
       <c r="Q29" s="125" t="s">
         <v>190</v>
+      </c>
+    </row>
+    <row r="30" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q30" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">

--- a/VT_REG2_TRA_V12.xlsx
+++ b/VT_REG2_TRA_V12.xlsx
@@ -1,28 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
-  <workbookPr showObjects="placeholders" codeName="ThisWorkbook"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\veda-testing-model-private\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09821A44-7A95-4717-A262-757D6EA23794}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="901" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="901" activeTab="5"/>
   </bookViews>
   <sheets>
-    <sheet name="EB2" sheetId="133" r:id="rId1"/>
-    <sheet name="RES_TRA" sheetId="153" r:id="rId2"/>
-    <sheet name="Sector_Fuels_TRA" sheetId="152" r:id="rId3"/>
-    <sheet name="DemTechs_TRA" sheetId="141" r:id="rId4"/>
-    <sheet name="Demands" sheetId="134" r:id="rId5"/>
-    <sheet name="Emi" sheetId="149" r:id="rId6"/>
+    <sheet name="EB2" sheetId="133" r:id="rId3"/>
+    <sheet name="RES_TRA" sheetId="153" r:id="rId4"/>
+    <sheet name="Sector_Fuels_TRA" sheetId="152" r:id="rId5"/>
+    <sheet name="DemTechs_TRA" sheetId="141" r:id="rId6"/>
+    <sheet name="Demands" sheetId="134" r:id="rId7"/>
+    <sheet name="Emi" sheetId="149" r:id="rId8"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId7"/>
-    <externalReference r:id="rId8"/>
+    <externalReference r:id="rId10"/>
+    <externalReference r:id="rId11"/>
   </externalReferences>
   <definedNames>
     <definedName name="FID_1">[1]AGR_Fuels!$A$2</definedName>
@@ -55,746 +54,10 @@
         <r>
           <rPr>
             <sz val="9"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
           <t>Includes fisheries consumption</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Gary Goldstein</author>
-    <author>Amit Kanudia</author>
-    <author>Maurizio Gargiulo</author>
-  </authors>
-  <commentList>
-    <comment ref="J3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Csets declarations are inherited until the next one is encountered.
-Allowed Cset:
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>NRG</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> (Energy)
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>ENV</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> (Emission)
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>DEM</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> (Demand)
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>MAT</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> (Material)
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>FIN</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> (Financial)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="O3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Amit Kanudia:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-LO for PRODUCTION &gt;= CONSUMPTION (Default)
-FX for PRODUCTION = CONSUMPTION
-UP for PRODUCTION &lt;= CONSUMPTION</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="P3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000003000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Allowed CTSLvl</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-SEASON</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> (Seasonal level)</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-WEEKLY</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> (Weekly level)</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-DAYNITE</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> (day and night level)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="Q3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000004000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Allowed PeakTS</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-ANNUAL </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>(to generate Peak Equation for all the TimeSlices)</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-User TS </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>(to generate Peak Equation for a single TS)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="R3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000005000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Allowed Ctype
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>ELC</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> (Electricity)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="P13" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000006000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Allowed TsLvl
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>ANNUAL</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> (Annual level)
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>SEASON</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> (Seasonal level)
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>WEEKLY</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> (Weekly level)
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>DAYNITE</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> (day and night level)</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="Q13" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000007000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Amit Kanudia:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Needed only when one wants to override the VEDA default assignment
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="R13" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000008000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Allowed Vintage</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-NO</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> (if empty by default mean </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>NO</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>)</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-YES</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J14" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000009000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Sets declarations are </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>inherited. 
-Allowed Process Sets</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-ELE </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>(Thermal Electric Power Plant)</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-CHP </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>(Combined Heat and Power)</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-STGTSS </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>(Pump Storage)</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-STGIPS</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> (Pump Storage IP)</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-PRE </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>(Genric Process/Technology)</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-DMD</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> (Demand Device)</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-IMP </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">(Import)
-</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>EXP</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> (Export)</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-MIN </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>(Mining Process)</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-RNW </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>(Renewable Technology)</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-HPL</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> (Heating Plant)</t>
         </r>
       </text>
     </comment>
@@ -810,12 +73,11 @@
     <author>Maurizio Gargiulo</author>
   </authors>
   <commentList>
-    <comment ref="O3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
+    <comment ref="J3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
       <text>
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -827,7 +89,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -836,7 +97,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -847,7 +107,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -856,7 +115,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -867,7 +125,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -876,7 +133,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -887,7 +143,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -896,7 +151,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -907,7 +161,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -916,7 +169,672 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (Financial)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="O3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Amit Kanudia:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+LO for PRODUCTION &gt;= CONSUMPTION (Default)
+FX for PRODUCTION = CONSUMPTION
+UP for PRODUCTION &lt;= CONSUMPTION</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000003000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Allowed CTSLvl</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+SEASON</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (Seasonal level)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+WEEKLY</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (Weekly level)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+DAYNITE</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (day and night level)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000004000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Allowed PeakTS</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+ANNUAL </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>(to generate Peak Equation for all the TimeSlices)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+User TS </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>(to generate Peak Equation for a single TS)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="R3" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000005000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Allowed Ctype
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>ELC</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (Electricity)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P13" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000006000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Allowed TsLvl
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>ANNUAL</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (Annual level)
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>SEASON</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (Seasonal level)
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>WEEKLY</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (Weekly level)
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>DAYNITE</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (day and night level)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q13" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0200-000007000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Amit Kanudia:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Needed only when one wants to override the VEDA default assignment
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="R13" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000008000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Allowed Vintage</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+NO</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (if empty by default mean </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>NO</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+YES</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J14" authorId="2" shapeId="0" xr:uid="{00000000-0006-0000-0200-000009000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Sets declarations are </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>inherited. 
+Allowed Process Sets</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+ELE </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>(Thermal Electric Power Plant)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+CHP </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>(Combined Heat and Power)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+STGTSS </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>(Pump Storage)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+STGIPS</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (Pump Storage IP)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+PRE </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>(Genric Process/Technology)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+DMD</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (Demand Device)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+IMP </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">(Import)
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>EXP</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (Export)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+MIN </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>(Mining Process)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+RNW </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>(Renewable Technology)</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+HPL</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (Heating Plant)</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Gary Goldstein</author>
+    <author>Amit Kanudia</author>
+    <author>Maurizio Gargiulo</author>
+  </authors>
+  <commentList>
+    <comment ref="O3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Csets declarations are inherited until the next one is encountered.
+Allowed Cset:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>NRG</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (Energy)
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>ENV</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (Emission)
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>DEM</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (Demand)
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>MAT</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> (Material)
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>FIN</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="8"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -930,7 +848,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -939,7 +856,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -955,7 +871,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -965,7 +880,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -975,7 +889,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -985,7 +898,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -995,7 +907,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1005,7 +916,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1015,7 +925,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1028,7 +937,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1038,7 +946,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1048,7 +955,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1058,7 +964,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1068,7 +973,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1081,7 +985,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1092,7 +995,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1101,7 +1003,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1114,7 +1015,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1125,7 +1025,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1134,7 +1033,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1145,7 +1043,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1154,7 +1051,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1165,7 +1061,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1174,7 +1069,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1185,7 +1079,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1194,7 +1087,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1208,7 +1100,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1217,7 +1108,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1232,7 +1122,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1242,7 +1131,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1252,7 +1140,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1262,7 +1149,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1271,7 +1157,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1281,7 +1166,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1295,7 +1179,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1304,7 +1187,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1315,7 +1197,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1325,7 +1206,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1335,7 +1215,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1345,7 +1224,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1355,7 +1233,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1365,7 +1242,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1375,7 +1251,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1385,7 +1260,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1395,7 +1269,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1405,7 +1278,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1415,7 +1287,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1425,7 +1296,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1435,7 +1305,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1445,7 +1314,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1456,7 +1324,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1465,7 +1332,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1475,7 +1341,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1485,7 +1350,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1495,7 +1359,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1505,7 +1368,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1515,7 +1377,6 @@
           <rPr>
             <b/>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1525,7 +1386,6 @@
         <r>
           <rPr>
             <sz val="8"/>
-            <color indexed="81"/>
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
@@ -1538,7 +1398,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="215">
   <si>
     <t>CommName</t>
   </si>
@@ -1648,535 +1508,541 @@
     <t>Demand</t>
   </si>
   <si>
+    <t>COM_FR</t>
+  </si>
+  <si>
+    <t>*Commodity Set Membership</t>
+  </si>
+  <si>
+    <t>*Process Set Membership</t>
+  </si>
+  <si>
+    <t>*Technology Name</t>
+  </si>
+  <si>
+    <t>Sense of the Balance EQN.</t>
+  </si>
+  <si>
+    <t>Timeslice Level</t>
+  </si>
+  <si>
+    <t>Primary Commodity Group</t>
+  </si>
+  <si>
+    <t>TimeSlice level of Process Activity</t>
+  </si>
+  <si>
+    <t>VOC</t>
+  </si>
+  <si>
+    <t>Nox</t>
+  </si>
+  <si>
+    <t>CO2</t>
+  </si>
+  <si>
+    <t>Sector</t>
+  </si>
+  <si>
+    <t>BNK</t>
+  </si>
+  <si>
+    <t>Non Energy</t>
+  </si>
+  <si>
+    <t>ELC</t>
+  </si>
+  <si>
+    <t>Kerosenes</t>
+  </si>
+  <si>
+    <t>Diesel oil</t>
+  </si>
+  <si>
+    <t>HET</t>
+  </si>
+  <si>
+    <t>BIO</t>
+  </si>
+  <si>
+    <t>NUC</t>
+  </si>
+  <si>
+    <t>HFO</t>
+  </si>
+  <si>
+    <t>AGR</t>
+  </si>
+  <si>
+    <t>Industry</t>
+  </si>
+  <si>
+    <t>IND</t>
+  </si>
+  <si>
+    <t>Commercial</t>
+  </si>
+  <si>
+    <t>COM</t>
+  </si>
+  <si>
+    <t>Residential</t>
+  </si>
+  <si>
+    <t>RSD</t>
+  </si>
+  <si>
+    <t>FINAL</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Default Units</t>
+  </si>
+  <si>
+    <t>Electricity</t>
+  </si>
+  <si>
+    <t>Derived Heat</t>
+  </si>
+  <si>
+    <t>Industrial Wastes</t>
+  </si>
+  <si>
+    <t>Wind energy</t>
+  </si>
+  <si>
+    <t>Biofuels</t>
+  </si>
+  <si>
+    <t>Share-I~UP</t>
+  </si>
+  <si>
+    <t>Sector Name</t>
+  </si>
+  <si>
+    <t>Commodity</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>OTH</t>
+  </si>
+  <si>
+    <t>Default Unit</t>
+  </si>
+  <si>
+    <t>Currency Unit</t>
+  </si>
+  <si>
+    <t>LIFE</t>
+  </si>
+  <si>
+    <t>WD</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>Bpass*km</t>
+  </si>
+  <si>
+    <t>DEM</t>
+  </si>
+  <si>
+    <t>Capacity to Activity Factor</t>
+  </si>
+  <si>
+    <t>EFF</t>
+  </si>
+  <si>
+    <t>Solar energy</t>
+  </si>
+  <si>
+    <t>Hydro power</t>
+  </si>
+  <si>
+    <t>OPP</t>
+  </si>
+  <si>
+    <t>Nuclear Energy</t>
+  </si>
+  <si>
+    <t>Efficiency</t>
+  </si>
+  <si>
+    <t>*Units</t>
+  </si>
+  <si>
+    <t>Years</t>
+  </si>
+  <si>
+    <t>NOX</t>
+  </si>
+  <si>
+    <t>Currency</t>
+  </si>
+  <si>
+    <t>Carbon dioxide</t>
+  </si>
+  <si>
+    <t>CAP2ACT</t>
+  </si>
+  <si>
+    <t>Demand Technologies</t>
+  </si>
+  <si>
+    <t>'000 km</t>
+  </si>
+  <si>
+    <t>Utilisation Factor</t>
+  </si>
+  <si>
+    <t>Existing</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>Naphtha</t>
+  </si>
+  <si>
+    <t>Emission by sector</t>
+  </si>
+  <si>
+    <t>Transport</t>
+  </si>
+  <si>
+    <t>Passenger/Car</t>
+  </si>
+  <si>
+    <t>DSL</t>
+  </si>
+  <si>
+    <t>OIL</t>
+  </si>
+  <si>
+    <t>Activity</t>
+  </si>
+  <si>
+    <t>COA</t>
+  </si>
+  <si>
+    <t>Emissions</t>
+  </si>
+  <si>
+    <t>Input Share</t>
+  </si>
+  <si>
+    <t>Sector Fuel</t>
+  </si>
+  <si>
+    <t>PRE</t>
+  </si>
+  <si>
+    <t>DEMO</t>
+  </si>
+  <si>
+    <t>BPass*km</t>
+  </si>
+  <si>
+    <t>Motor spirit</t>
+  </si>
+  <si>
+    <t>GAS</t>
+  </si>
+  <si>
+    <t>Activity to Flo</t>
+  </si>
+  <si>
+    <t>SN</t>
+  </si>
+  <si>
+    <t>*Unit</t>
+  </si>
+  <si>
+    <t>Demand Unit</t>
+  </si>
+  <si>
+    <t>Demand Commodity Name</t>
+  </si>
+  <si>
+    <t>Timeslices</t>
+  </si>
+  <si>
+    <t>Attribute</t>
+  </si>
+  <si>
+    <t>Deafult unit</t>
+  </si>
+  <si>
+    <t>TRA</t>
+  </si>
+  <si>
+    <t>STOCK</t>
+  </si>
+  <si>
+    <t>Crude oil</t>
+  </si>
+  <si>
+    <t>Pub</t>
+  </si>
+  <si>
+    <t>PUB</t>
+  </si>
+  <si>
+    <t>REG2</t>
+  </si>
+  <si>
+    <t>Cars</t>
+  </si>
+  <si>
+    <t>CAR</t>
+  </si>
+  <si>
+    <t>Biomass</t>
+  </si>
+  <si>
+    <t>Break-out by end-use</t>
+  </si>
+  <si>
+    <t>M€2005</t>
+  </si>
+  <si>
+    <t>TOT</t>
+  </si>
+  <si>
+    <t>Solid Fuels</t>
+  </si>
+  <si>
+    <t>kt</t>
+  </si>
+  <si>
+    <t>PJ</t>
+  </si>
+  <si>
+    <t>Natural Gas</t>
+  </si>
+  <si>
+    <t>GSL</t>
+  </si>
+  <si>
+    <t>DMD</t>
+  </si>
+  <si>
+    <t>bvkm/mvkm</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>BV*km/PJ</t>
+  </si>
+  <si>
+    <t>ENV</t>
+  </si>
+  <si>
+    <t>CALIBRATION</t>
+  </si>
+  <si>
+    <t>opuipo</t>
+  </si>
+  <si>
+    <t>;</t>
+  </si>
+  <si>
+    <t>AFA</t>
+  </si>
+  <si>
+    <t>WN</t>
+  </si>
+  <si>
+    <t>SD</t>
+  </si>
+  <si>
+    <t>NRG</t>
+  </si>
+  <si>
+    <t>DAYNITE</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>Heavy Fuel Oil</t>
+  </si>
+  <si>
+    <t>;'</t>
+  </si>
+  <si>
+    <t>User inputs</t>
+  </si>
+  <si>
+    <t>Linked to the Energy Balance</t>
+  </si>
+  <si>
+    <t>Transport Demand Sectors</t>
+  </si>
+  <si>
+    <t>Other Petroleum Products</t>
+  </si>
+  <si>
+    <t>KER</t>
+  </si>
+  <si>
+    <t>NAP</t>
+  </si>
+  <si>
+    <t>LPG</t>
+  </si>
+  <si>
+    <t>NEN</t>
+  </si>
+  <si>
+    <t>Reference Energy System (from VEDA-FE Go-To RES feature)</t>
+  </si>
+  <si>
+    <t>Data used in the template to buld the model</t>
+  </si>
+  <si>
+    <t>Total Final Consumption</t>
+  </si>
+  <si>
+    <t>TFC</t>
+  </si>
+  <si>
+    <t>Bunkers</t>
+  </si>
+  <si>
+    <t>SLU</t>
+  </si>
+  <si>
+    <t>SOL</t>
+  </si>
+  <si>
+    <t>WIN</t>
+  </si>
+  <si>
+    <t>HYD</t>
+  </si>
+  <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
+    <t>Lifetime</t>
+  </si>
+  <si>
+    <t>Fixed O&amp;M Cost</t>
+  </si>
+  <si>
+    <t>FIXOM</t>
+  </si>
+  <si>
+    <t>ACTFLO~DEMO</t>
+  </si>
+  <si>
+    <t>BPkm</t>
+  </si>
+  <si>
+    <t>000_Units</t>
+  </si>
+  <si>
+    <t>Capacity</t>
+  </si>
+  <si>
     <t>Demand Value</t>
   </si>
   <si>
-    <t>*Commodity Set Membership</t>
-  </si>
-  <si>
-    <t>*Process Set Membership</t>
-  </si>
-  <si>
-    <t>*Technology Name</t>
-  </si>
-  <si>
-    <t>Sense of the Balance EQN.</t>
-  </si>
-  <si>
-    <t>Timeslice Level</t>
-  </si>
-  <si>
-    <t>Primary Commodity Group</t>
-  </si>
-  <si>
-    <t>TimeSlice level of Process Activity</t>
-  </si>
-  <si>
-    <t>COA</t>
-  </si>
-  <si>
-    <t>GAS</t>
-  </si>
-  <si>
-    <t>OIL</t>
-  </si>
-  <si>
-    <t>NUC</t>
-  </si>
-  <si>
-    <t>SLU</t>
-  </si>
-  <si>
-    <t>HET</t>
-  </si>
-  <si>
-    <t>ELC</t>
-  </si>
-  <si>
-    <t>Solid Fuels</t>
-  </si>
-  <si>
-    <t>Natural Gas</t>
-  </si>
-  <si>
-    <t>Nuclear Energy</t>
-  </si>
-  <si>
-    <t>Industrial Wastes</t>
-  </si>
-  <si>
-    <t>Derived Heat</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>FINAL</t>
-  </si>
-  <si>
-    <t>RSD</t>
-  </si>
-  <si>
-    <t>Residential</t>
-  </si>
-  <si>
-    <t>COM</t>
-  </si>
-  <si>
-    <t>Commercial</t>
-  </si>
-  <si>
-    <t>IND</t>
-  </si>
-  <si>
-    <t>Industry</t>
-  </si>
-  <si>
-    <t>AGR</t>
-  </si>
-  <si>
-    <t>Agriculture</t>
-  </si>
-  <si>
-    <t>TRA</t>
-  </si>
-  <si>
-    <t>Transport</t>
-  </si>
-  <si>
-    <t>OTH</t>
-  </si>
-  <si>
-    <t>Other</t>
-  </si>
-  <si>
-    <t>Non Energy</t>
-  </si>
-  <si>
-    <t>Bunkers</t>
-  </si>
-  <si>
-    <t>NRG</t>
-  </si>
-  <si>
-    <t>Sector Name</t>
-  </si>
-  <si>
-    <t>Commodity</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>PJ</t>
-  </si>
-  <si>
-    <t>Default Unit</t>
-  </si>
-  <si>
-    <t>Currency Unit</t>
-  </si>
-  <si>
-    <t>LIFE</t>
-  </si>
-  <si>
-    <t>Attribute</t>
-  </si>
-  <si>
-    <t>*</t>
-  </si>
-  <si>
-    <t>Demand Commodity Name</t>
-  </si>
-  <si>
-    <t>DEM</t>
-  </si>
-  <si>
-    <t>FIXOM</t>
-  </si>
-  <si>
-    <t>EFF</t>
-  </si>
-  <si>
-    <t>NEN</t>
-  </si>
-  <si>
-    <t>BNK</t>
-  </si>
-  <si>
-    <t>Electricity</t>
-  </si>
-  <si>
-    <t>TFC</t>
-  </si>
-  <si>
-    <t>Efficiency</t>
-  </si>
-  <si>
-    <t>*Units</t>
-  </si>
-  <si>
-    <t>Years</t>
-  </si>
-  <si>
-    <t>Default Units</t>
-  </si>
-  <si>
-    <t>Currency</t>
-  </si>
-  <si>
-    <t>Activity</t>
-  </si>
-  <si>
-    <t>Fixed O&amp;M Cost</t>
-  </si>
-  <si>
-    <t>DMD</t>
-  </si>
-  <si>
-    <t>AFA</t>
-  </si>
-  <si>
-    <t>Utilisation Factor</t>
-  </si>
-  <si>
-    <t>Existing</t>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>Sector</t>
-  </si>
-  <si>
-    <t>Emissions</t>
-  </si>
-  <si>
-    <t>kt</t>
-  </si>
-  <si>
-    <t>ENV</t>
-  </si>
-  <si>
-    <t>CO2</t>
-  </si>
-  <si>
-    <t>Nox</t>
-  </si>
-  <si>
-    <t>VOC</t>
-  </si>
-  <si>
-    <t>Carbon dioxide</t>
-  </si>
-  <si>
-    <t>NOX</t>
-  </si>
-  <si>
-    <t>Sector Fuel</t>
-  </si>
-  <si>
-    <t>PRE</t>
-  </si>
-  <si>
-    <t>Deafult unit</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Demand Technologies</t>
-  </si>
-  <si>
-    <t>Break-out by end-use</t>
-  </si>
-  <si>
-    <t>Emission by sector</t>
-  </si>
-  <si>
-    <t>CALIBRATION</t>
-  </si>
-  <si>
-    <t>Timeslices</t>
-  </si>
-  <si>
-    <t>COM_FR</t>
-  </si>
-  <si>
-    <t>SD</t>
-  </si>
-  <si>
-    <t>SN</t>
-  </si>
-  <si>
-    <t>WD</t>
-  </si>
-  <si>
-    <t>WN</t>
-  </si>
-  <si>
-    <t>DAYNITE</t>
-  </si>
-  <si>
-    <t>REG2</t>
-  </si>
-  <si>
-    <t>STOCK</t>
-  </si>
-  <si>
-    <t>Crude oil</t>
-  </si>
-  <si>
-    <t>DSL</t>
-  </si>
-  <si>
-    <t>KER</t>
-  </si>
-  <si>
-    <t>LPG</t>
-  </si>
-  <si>
-    <t>GSL</t>
-  </si>
-  <si>
-    <t>NAP</t>
-  </si>
-  <si>
-    <t>HFO</t>
-  </si>
-  <si>
-    <t>OPP</t>
-  </si>
-  <si>
-    <t>Heavy Fuel Oil</t>
-  </si>
-  <si>
-    <t>Other Petroleum Products</t>
-  </si>
-  <si>
-    <t>Kerosenes</t>
-  </si>
-  <si>
-    <t>Motor spirit</t>
-  </si>
-  <si>
-    <t>Naphtha</t>
-  </si>
-  <si>
-    <t>Diesel oil</t>
-  </si>
-  <si>
-    <t>Cars</t>
-  </si>
-  <si>
-    <t>Capacity</t>
-  </si>
-  <si>
-    <t>000_Units</t>
-  </si>
-  <si>
-    <t>DEMO</t>
-  </si>
-  <si>
-    <t>ACTFLO~DEMO</t>
-  </si>
-  <si>
-    <t>Passenger/Car</t>
-  </si>
-  <si>
-    <t>Activity to Flo</t>
+    <t>iui</t>
+  </si>
+  <si>
+    <t>kl;'</t>
+  </si>
+  <si>
+    <t>l</t>
+  </si>
+  <si>
+    <t>kl</t>
+  </si>
+  <si>
+    <t>ipo</t>
+  </si>
+  <si>
+    <t>fsdf</t>
+  </si>
+  <si>
+    <t>sdfs</t>
+  </si>
+  <si>
+    <t>oou</t>
+  </si>
+  <si>
+    <t>uipoui</t>
   </si>
   <si>
     <t>Dynamic coefficients for combustion emissions in transport</t>
   </si>
   <si>
+    <t>fdf</t>
+  </si>
+  <si>
+    <t>f</t>
+  </si>
+  <si>
+    <t>d</t>
+  </si>
+  <si>
     <t>~COMEMI</t>
   </si>
   <si>
-    <t>'000 km</t>
-  </si>
-  <si>
-    <t>*Unit</t>
-  </si>
-  <si>
-    <t>Demand Unit</t>
-  </si>
-  <si>
-    <t>Input Share</t>
-  </si>
-  <si>
-    <t>Share-I~UP</t>
-  </si>
-  <si>
-    <t>M€2005</t>
-  </si>
-  <si>
-    <t>Data used in the template to buld the model</t>
+    <t>sfd</t>
   </si>
   <si>
     <t>kt/PJ</t>
   </si>
   <si>
-    <t>User inputs</t>
-  </si>
-  <si>
-    <t>Linked to the Energy Balance</t>
-  </si>
-  <si>
-    <t>Reference Energy System (from VEDA-FE Go-To RES feature)</t>
-  </si>
-  <si>
-    <t>Total Final Consumption</t>
-  </si>
-  <si>
-    <t>Pub</t>
-  </si>
-  <si>
-    <t>CAR</t>
-  </si>
-  <si>
-    <t>PUB</t>
-  </si>
-  <si>
-    <t>TOT</t>
-  </si>
-  <si>
-    <t>Transport Demand Sectors</t>
-  </si>
-  <si>
-    <t>BIO</t>
-  </si>
-  <si>
-    <t>HYD</t>
-  </si>
-  <si>
-    <t>WIN</t>
-  </si>
-  <si>
-    <t>SOL</t>
-  </si>
-  <si>
-    <t>Biomass</t>
-  </si>
-  <si>
-    <t>Hydro power</t>
-  </si>
-  <si>
-    <t>Wind energy</t>
-  </si>
-  <si>
-    <t>Solar energy</t>
-  </si>
-  <si>
-    <t>Biofuels</t>
-  </si>
-  <si>
-    <t>Lifetime</t>
-  </si>
-  <si>
-    <t>CAP2ACT</t>
-  </si>
-  <si>
-    <t>Capacity to Activity Factor</t>
-  </si>
-  <si>
-    <t>BV*km/PJ</t>
-  </si>
-  <si>
-    <t>bvkm/mvkm</t>
-  </si>
-  <si>
-    <t>BPass*km</t>
-  </si>
-  <si>
-    <t>BPkm</t>
-  </si>
-  <si>
-    <t>Bpass*km</t>
+    <t>kljkljk</t>
+  </si>
+  <si>
+    <t>ddfs</t>
+  </si>
+  <si>
+    <t>;k</t>
+  </si>
+  <si>
+    <t>kijopiop</t>
+  </si>
+  <si>
+    <t>ds</t>
+  </si>
+  <si>
+    <t>nlj</t>
+  </si>
+  <si>
+    <t>sf</t>
   </si>
   <si>
     <t>kj;</t>
   </si>
   <si>
-    <t>kl</t>
-  </si>
-  <si>
-    <t>l</t>
-  </si>
-  <si>
-    <t>kl;'</t>
-  </si>
-  <si>
-    <t>;'</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
-    <t>;</t>
+    <t>fd</t>
+  </si>
+  <si>
+    <t>fds</t>
+  </si>
+  <si>
+    <t>df</t>
+  </si>
+  <si>
+    <t>v</t>
   </si>
   <si>
     <t>k;l</t>
-  </si>
-  <si>
-    <t>;k</t>
-  </si>
-  <si>
-    <t>v</t>
-  </si>
-  <si>
-    <t>fds</t>
-  </si>
-  <si>
-    <t>fd</t>
-  </si>
-  <si>
-    <t>ddfs</t>
-  </si>
-  <si>
-    <t>ds</t>
-  </si>
-  <si>
-    <t>f</t>
-  </si>
-  <si>
-    <t>df</t>
-  </si>
-  <si>
-    <t>sfd</t>
-  </si>
-  <si>
-    <t>fdf</t>
-  </si>
-  <si>
-    <t>d</t>
-  </si>
-  <si>
-    <t>sdfs</t>
-  </si>
-  <si>
-    <t>fsdf</t>
-  </si>
-  <si>
-    <t>sf</t>
-  </si>
-  <si>
-    <t>kijopiop</t>
-  </si>
-  <si>
-    <t>iui</t>
-  </si>
-  <si>
-    <t>uipoui</t>
-  </si>
-  <si>
-    <t>ipo</t>
-  </si>
-  <si>
-    <t>oou</t>
-  </si>
-  <si>
-    <t>opuipo</t>
   </si>
 </sst>
 </file>
@@ -2189,14 +2055,17 @@
     <numFmt numFmtId="166" formatCode="General_)"/>
     <numFmt numFmtId="167" formatCode="\Te\x\t"/>
   </numFmts>
-  <fonts count="28" x14ac:knownFonts="1">
+  <fonts count="25">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -2210,11 +2079,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="10"/>
       <color indexed="12"/>
@@ -2223,14 +2087,12 @@
     </font>
     <font>
       <sz val="8"/>
-      <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="8"/>
-      <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
@@ -2247,23 +2109,12 @@
     </font>
     <font>
       <sz val="9"/>
-      <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="14"/>
       <color indexed="9"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -2338,15 +2189,9 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="10"/>
-      <color theme="9" tint="-0.249977111117893"/>
+      <color theme="9" tint="-0.249970003962517"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -2364,6 +2209,13 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="9" tint="-0.249929994344711"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="20">
     <fill>
@@ -2374,7 +2226,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799979984760284"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599990010261536"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399980008602142"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor indexed="43"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799979984760284"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599990010261536"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2386,91 +2304,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor theme="4" tint="0.799979984760284"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="6" tint="0.799979984760284"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
+        <fgColor theme="7" tint="0.799979984760284"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
+        <fgColor theme="3" tint="0.799979984760284"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
+        <fgColor theme="9" tint="0.599990010261536"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2480,186 +2338,6 @@
       <left/>
       <right/>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -2676,317 +2354,646 @@
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
       </bottom>
-      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
     </border>
   </borders>
-  <cellStyleXfs count="24">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+  <cellStyleXfs count="42">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="126">
+  <cellXfs count="132">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="13" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="32" applyAlignment="1">
       <alignment horizontal="right"/>
+      <protection/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="13" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="32" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+      <protection/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="5"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="8" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" xfId="8" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="10" applyFont="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="24"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="27" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" xfId="27" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="29" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="4" xfId="20" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="4" xfId="20" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="20" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="2" xfId="32" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+      <protection/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" xfId="8" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" xfId="27" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="9" fontId="22" fillId="0" borderId="0" xfId="18" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="11"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="11" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="30">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="30" applyAlignment="1">
+      <alignment wrapText="1"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="32" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="30" applyNumberFormat="1">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="30" applyBorder="1">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="13" borderId="0" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="24" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" xfId="27" applyFont="1" applyFill="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="20" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="32" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="4" xfId="32" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" xfId="27" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="13" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="11" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="11" applyBorder="1"/>
-    <xf numFmtId="1" fontId="24" fillId="14" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="5" applyFill="1"/>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" xfId="8" quotePrefix="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="13" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="166" fontId="8" fillId="17" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="17" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="15" fillId="9" borderId="0" xfId="28" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="1" fontId="13" fillId="7" borderId="5" xfId="25" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="13" fillId="7" borderId="6" xfId="25" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="7" borderId="7" xfId="25" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="17" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" xfId="8" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="166" fontId="8" fillId="17" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="17" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="17" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="17" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="17" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="166" fontId="9" fillId="17" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="17" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="18" fillId="11" borderId="0" xfId="9" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="1" fontId="16" fillId="9" borderId="4" xfId="6" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="16" fillId="9" borderId="5" xfId="6" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="16" fillId="9" borderId="6" xfId="6" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="17" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="17" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="17" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="17" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="17" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="17" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="7" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="3" xfId="23" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="2" fontId="4" fillId="16" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" xfId="10" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="16" borderId="0" xfId="29" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="29" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="4" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="29" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="2" xfId="32" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="2" xfId="20" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="14" xfId="20" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="2" xfId="33" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="14" xfId="20" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="14" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="13" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="3"/>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="18" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="22"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="1" fontId="3" fillId="17" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="3" fillId="17" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="3" fillId="17" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="5" xfId="20" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="17" borderId="10" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="8" fillId="17" borderId="11" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="17" borderId="1" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="8" fillId="17" borderId="2" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="17" borderId="11" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="8" fillId="17" borderId="12" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="17" borderId="2" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="8" fillId="17" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="18" fillId="11" borderId="1" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="18" fillId="11" borderId="2" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="22" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="4" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="24" fillId="14" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="15" fillId="9" borderId="2" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="9" fontId="15" fillId="9" borderId="3" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="40" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="16" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="16" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="16" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="16" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="1" fillId="13" borderId="3" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="20" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="11" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" xfId="11" applyFont="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="18" fillId="11" borderId="16" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="18" fillId="11" borderId="14" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="9" fillId="17" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="30" applyFont="1">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" xfId="30" applyFont="1" applyFill="1">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="9" fontId="15" fillId="9" borderId="17" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="9" fontId="15" fillId="9" borderId="15" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="17" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="17" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="17" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="17" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="17" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="24" fillId="14" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="13" borderId="2" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="24" fillId="14" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="13" borderId="4" xfId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="3" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="3" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="167" fontId="21" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="18" fillId="2" borderId="4" xfId="20" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="21" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="18" fillId="2" borderId="4" xfId="20" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="24">
-    <cellStyle name="20% - Accent5" xfId="1" builtinId="46"/>
-    <cellStyle name="40% - Accent3" xfId="2" builtinId="39"/>
-    <cellStyle name="60% - Accent2" xfId="3" builtinId="36"/>
-    <cellStyle name="Accent1" xfId="4" builtinId="29"/>
-    <cellStyle name="Accent2" xfId="5" builtinId="33"/>
-    <cellStyle name="Calculation" xfId="6" builtinId="22"/>
-    <cellStyle name="Comma 2" xfId="7" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
-    <cellStyle name="Good" xfId="8" builtinId="26"/>
-    <cellStyle name="Input" xfId="9" builtinId="20"/>
-    <cellStyle name="Neutral" xfId="10" builtinId="28"/>
+  <cellStyles count="28">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 10" xfId="11" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
-    <cellStyle name="Normal 2" xfId="12" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
-    <cellStyle name="Normal 4" xfId="13" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
-    <cellStyle name="Normal 4 2" xfId="14" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
-    <cellStyle name="Normal 8" xfId="15" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
-    <cellStyle name="Normal 9 2" xfId="16" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
-    <cellStyle name="Normale_B2020" xfId="17" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
-    <cellStyle name="Percent" xfId="18" builtinId="5"/>
-    <cellStyle name="Percent 2" xfId="19" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
-    <cellStyle name="Percent 3" xfId="20" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
-    <cellStyle name="Percent 4" xfId="21" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
-    <cellStyle name="Percent 5" xfId="22" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
-    <cellStyle name="Standard_Sce_D_Extraction" xfId="23" xr:uid="{00000000-0005-0000-0000-000017000000}"/>
+    <cellStyle name="Percent" xfId="15" builtinId="5"/>
+    <cellStyle name="Currency" xfId="16" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="17" builtinId="7"/>
+    <cellStyle name="Comma" xfId="18" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="19" builtinId="6"/>
+    <cellStyle name="20% - Accent5" xfId="20" builtinId="46"/>
+    <cellStyle name="40% - Accent3" xfId="21" builtinId="39"/>
+    <cellStyle name="60% - Accent2" xfId="22" builtinId="36"/>
+    <cellStyle name="Accent1" xfId="23" builtinId="29"/>
+    <cellStyle name="Accent2" xfId="24" builtinId="33"/>
+    <cellStyle name="Calculation" xfId="25" builtinId="22"/>
+    <cellStyle name="Comma 2" xfId="26"/>
+    <cellStyle name="Good" xfId="27" builtinId="26"/>
+    <cellStyle name="Input" xfId="28" builtinId="20"/>
+    <cellStyle name="Neutral" xfId="29" builtinId="28"/>
+    <cellStyle name="Normal 10" xfId="30"/>
+    <cellStyle name="Normal 2" xfId="31"/>
+    <cellStyle name="Normal 4" xfId="32"/>
+    <cellStyle name="Normal 4 2" xfId="33"/>
+    <cellStyle name="Normal 8" xfId="34"/>
+    <cellStyle name="Normal 9 2" xfId="35"/>
+    <cellStyle name="Normale_B2020" xfId="36"/>
+    <cellStyle name="Percent 2" xfId="37"/>
+    <cellStyle name="Percent 3" xfId="38"/>
+    <cellStyle name="Percent 4" xfId="39"/>
+    <cellStyle name="Percent 5" xfId="40"/>
+    <cellStyle name="Standard_Sce_D_Extraction" xfId="41"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2999,7 +3006,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
@@ -3013,12 +3020,12 @@
       <xdr:row>20</xdr:row>
       <xdr:rowOff>150451</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="TextBox 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E62E8ED2-0747-4AA0-BD7A-0074F8087EB6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{e62e8ed2-0747-4aa0-bd7a-0074f8087eb6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3026,12 +3033,10 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5793950" y="4636347"/>
-          <a:ext cx="4318000" cy="964521"/>
+          <a:off x="5800725" y="2857500"/>
+          <a:ext cx="4343400" cy="981075"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+        <a:prstGeom prst="rect"/>
         <a:solidFill>
           <a:schemeClr val="accent6">
             <a:lumMod val="20000"/>
@@ -3040,7 +3045,7 @@
         </a:solidFill>
         <a:ln w="9525" cmpd="sng">
           <a:solidFill>
-            <a:schemeClr val="lt1">
+            <a:schemeClr val="bg1">
               <a:shade val="50000"/>
             </a:schemeClr>
           </a:solidFill>
@@ -3048,32 +3053,45 @@
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:lnRef>
         <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:fillRef>
         <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:effectRef>
         <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
+          <a:schemeClr val="tx1"/>
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
         <a:lstStyle/>
         <a:p>
+          <a:pPr/>
           <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="1"/>
+            <a:rPr lang="en-GB" sz="1100" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
             <a:t>Column B</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-GB" sz="1100"/>
+            <a:rPr lang="en-GB" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
             <a:t> (rows</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-GB" sz="1100" baseline="0"/>
+            <a:rPr lang="en-GB" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
             <a:t> 5 -24) is used to set up the technology and commoditiy names and descriptions in the model.</a:t>
           </a:r>
         </a:p>
@@ -3082,7 +3100,11 @@
         </a:p>
         <a:p>
           <a:r>
-            <a:rPr lang="en-GB" sz="1100" baseline="0"/>
+            <a:rPr lang="en-GB" sz="1100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
             <a:t>Row 2 and Row 3 are used to build  techology and commodity names and descriptions in the model.</a:t>
           </a:r>
           <a:endParaRPr lang="en-GB" sz="1100"/>
@@ -3095,7 +3117,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -3114,7 +3136,7 @@
         <xdr:cNvPr id="57420" name="Picture 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC30F54F-2C1D-4DC4-B84A-ED3CC3DC8E4F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{fc30f54f-2c1d-4dc4-b84a-ed3cc3dc8e4f}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3123,14 +3145,13 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+        <a:blip r:embed="rId1">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
             </a:ext>
           </a:extLst>
         </a:blip>
-        <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3140,9 +3161,7 @@
           <a:off x="123825" y="895350"/>
           <a:ext cx="800100" cy="2238375"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+        <a:prstGeom prst="rect"/>
         <a:noFill/>
         <a:ln>
           <a:noFill/>
@@ -3188,7 +3207,7 @@
         <xdr:cNvPr id="57421" name="Picture 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4FA8FA22-4A37-4FFA-8FE4-0511CE0577A7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4fa8fa22-4a37-4ffa-8fe4-0511ce0577a7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3197,14 +3216,13 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+        <a:blip r:embed="rId2">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
             </a:ext>
           </a:extLst>
         </a:blip>
-        <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3214,9 +3232,7 @@
           <a:off x="1095375" y="18859500"/>
           <a:ext cx="4029075" cy="1905000"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+        <a:prstGeom prst="rect"/>
         <a:noFill/>
         <a:ln>
           <a:noFill/>
@@ -3262,7 +3278,7 @@
         <xdr:cNvPr id="57422" name="Picture 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23FD6060-ADED-4401-82CC-C5DB068DD5F1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23fd6060-aded-4401-82cc-c5db068dd5f1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3271,14 +3287,13 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+        <a:blip r:embed="rId3">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
             </a:ext>
           </a:extLst>
         </a:blip>
-        <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3288,9 +3303,7 @@
           <a:off x="1114425" y="1038225"/>
           <a:ext cx="3114675" cy="3933825"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+        <a:prstGeom prst="rect"/>
         <a:noFill/>
         <a:ln>
           <a:noFill/>
@@ -3336,7 +3349,7 @@
         <xdr:cNvPr id="57423" name="Picture 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{506D0267-C98D-40FD-8AD7-5B8F501AB408}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{506d0267-c98d-40fd-8ad7-5b8f501ab408}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3345,14 +3358,13 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+        <a:blip r:embed="rId4">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
             </a:ext>
           </a:extLst>
         </a:blip>
-        <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3362,9 +3374,7 @@
           <a:off x="1114425" y="4972050"/>
           <a:ext cx="3114675" cy="3848100"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+        <a:prstGeom prst="rect"/>
         <a:noFill/>
         <a:ln>
           <a:noFill/>
@@ -3396,7 +3406,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
@@ -3410,12 +3420,12 @@
       <xdr:row>37</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="TextBox 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BDD6F24D-C157-4397-A14D-07C5288E415B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{bdd6f24d-c157-4397-a14d-07c5288e415b}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3423,12 +3433,10 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6528435" y="5210175"/>
-          <a:ext cx="6461760" cy="981075"/>
+          <a:off x="6524625" y="5372100"/>
+          <a:ext cx="6457950" cy="981075"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+        <a:prstGeom prst="rect"/>
         <a:solidFill>
           <a:schemeClr val="accent6">
             <a:lumMod val="20000"/>
@@ -3437,7 +3445,7 @@
         </a:solidFill>
         <a:ln w="9525" cmpd="sng">
           <a:solidFill>
-            <a:schemeClr val="lt1">
+            <a:schemeClr val="bg1">
               <a:shade val="50000"/>
             </a:schemeClr>
           </a:solidFill>
@@ -3445,16 +3453,16 @@
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:lnRef>
         <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:fillRef>
         <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:effectRef>
         <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
+          <a:schemeClr val="tx1"/>
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
@@ -3465,7 +3473,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -3477,7 +3485,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -3489,7 +3497,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -3503,7 +3511,7 @@
           <a:pPr lvl="0"/>
           <a:endParaRPr lang="en-GB" sz="1100">
             <a:solidFill>
-              <a:schemeClr val="dk1"/>
+              <a:schemeClr val="tx1"/>
             </a:solidFill>
             <a:effectLst/>
             <a:latin typeface="+mn-lt"/>
@@ -3516,7 +3524,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -3528,7 +3536,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -3539,7 +3547,7 @@
           </a:r>
           <a:endParaRPr lang="en-GB" sz="1100">
             <a:solidFill>
-              <a:schemeClr val="dk1"/>
+              <a:schemeClr val="tx1"/>
             </a:solidFill>
             <a:effectLst/>
             <a:latin typeface="+mn-lt"/>
@@ -3555,7 +3563,7 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>14</xdr:col>
@@ -3569,12 +3577,12 @@
       <xdr:row>33</xdr:row>
       <xdr:rowOff>12700</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="TextBox 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{821CAE80-4917-41B7-AB6B-8A92DDC5D758}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{821cae80-4917-41b7-ab6b-8a92ddc5d758}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3582,12 +3590,10 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9736666" y="4402667"/>
-          <a:ext cx="5886255" cy="1028700"/>
+          <a:off x="9877425" y="4933950"/>
+          <a:ext cx="5895975" cy="1047750"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+        <a:prstGeom prst="rect"/>
         <a:solidFill>
           <a:schemeClr val="accent6">
             <a:lumMod val="20000"/>
@@ -3596,7 +3602,7 @@
         </a:solidFill>
         <a:ln w="9525" cmpd="sng">
           <a:solidFill>
-            <a:schemeClr val="lt1">
+            <a:schemeClr val="bg1">
               <a:shade val="50000"/>
             </a:schemeClr>
           </a:solidFill>
@@ -3604,16 +3610,16 @@
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:lnRef>
         <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:fillRef>
         <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:effectRef>
         <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
+          <a:schemeClr val="tx1"/>
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
@@ -3624,7 +3630,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -3636,7 +3642,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -3648,7 +3654,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -3660,7 +3666,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -3672,7 +3678,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -3684,7 +3690,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -3696,7 +3702,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -3710,7 +3716,7 @@
           <a:pPr lvl="0"/>
           <a:endParaRPr lang="en-GB" sz="1100">
             <a:solidFill>
-              <a:schemeClr val="dk1"/>
+              <a:schemeClr val="tx1"/>
             </a:solidFill>
             <a:effectLst/>
             <a:latin typeface="+mn-lt"/>
@@ -3723,7 +3729,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -3735,7 +3741,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -3746,7 +3752,7 @@
           </a:r>
           <a:endParaRPr lang="en-GB" sz="1100">
             <a:solidFill>
-              <a:schemeClr val="dk1"/>
+              <a:schemeClr val="tx1"/>
             </a:solidFill>
             <a:effectLst/>
             <a:latin typeface="+mn-lt"/>
@@ -3762,7 +3768,7 @@
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -3776,12 +3782,12 @@
       <xdr:row>20</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="TextBox 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{325F9516-E8C4-4D8C-90A3-A97EB54BE666}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{325f9516-e8c4-4d8c-90a3-a97eb54be666}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3792,9 +3798,7 @@
           <a:off x="152400" y="2981325"/>
           <a:ext cx="3238500" cy="600075"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+        <a:prstGeom prst="rect"/>
         <a:solidFill>
           <a:schemeClr val="accent6">
             <a:lumMod val="20000"/>
@@ -3803,7 +3807,7 @@
         </a:solidFill>
         <a:ln w="9525" cmpd="sng">
           <a:solidFill>
-            <a:schemeClr val="lt1">
+            <a:schemeClr val="bg1">
               <a:shade val="50000"/>
             </a:schemeClr>
           </a:solidFill>
@@ -3811,16 +3815,16 @@
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:lnRef>
         <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:fillRef>
         <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:effectRef>
         <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
+          <a:schemeClr val="tx1"/>
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
@@ -3831,7 +3835,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -3843,7 +3847,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -3854,7 +3858,7 @@
           </a:r>
           <a:endParaRPr lang="en-GB" sz="1100">
             <a:solidFill>
-              <a:schemeClr val="dk1"/>
+              <a:schemeClr val="tx1"/>
             </a:solidFill>
             <a:effectLst/>
             <a:latin typeface="+mn-lt"/>
@@ -3870,7 +3874,7 @@
 </file>
 
 <file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -3884,12 +3888,12 @@
       <xdr:row>15</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:to>
-    <xdr:sp macro="" textlink="">
+    <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="2" name="TextBox 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C96F7D35-63F1-4D04-89D3-937EDEF15038}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{c96f7d35-63f1-4d04-89d3-937edef15038}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3897,12 +3901,10 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="609600" y="1971675"/>
+          <a:off x="609600" y="2143125"/>
           <a:ext cx="4391025" cy="552450"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
+        <a:prstGeom prst="rect"/>
         <a:solidFill>
           <a:schemeClr val="accent6">
             <a:lumMod val="20000"/>
@@ -3911,7 +3913,7 @@
         </a:solidFill>
         <a:ln w="9525" cmpd="sng">
           <a:solidFill>
-            <a:schemeClr val="lt1">
+            <a:schemeClr val="bg1">
               <a:shade val="50000"/>
             </a:schemeClr>
           </a:solidFill>
@@ -3919,16 +3921,16 @@
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:lnRef>
         <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:fillRef>
         <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
+          <a:srgbClr val="000000"/>
         </a:effectRef>
         <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
+          <a:schemeClr val="tx1"/>
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
@@ -3939,7 +3941,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -3951,7 +3953,7 @@
           <a:r>
             <a:rPr lang="en-GB" sz="1100" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="dk1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:effectLst/>
               <a:latin typeface="+mn-lt"/>
@@ -3962,7 +3964,7 @@
           </a:r>
           <a:endParaRPr lang="en-GB" sz="1100">
             <a:solidFill>
-              <a:schemeClr val="dk1"/>
+              <a:schemeClr val="tx1"/>
             </a:solidFill>
             <a:effectLst/>
             <a:latin typeface="+mn-lt"/>
@@ -3978,7 +3980,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="IEA Data"/>
@@ -4113,7 +4115,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="EnergyBalance"/>
@@ -4127,10 +4129,10 @@
       <sheetData sheetId="2">
         <row r="16">
           <cell r="D16">
-            <v>124.79425000000001</v>
+            <v>124.79425</v>
           </cell>
           <cell r="E16">
-            <v>3095.8757999999998</v>
+            <v>3095.8758</v>
           </cell>
           <cell r="G16">
             <v>862.053</v>
@@ -4139,10 +4141,10 @@
             <v>72.9495</v>
           </cell>
           <cell r="I16">
-            <v>190.17599999999999</v>
+            <v>190.176</v>
           </cell>
           <cell r="J16">
-            <v>3.1680000000000001</v>
+            <v>3.168</v>
           </cell>
           <cell r="K16">
             <v>0</v>
@@ -4157,7 +4159,7 @@
             <v>0</v>
           </cell>
           <cell r="O16">
-            <v>298.48174999999992</v>
+            <v>298.48175</v>
           </cell>
           <cell r="P16">
             <v>0</v>
@@ -4172,21 +4174,21 @@
             <v>0</v>
           </cell>
           <cell r="T16">
-            <v>432.74250000000001</v>
+            <v>432.7425</v>
           </cell>
           <cell r="U16">
-            <v>1435.8710000000001</v>
+            <v>1435.871</v>
           </cell>
         </row>
         <row r="17">
           <cell r="D17">
-            <v>19.923749999999998</v>
+            <v>19.92375</v>
           </cell>
           <cell r="E17">
             <v>1051.038</v>
           </cell>
           <cell r="G17">
-            <v>368.84399999999999</v>
+            <v>368.844</v>
           </cell>
           <cell r="H17">
             <v>1.677</v>
@@ -4204,7 +4206,7 @@
             <v>19.32</v>
           </cell>
           <cell r="M17">
-            <v>0.24199999999999999</v>
+            <v>0.242</v>
           </cell>
           <cell r="N17">
             <v>0</v>
@@ -4222,10 +4224,10 @@
             <v>7.5</v>
           </cell>
           <cell r="S17">
-            <v>0.60850000000000004</v>
+            <v>0.6085</v>
           </cell>
           <cell r="T17">
-            <v>127.32299999999999</v>
+            <v>127.323</v>
           </cell>
           <cell r="U17">
             <v>1263.6955</v>
@@ -4233,37 +4235,37 @@
         </row>
         <row r="18">
           <cell r="D18">
-            <v>663.94509999999991</v>
+            <v>663.9451</v>
           </cell>
           <cell r="E18">
-            <v>2662.2965999999997</v>
+            <v>2662.2966</v>
           </cell>
           <cell r="G18">
             <v>298.68</v>
           </cell>
           <cell r="H18">
-            <v>36.356499999999997</v>
+            <v>36.3565</v>
           </cell>
           <cell r="I18">
-            <v>142.97149999999999</v>
+            <v>142.9715</v>
           </cell>
           <cell r="J18">
             <v>7.766</v>
           </cell>
           <cell r="K18">
-            <v>44.066000000000003</v>
+            <v>44.066</v>
           </cell>
           <cell r="L18">
             <v>286.0505</v>
           </cell>
           <cell r="M18">
-            <v>191.57300000000001</v>
+            <v>191.573</v>
           </cell>
           <cell r="N18">
             <v>0</v>
           </cell>
           <cell r="O18">
-            <v>180.41775000000007</v>
+            <v>180.41775</v>
           </cell>
           <cell r="P18">
             <v>0</v>
@@ -4275,10 +4277,10 @@
             <v>0</v>
           </cell>
           <cell r="S18">
-            <v>58.595999999999997</v>
+            <v>58.596</v>
           </cell>
           <cell r="T18">
-            <v>316.79149999999998</v>
+            <v>316.7915</v>
           </cell>
           <cell r="U18">
             <v>2044.222</v>
@@ -4286,16 +4288,16 @@
         </row>
         <row r="19">
           <cell r="D19">
-            <v>15.434999999999999</v>
+            <v>15.435</v>
           </cell>
           <cell r="E19">
-            <v>120.72359999999999</v>
+            <v>120.7236</v>
           </cell>
           <cell r="G19">
-            <v>366.58800000000002</v>
+            <v>366.588</v>
           </cell>
           <cell r="H19">
-            <v>0.47299999999999998</v>
+            <v>0.473</v>
           </cell>
           <cell r="I19">
             <v>16.169</v>
@@ -4316,7 +4318,7 @@
             <v>0</v>
           </cell>
           <cell r="O19">
-            <v>15.771500000000003</v>
+            <v>15.7715</v>
           </cell>
           <cell r="P19">
             <v>0</v>
@@ -4328,13 +4330,13 @@
             <v>0</v>
           </cell>
           <cell r="S19">
-            <v>5.0000000000000001E-4</v>
+            <v>0.0005</v>
           </cell>
           <cell r="T19">
-            <v>7.7869999999999999</v>
+            <v>7.787</v>
           </cell>
           <cell r="U19">
-            <v>9.6930000000000014</v>
+            <v>9.693</v>
           </cell>
         </row>
         <row r="20">
@@ -4351,10 +4353,10 @@
             <v>1047.652</v>
           </cell>
           <cell r="I20">
-            <v>94.230999999999995</v>
+            <v>94.231</v>
           </cell>
           <cell r="J20">
-            <v>2394.2159999999999</v>
+            <v>2394.216</v>
           </cell>
           <cell r="K20">
             <v>0</v>
@@ -4387,12 +4389,12 @@
             <v>0</v>
           </cell>
           <cell r="U20">
-            <v>132.98599999999999</v>
+            <v>132.986</v>
           </cell>
         </row>
         <row r="21">
           <cell r="D21">
-            <v>416.23084999999924</v>
+            <v>416.230849999999</v>
           </cell>
           <cell r="E21">
             <v>0</v>
@@ -4437,7 +4439,7 @@
             <v>0</v>
           </cell>
           <cell r="T21">
-            <v>313.51900000000001</v>
+            <v>313.519</v>
           </cell>
           <cell r="U21">
             <v>325</v>
@@ -4445,31 +4447,31 @@
         </row>
         <row r="22">
           <cell r="D22">
-            <v>18.358550000000001</v>
+            <v>18.35855</v>
           </cell>
           <cell r="E22">
-            <v>380.29379999999998</v>
+            <v>380.2938</v>
           </cell>
           <cell r="G22">
-            <v>76.465000000000003</v>
+            <v>76.465</v>
           </cell>
           <cell r="H22">
-            <v>4.7945000000000002</v>
+            <v>4.7945</v>
           </cell>
           <cell r="I22">
-            <v>199.87350000000001</v>
+            <v>199.8735</v>
           </cell>
           <cell r="J22">
-            <v>3.1459999999999999</v>
+            <v>3.146</v>
           </cell>
           <cell r="K22">
-            <v>899.20600000000002</v>
+            <v>899.206</v>
           </cell>
           <cell r="L22">
             <v>52.04</v>
           </cell>
           <cell r="M22">
-            <v>800.72900000000004</v>
+            <v>800.729</v>
           </cell>
           <cell r="N22">
             <v>0</v>
@@ -4504,7 +4506,7 @@
             <v>0</v>
           </cell>
           <cell r="G23">
-            <v>146.90600000000001</v>
+            <v>146.906</v>
           </cell>
           <cell r="H23">
             <v>0</v>
@@ -4903,170 +4905,170 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:AA31"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.28515625" customWidth="1"/>
-    <col min="4" max="21" width="10.85546875" customWidth="1"/>
-    <col min="22" max="22" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.4285714285714" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.2857142857143" customWidth="1"/>
+    <col min="4" max="21" width="10.8571428571429" customWidth="1"/>
+    <col min="22" max="22" width="7.28571428571429" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="2" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.5714285714286" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.71428571428571" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="9.28571428571429" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="1" spans="24:27" ht="12.75">
       <c r="X1" s="20" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="Y1" s="1" t="s">
         <v>94</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="2" spans="2:27" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="D2" s="41" t="s">
-        <v>44</v>
-      </c>
-      <c r="E2" s="41" t="s">
-        <v>45</v>
-      </c>
-      <c r="F2" s="41" t="s">
-        <v>46</v>
-      </c>
-      <c r="G2" s="41" t="s">
-        <v>129</v>
-      </c>
-      <c r="H2" s="41" t="s">
-        <v>130</v>
-      </c>
-      <c r="I2" s="41" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="2" spans="4:27" ht="15.75">
+      <c r="D2" s="126" t="s">
+        <v>109</v>
+      </c>
+      <c r="E2" s="126" t="s">
+        <v>117</v>
+      </c>
+      <c r="F2" s="126" t="s">
+        <v>107</v>
+      </c>
+      <c r="G2" s="126" t="s">
+        <v>106</v>
+      </c>
+      <c r="H2" s="126" t="s">
+        <v>163</v>
+      </c>
+      <c r="I2" s="126" t="s">
+        <v>165</v>
+      </c>
+      <c r="J2" s="126" t="s">
+        <v>142</v>
+      </c>
+      <c r="K2" s="126" t="s">
+        <v>164</v>
+      </c>
+      <c r="L2" s="126" t="s">
+        <v>56</v>
+      </c>
+      <c r="M2" s="126" t="s">
+        <v>88</v>
+      </c>
+      <c r="N2" s="126" t="s">
+        <v>55</v>
+      </c>
+      <c r="O2" s="126" t="s">
+        <v>54</v>
+      </c>
+      <c r="P2" s="126" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q2" s="126" t="s">
+        <v>174</v>
+      </c>
+      <c r="R2" s="126" t="s">
+        <v>173</v>
+      </c>
+      <c r="S2" s="126" t="s">
+        <v>172</v>
+      </c>
+      <c r="T2" s="126" t="s">
+        <v>53</v>
+      </c>
+      <c r="U2" s="126" t="s">
+        <v>50</v>
+      </c>
+      <c r="V2" s="126" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y2" s="40" t="s">
+        <v>136</v>
+      </c>
+      <c r="Z2" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="AA2" s="10" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="3" spans="3:22" ht="38.25">
+      <c r="C3" s="61" t="s">
         <v>131</v>
       </c>
-      <c r="J2" s="41" t="s">
-        <v>132</v>
-      </c>
-      <c r="K2" s="41" t="s">
-        <v>133</v>
-      </c>
-      <c r="L2" s="41" t="s">
-        <v>134</v>
-      </c>
-      <c r="M2" s="41" t="s">
-        <v>135</v>
-      </c>
-      <c r="N2" s="41" t="s">
-        <v>47</v>
-      </c>
-      <c r="O2" s="41" t="s">
-        <v>168</v>
-      </c>
-      <c r="P2" s="41" t="s">
-        <v>169</v>
-      </c>
-      <c r="Q2" s="41" t="s">
-        <v>170</v>
-      </c>
-      <c r="R2" s="41" t="s">
-        <v>171</v>
-      </c>
-      <c r="S2" s="41" t="s">
-        <v>48</v>
-      </c>
-      <c r="T2" s="41" t="s">
-        <v>49</v>
-      </c>
-      <c r="U2" s="41" t="s">
-        <v>50</v>
-      </c>
-      <c r="V2" s="41" t="s">
-        <v>166</v>
-      </c>
-      <c r="Y2" s="40" t="s">
-        <v>156</v>
-      </c>
-      <c r="Z2" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="AA2" s="10" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="3" spans="2:27" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="C3" s="61" t="s">
-        <v>126</v>
-      </c>
       <c r="D3" s="42" t="s">
-        <v>51</v>
+        <v>138</v>
       </c>
       <c r="E3" s="42" t="s">
-        <v>52</v>
+        <v>141</v>
       </c>
       <c r="F3" s="42" t="s">
         <v>128</v>
       </c>
       <c r="G3" s="42" t="s">
-        <v>141</v>
+        <v>52</v>
       </c>
       <c r="H3" s="42" t="s">
-        <v>138</v>
+        <v>51</v>
       </c>
       <c r="I3" s="42" t="s">
-        <v>131</v>
+        <v>165</v>
       </c>
       <c r="J3" s="42" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="K3" s="42" t="s">
-        <v>140</v>
+        <v>102</v>
       </c>
       <c r="L3" s="42" t="s">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="M3" s="42" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="N3" s="42" t="s">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="O3" s="42" t="s">
-        <v>176</v>
+        <v>71</v>
       </c>
       <c r="P3" s="42" t="s">
-        <v>173</v>
+        <v>87</v>
       </c>
       <c r="Q3" s="42" t="s">
-        <v>174</v>
+        <v>70</v>
       </c>
       <c r="R3" s="42" t="s">
-        <v>175</v>
+        <v>86</v>
       </c>
       <c r="S3" s="42" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="T3" s="42" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="U3" s="42" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="V3" s="42" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" spans="2:27" x14ac:dyDescent="0.2">
-      <c r="B4" s="39"/>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="2:22" ht="12.75">
+      <c r="B4" s="127"/>
       <c r="C4" s="79" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -5088,83 +5090,83 @@
       <c r="U4" s="6"/>
       <c r="V4" s="80"/>
     </row>
-    <row r="5" spans="2:27" x14ac:dyDescent="0.2">
-      <c r="B5" s="43" t="s">
-        <v>58</v>
+    <row r="5" spans="2:22" ht="12.75">
+      <c r="B5" s="128" t="s">
+        <v>63</v>
       </c>
       <c r="C5" s="51" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D5" s="81">
-        <f>[2]EB2!D16</f>
+        <f>'[2]EB2'!D16</f>
         <v>124.79425000000001</v>
       </c>
       <c r="E5" s="81">
-        <f>[2]EB2!E16</f>
+        <f>'[2]EB2'!E16</f>
         <v>3095.8757999999998</v>
       </c>
       <c r="F5" s="81">
-        <f>[2]EB2!F16</f>
+        <f>'[2]EB2'!F16</f>
         <v>0</v>
       </c>
       <c r="G5" s="81">
-        <f>[2]EB2!G16</f>
+        <f>'[2]EB2'!G16</f>
         <v>862.053</v>
       </c>
       <c r="H5" s="81">
-        <f>[2]EB2!H16</f>
+        <f>'[2]EB2'!H16</f>
         <v>72.9495</v>
       </c>
       <c r="I5" s="81">
-        <f>[2]EB2!I16</f>
+        <f>'[2]EB2'!I16</f>
         <v>190.17599999999999</v>
       </c>
       <c r="J5" s="81">
-        <f>[2]EB2!J16</f>
+        <f>'[2]EB2'!J16</f>
         <v>3.1680000000000001</v>
       </c>
       <c r="K5" s="81">
-        <f>[2]EB2!K16</f>
+        <f>'[2]EB2'!K16</f>
         <v>0</v>
       </c>
       <c r="L5" s="81">
-        <f>[2]EB2!L16</f>
+        <f>'[2]EB2'!L16</f>
         <v>15.38</v>
       </c>
       <c r="M5" s="81">
-        <f>[2]EB2!M16</f>
+        <f>'[2]EB2'!M16</f>
         <v>0.92</v>
       </c>
       <c r="N5" s="82">
-        <f>[2]EB2!N16</f>
+        <f>'[2]EB2'!N16</f>
         <v>0</v>
       </c>
       <c r="O5" s="81">
-        <f>[2]EB2!O16</f>
-        <v>298.48174999999992</v>
+        <f>'[2]EB2'!O16</f>
+        <v>298.48174999999998</v>
       </c>
       <c r="P5" s="81">
-        <f>[2]EB2!P16</f>
+        <f>'[2]EB2'!P16</f>
         <v>0</v>
       </c>
       <c r="Q5" s="81">
-        <f>[2]EB2!Q16</f>
+        <f>'[2]EB2'!Q16</f>
         <v>0</v>
       </c>
       <c r="R5" s="81">
-        <f>[2]EB2!R16</f>
+        <f>'[2]EB2'!R16</f>
         <v>50</v>
       </c>
       <c r="S5" s="81">
-        <f>[2]EB2!S16</f>
+        <f>'[2]EB2'!S16</f>
         <v>0</v>
       </c>
       <c r="T5" s="81">
-        <f>[2]EB2!T16</f>
-        <v>432.74250000000001</v>
+        <f>'[2]EB2'!T16</f>
+        <v>432.7425</v>
       </c>
       <c r="U5" s="81">
-        <f>[2]EB2!U16</f>
+        <f>'[2]EB2'!U16</f>
         <v>1435.8710000000001</v>
       </c>
       <c r="V5" s="83">
@@ -5172,658 +5174,658 @@
         <v>6582.4117999999999</v>
       </c>
     </row>
-    <row r="6" spans="2:27" x14ac:dyDescent="0.2">
-      <c r="B6" s="43" t="s">
+    <row r="6" spans="2:22" ht="12.75">
+      <c r="B6" s="128" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="52" t="s">
         <v>60</v>
       </c>
-      <c r="C6" s="52" t="s">
-        <v>61</v>
-      </c>
       <c r="D6" s="81">
-        <f>[2]EB2!D17</f>
+        <f>'[2]EB2'!D17</f>
         <v>19.923749999999998</v>
       </c>
       <c r="E6" s="81">
-        <f>[2]EB2!E17</f>
+        <f>'[2]EB2'!E17</f>
         <v>1051.038</v>
       </c>
       <c r="F6" s="81">
-        <f>[2]EB2!F17</f>
+        <f>'[2]EB2'!F17</f>
         <v>0</v>
       </c>
       <c r="G6" s="81">
-        <f>[2]EB2!G17</f>
+        <f>'[2]EB2'!G17</f>
         <v>368.84399999999999</v>
       </c>
       <c r="H6" s="81">
-        <f>[2]EB2!H17</f>
+        <f>'[2]EB2'!H17</f>
         <v>1.677</v>
       </c>
       <c r="I6" s="81">
-        <f>[2]EB2!I17</f>
+        <f>'[2]EB2'!I17</f>
         <v>31.602</v>
       </c>
       <c r="J6" s="81">
-        <f>[2]EB2!J17</f>
+        <f>'[2]EB2'!J17</f>
         <v>5.72</v>
       </c>
       <c r="K6" s="81">
-        <f>[2]EB2!K17</f>
+        <f>'[2]EB2'!K17</f>
         <v>0</v>
       </c>
       <c r="L6" s="81">
-        <f>[2]EB2!L17</f>
+        <f>'[2]EB2'!L17</f>
         <v>19.32</v>
       </c>
       <c r="M6" s="81">
-        <f>[2]EB2!M17</f>
+        <f>'[2]EB2'!M17</f>
         <v>0.24199999999999999</v>
       </c>
       <c r="N6" s="82">
-        <f>[2]EB2!N17</f>
+        <f>'[2]EB2'!N17</f>
         <v>0</v>
       </c>
       <c r="O6" s="81">
-        <f>[2]EB2!O17</f>
+        <f>'[2]EB2'!O17</f>
         <v>13</v>
       </c>
       <c r="P6" s="81">
-        <f>[2]EB2!P17</f>
+        <f>'[2]EB2'!P17</f>
         <v>0</v>
       </c>
       <c r="Q6" s="81">
-        <f>[2]EB2!Q17</f>
+        <f>'[2]EB2'!Q17</f>
         <v>0</v>
       </c>
       <c r="R6" s="81">
-        <f>[2]EB2!R17</f>
-        <v>7.5</v>
+        <f>'[2]EB2'!R17</f>
+        <v>7.50</v>
       </c>
       <c r="S6" s="81">
-        <f>[2]EB2!S17</f>
+        <f>'[2]EB2'!S17</f>
         <v>0.60850000000000004</v>
       </c>
       <c r="T6" s="81">
-        <f>[2]EB2!T17</f>
+        <f>'[2]EB2'!T17</f>
         <v>127.32299999999999</v>
       </c>
       <c r="U6" s="81">
-        <f>[2]EB2!U17</f>
+        <f>'[2]EB2'!U17</f>
         <v>1263.6955</v>
       </c>
       <c r="V6" s="83">
-        <f t="shared" ref="V6:V12" si="0">SUM(D6:U6)</f>
+        <f>SUM(D6:U6)</f>
         <v>2910.4937500000001</v>
       </c>
     </row>
-    <row r="7" spans="2:27" x14ac:dyDescent="0.2">
-      <c r="B7" s="43" t="s">
-        <v>62</v>
+    <row r="7" spans="2:22" ht="12.75">
+      <c r="B7" s="128" t="s">
+        <v>59</v>
       </c>
       <c r="C7" s="52" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="D7" s="81">
-        <f>[2]EB2!D18</f>
-        <v>663.94509999999991</v>
+        <f>'[2]EB2'!D18</f>
+        <v>663.94510000000002</v>
       </c>
       <c r="E7" s="81">
-        <f>[2]EB2!E18</f>
-        <v>2662.2965999999997</v>
+        <f>'[2]EB2'!E18</f>
+        <v>2662.2966000000001</v>
       </c>
       <c r="F7" s="81">
-        <f>[2]EB2!F18</f>
+        <f>'[2]EB2'!F18</f>
         <v>0</v>
       </c>
       <c r="G7" s="81">
-        <f>[2]EB2!G18</f>
+        <f>'[2]EB2'!G18</f>
         <v>298.68</v>
       </c>
       <c r="H7" s="81">
-        <f>[2]EB2!H18</f>
+        <f>'[2]EB2'!H18</f>
         <v>36.356499999999997</v>
       </c>
       <c r="I7" s="81">
-        <f>[2]EB2!I18</f>
+        <f>'[2]EB2'!I18</f>
         <v>142.97149999999999</v>
       </c>
       <c r="J7" s="81">
-        <f>[2]EB2!J18</f>
+        <f>'[2]EB2'!J18</f>
         <v>7.766</v>
       </c>
       <c r="K7" s="81">
-        <f>[2]EB2!K18</f>
+        <f>'[2]EB2'!K18</f>
         <v>44.066000000000003</v>
       </c>
       <c r="L7" s="81">
-        <f>[2]EB2!L18</f>
+        <f>'[2]EB2'!L18</f>
         <v>286.0505</v>
       </c>
       <c r="M7" s="81">
-        <f>[2]EB2!M18</f>
+        <f>'[2]EB2'!M18</f>
         <v>191.57300000000001</v>
       </c>
       <c r="N7" s="82">
-        <f>[2]EB2!N18</f>
+        <f>'[2]EB2'!N18</f>
         <v>0</v>
       </c>
       <c r="O7" s="81">
-        <f>[2]EB2!O18</f>
-        <v>180.41775000000007</v>
+        <f>'[2]EB2'!O18</f>
+        <v>180.41775000000001</v>
       </c>
       <c r="P7" s="81">
-        <f>[2]EB2!P18</f>
+        <f>'[2]EB2'!P18</f>
         <v>0</v>
       </c>
       <c r="Q7" s="81">
-        <f>[2]EB2!Q18</f>
+        <f>'[2]EB2'!Q18</f>
         <v>0</v>
       </c>
       <c r="R7" s="81">
-        <f>[2]EB2!R18</f>
+        <f>'[2]EB2'!R18</f>
         <v>0</v>
       </c>
       <c r="S7" s="81">
-        <f>[2]EB2!S18</f>
+        <f>'[2]EB2'!S18</f>
         <v>58.595999999999997</v>
       </c>
       <c r="T7" s="81">
-        <f>[2]EB2!T18</f>
+        <f>'[2]EB2'!T18</f>
         <v>316.79149999999998</v>
       </c>
       <c r="U7" s="81">
-        <f>[2]EB2!U18</f>
+        <f>'[2]EB2'!U18</f>
         <v>2044.222</v>
       </c>
       <c r="V7" s="83">
-        <f t="shared" si="0"/>
-        <v>6933.7324499999986</v>
-      </c>
-    </row>
-    <row r="8" spans="2:27" x14ac:dyDescent="0.2">
-      <c r="B8" s="43" t="s">
-        <v>64</v>
+        <f>SUM(D7:U7)</f>
+        <v>6933.7324499999995</v>
+      </c>
+    </row>
+    <row r="8" spans="2:22" ht="12.75">
+      <c r="B8" s="128" t="s">
+        <v>57</v>
       </c>
       <c r="C8" s="52" t="s">
-        <v>65</v>
+        <v>176</v>
       </c>
       <c r="D8" s="81">
-        <f>[2]EB2!D19</f>
-        <v>15.434999999999999</v>
+        <f>'[2]EB2'!D19</f>
+        <v>15.435</v>
       </c>
       <c r="E8" s="81">
-        <f>[2]EB2!E19</f>
-        <v>120.72359999999999</v>
+        <f>'[2]EB2'!E19</f>
+        <v>120.7236</v>
       </c>
       <c r="F8" s="81">
-        <f>[2]EB2!F19</f>
+        <f>'[2]EB2'!F19</f>
         <v>0</v>
       </c>
       <c r="G8" s="81">
-        <f>[2]EB2!G19</f>
+        <f>'[2]EB2'!G19</f>
         <v>366.58800000000002</v>
       </c>
       <c r="H8" s="81">
-        <f>[2]EB2!H19</f>
+        <f>'[2]EB2'!H19</f>
         <v>0.47299999999999998</v>
       </c>
       <c r="I8" s="81">
-        <f>[2]EB2!I19</f>
+        <f>'[2]EB2'!I19</f>
         <v>16.169</v>
       </c>
       <c r="J8" s="81">
-        <f>[2]EB2!J19</f>
+        <f>'[2]EB2'!J19</f>
         <v>1.716</v>
       </c>
       <c r="K8" s="81">
-        <f>[2]EB2!K19</f>
+        <f>'[2]EB2'!K19</f>
         <v>0</v>
       </c>
       <c r="L8" s="81">
-        <f>[2]EB2!L19</f>
+        <f>'[2]EB2'!L19</f>
         <v>13.74</v>
       </c>
       <c r="M8" s="81">
-        <f>[2]EB2!M19</f>
+        <f>'[2]EB2'!M19</f>
         <v>0</v>
       </c>
       <c r="N8" s="82">
-        <f>[2]EB2!N19</f>
+        <f>'[2]EB2'!N19</f>
         <v>0</v>
       </c>
       <c r="O8" s="81">
-        <f>[2]EB2!O19</f>
-        <v>15.771500000000003</v>
+        <f>'[2]EB2'!O19</f>
+        <v>15.7715</v>
       </c>
       <c r="P8" s="81">
-        <f>[2]EB2!P19</f>
+        <f>'[2]EB2'!P19</f>
         <v>0</v>
       </c>
       <c r="Q8" s="81">
-        <f>[2]EB2!Q19</f>
+        <f>'[2]EB2'!Q19</f>
         <v>0</v>
       </c>
       <c r="R8" s="81">
-        <f>[2]EB2!R19</f>
+        <f>'[2]EB2'!R19</f>
         <v>0</v>
       </c>
       <c r="S8" s="81">
-        <f>[2]EB2!S19</f>
-        <v>5.0000000000000001E-4</v>
+        <f>'[2]EB2'!S19</f>
+        <v>0.00050000000000000001</v>
       </c>
       <c r="T8" s="81">
-        <f>[2]EB2!T19</f>
+        <f>'[2]EB2'!T19</f>
         <v>7.7869999999999999</v>
       </c>
       <c r="U8" s="81">
-        <f>[2]EB2!U19</f>
-        <v>9.6930000000000014</v>
+        <f>'[2]EB2'!U19</f>
+        <v>9.6929999999999996</v>
       </c>
       <c r="V8" s="83">
-        <f t="shared" si="0"/>
-        <v>568.09659999999997</v>
-      </c>
-    </row>
-    <row r="9" spans="2:27" ht="15" x14ac:dyDescent="0.25">
-      <c r="B9" s="43" t="s">
-        <v>66</v>
+        <f>SUM(D8:U8)</f>
+        <v>568.09660000000008</v>
+      </c>
+    </row>
+    <row r="9" spans="2:22" ht="15">
+      <c r="B9" s="128" t="s">
+        <v>126</v>
       </c>
       <c r="C9" s="52" t="s">
-        <v>67</v>
+        <v>104</v>
       </c>
       <c r="D9" s="81">
-        <f>[2]EB2!D20</f>
+        <f>'[2]EB2'!D20</f>
         <v>0.1946</v>
       </c>
       <c r="E9" s="47">
-        <f>[2]EB2!E20</f>
+        <f>'[2]EB2'!E20</f>
         <v>12.7494</v>
       </c>
       <c r="F9" s="81">
-        <f>[2]EB2!F20</f>
+        <f>'[2]EB2'!F20</f>
         <v>0</v>
       </c>
       <c r="G9" s="47">
-        <f>[2]EB2!G20</f>
+        <f>'[2]EB2'!G20</f>
         <v>3856.2855</v>
       </c>
       <c r="H9" s="81">
-        <f>[2]EB2!H20</f>
+        <f>'[2]EB2'!H20</f>
         <v>1047.652</v>
       </c>
       <c r="I9" s="47">
-        <f>[2]EB2!I20</f>
+        <f>'[2]EB2'!I20</f>
         <v>94.230999999999995</v>
       </c>
       <c r="J9" s="47">
-        <f>[2]EB2!J20</f>
+        <f>'[2]EB2'!J20</f>
         <v>2394.2159999999999</v>
       </c>
       <c r="K9" s="81">
-        <f>[2]EB2!K20</f>
+        <f>'[2]EB2'!K20</f>
         <v>0</v>
       </c>
       <c r="L9" s="81">
-        <f>[2]EB2!L20</f>
+        <f>'[2]EB2'!L20</f>
         <v>33.24</v>
       </c>
       <c r="M9" s="81">
-        <f>[2]EB2!M20</f>
+        <f>'[2]EB2'!M20</f>
         <v>0</v>
       </c>
       <c r="N9" s="81">
-        <f>[2]EB2!N20</f>
+        <f>'[2]EB2'!N20</f>
         <v>0</v>
       </c>
       <c r="O9" s="47">
-        <f>[2]EB2!O20</f>
+        <f>'[2]EB2'!O20</f>
         <v>40.25</v>
       </c>
       <c r="P9" s="81">
-        <f>[2]EB2!P20</f>
+        <f>'[2]EB2'!P20</f>
         <v>0</v>
       </c>
       <c r="Q9" s="81">
-        <f>[2]EB2!Q20</f>
+        <f>'[2]EB2'!Q20</f>
         <v>0</v>
       </c>
       <c r="R9" s="81">
-        <f>[2]EB2!R20</f>
+        <f>'[2]EB2'!R20</f>
         <v>0</v>
       </c>
       <c r="S9" s="81">
-        <f>[2]EB2!S20</f>
+        <f>'[2]EB2'!S20</f>
         <v>0</v>
       </c>
       <c r="T9" s="81">
-        <f>[2]EB2!T20</f>
+        <f>'[2]EB2'!T20</f>
         <v>0</v>
       </c>
       <c r="U9" s="47">
-        <f>[2]EB2!U20</f>
+        <f>'[2]EB2'!U20</f>
         <v>132.98599999999999</v>
       </c>
       <c r="V9" s="83">
-        <f t="shared" si="0"/>
+        <f>SUM(D9:U9)</f>
         <v>7611.8044999999993</v>
       </c>
     </row>
-    <row r="10" spans="2:27" x14ac:dyDescent="0.2">
-      <c r="B10" s="43" t="s">
-        <v>68</v>
+    <row r="10" spans="2:22" ht="12.75">
+      <c r="B10" s="128" t="s">
+        <v>76</v>
       </c>
       <c r="C10" s="53" t="s">
-        <v>69</v>
+        <v>156</v>
       </c>
       <c r="D10" s="46">
-        <f>[2]EB2!D21</f>
-        <v>416.23084999999924</v>
+        <f>'[2]EB2'!D21</f>
+        <v>416.23084999999901</v>
       </c>
       <c r="E10" s="46">
-        <f>[2]EB2!E21</f>
+        <f>'[2]EB2'!E21</f>
         <v>0</v>
       </c>
       <c r="F10" s="46">
-        <f>[2]EB2!F21</f>
+        <f>'[2]EB2'!F21</f>
         <v>0</v>
       </c>
       <c r="G10" s="46">
-        <f>[2]EB2!G21</f>
+        <f>'[2]EB2'!G21</f>
         <v>0</v>
       </c>
       <c r="H10" s="46">
-        <f>[2]EB2!H21</f>
+        <f>'[2]EB2'!H21</f>
         <v>0</v>
       </c>
       <c r="I10" s="46">
-        <f>[2]EB2!I21</f>
+        <f>'[2]EB2'!I21</f>
         <v>0</v>
       </c>
       <c r="J10" s="46">
-        <f>[2]EB2!J21</f>
+        <f>'[2]EB2'!J21</f>
         <v>0</v>
       </c>
       <c r="K10" s="46">
-        <f>[2]EB2!K21</f>
+        <f>'[2]EB2'!K21</f>
         <v>0</v>
       </c>
       <c r="L10" s="46">
-        <f>[2]EB2!L21</f>
+        <f>'[2]EB2'!L21</f>
         <v>0</v>
       </c>
       <c r="M10" s="46">
-        <f>[2]EB2!M21</f>
+        <f>'[2]EB2'!M21</f>
         <v>0</v>
       </c>
       <c r="N10" s="46">
-        <f>[2]EB2!N21</f>
+        <f>'[2]EB2'!N21</f>
         <v>0</v>
       </c>
       <c r="O10" s="46">
-        <f>[2]EB2!O21</f>
+        <f>'[2]EB2'!O21</f>
         <v>0</v>
       </c>
       <c r="P10" s="46">
-        <f>[2]EB2!P21</f>
+        <f>'[2]EB2'!P21</f>
         <v>0</v>
       </c>
       <c r="Q10" s="46">
-        <f>[2]EB2!Q21</f>
+        <f>'[2]EB2'!Q21</f>
         <v>0</v>
       </c>
       <c r="R10" s="46">
-        <f>[2]EB2!R21</f>
+        <f>'[2]EB2'!R21</f>
         <v>0</v>
       </c>
       <c r="S10" s="46">
-        <f>[2]EB2!S21</f>
+        <f>'[2]EB2'!S21</f>
         <v>0</v>
       </c>
       <c r="T10" s="46">
-        <f>[2]EB2!T21</f>
+        <f>'[2]EB2'!T21</f>
         <v>313.51900000000001</v>
       </c>
       <c r="U10" s="46">
-        <f>[2]EB2!U21</f>
+        <f>'[2]EB2'!U21</f>
         <v>325</v>
       </c>
       <c r="V10" s="84">
-        <f t="shared" si="0"/>
-        <v>1054.7498499999992</v>
-      </c>
-    </row>
-    <row r="11" spans="2:27" x14ac:dyDescent="0.2">
-      <c r="B11" s="43" t="s">
-        <v>86</v>
+        <f>SUM(D10:U10)</f>
+        <v>1054.749849999999</v>
+      </c>
+    </row>
+    <row r="11" spans="2:22" ht="12.75">
+      <c r="B11" s="128" t="s">
+        <v>166</v>
       </c>
       <c r="C11" s="52" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="D11" s="81">
-        <f>[2]EB2!D22</f>
+        <f>'[2]EB2'!D22</f>
         <v>18.358550000000001</v>
       </c>
       <c r="E11" s="81">
-        <f>[2]EB2!E22</f>
+        <f>'[2]EB2'!E22</f>
         <v>380.29379999999998</v>
       </c>
       <c r="F11" s="81">
-        <f>[2]EB2!F22</f>
+        <f>'[2]EB2'!F22</f>
         <v>0</v>
       </c>
       <c r="G11" s="81">
-        <f>[2]EB2!G22</f>
-        <v>76.465000000000003</v>
+        <f>'[2]EB2'!G22</f>
+        <v>76.465</v>
       </c>
       <c r="H11" s="81">
-        <f>[2]EB2!H22</f>
+        <f>'[2]EB2'!H22</f>
         <v>4.7945000000000002</v>
       </c>
       <c r="I11" s="81">
-        <f>[2]EB2!I22</f>
+        <f>'[2]EB2'!I22</f>
         <v>199.87350000000001</v>
       </c>
       <c r="J11" s="81">
-        <f>[2]EB2!J22</f>
+        <f>'[2]EB2'!J22</f>
         <v>3.1459999999999999</v>
       </c>
       <c r="K11" s="81">
-        <f>[2]EB2!K22</f>
+        <f>'[2]EB2'!K22</f>
         <v>899.20600000000002</v>
       </c>
       <c r="L11" s="81">
-        <f>[2]EB2!L22</f>
+        <f>'[2]EB2'!L22</f>
         <v>52.04</v>
       </c>
       <c r="M11" s="81">
-        <f>[2]EB2!M22</f>
+        <f>'[2]EB2'!M22</f>
         <v>800.72900000000004</v>
       </c>
       <c r="N11" s="82">
-        <f>[2]EB2!N22</f>
+        <f>'[2]EB2'!N22</f>
         <v>0</v>
       </c>
       <c r="O11" s="81">
-        <f>[2]EB2!O22</f>
+        <f>'[2]EB2'!O22</f>
         <v>0</v>
       </c>
       <c r="P11" s="81">
-        <f>[2]EB2!P22</f>
+        <f>'[2]EB2'!P22</f>
         <v>0</v>
       </c>
       <c r="Q11" s="81">
-        <f>[2]EB2!Q22</f>
+        <f>'[2]EB2'!Q22</f>
         <v>0</v>
       </c>
       <c r="R11" s="81">
-        <f>[2]EB2!R22</f>
+        <f>'[2]EB2'!R22</f>
         <v>0</v>
       </c>
       <c r="S11" s="81">
-        <f>[2]EB2!S22</f>
+        <f>'[2]EB2'!S22</f>
         <v>0</v>
       </c>
       <c r="T11" s="81">
-        <f>[2]EB2!T22</f>
+        <f>'[2]EB2'!T22</f>
         <v>0</v>
       </c>
       <c r="U11" s="81">
-        <f>[2]EB2!U22</f>
+        <f>'[2]EB2'!U22</f>
         <v>0</v>
       </c>
       <c r="V11" s="83">
-        <f t="shared" si="0"/>
+        <f>SUM(D11:U11)</f>
         <v>2434.9063500000002</v>
       </c>
     </row>
-    <row r="12" spans="2:27" x14ac:dyDescent="0.2">
-      <c r="B12" s="43" t="s">
-        <v>87</v>
+    <row r="12" spans="2:22" ht="12.75">
+      <c r="B12" s="128" t="s">
+        <v>48</v>
       </c>
       <c r="C12" s="52" t="s">
-        <v>71</v>
+        <v>171</v>
       </c>
       <c r="D12" s="81">
-        <f>[2]EB2!D23</f>
+        <f>'[2]EB2'!D23</f>
         <v>0</v>
       </c>
       <c r="E12" s="81">
-        <f>[2]EB2!E23</f>
+        <f>'[2]EB2'!E23</f>
         <v>0</v>
       </c>
       <c r="F12" s="81">
-        <f>[2]EB2!F23</f>
+        <f>'[2]EB2'!F23</f>
         <v>0</v>
       </c>
       <c r="G12" s="81">
-        <f>[2]EB2!G23</f>
+        <f>'[2]EB2'!G23</f>
         <v>146.90600000000001</v>
       </c>
       <c r="H12" s="81">
-        <f>[2]EB2!H23</f>
+        <f>'[2]EB2'!H23</f>
         <v>0</v>
       </c>
       <c r="I12" s="81">
-        <f>[2]EB2!I23</f>
+        <f>'[2]EB2'!I23</f>
         <v>0</v>
       </c>
       <c r="J12" s="81">
-        <f>[2]EB2!J23</f>
+        <f>'[2]EB2'!J23</f>
         <v>0</v>
       </c>
       <c r="K12" s="81">
-        <f>[2]EB2!K23</f>
+        <f>'[2]EB2'!K23</f>
         <v>0</v>
       </c>
       <c r="L12" s="81">
-        <f>[2]EB2!L23</f>
+        <f>'[2]EB2'!L23</f>
         <v>902.14</v>
       </c>
       <c r="M12" s="81">
-        <f>[2]EB2!M23</f>
-        <v>6.5</v>
+        <f>'[2]EB2'!M23</f>
+        <v>6.50</v>
       </c>
       <c r="N12" s="82">
-        <f>[2]EB2!N23</f>
+        <f>'[2]EB2'!N23</f>
         <v>0</v>
       </c>
       <c r="O12" s="46">
-        <f>[2]EB2!O23</f>
+        <f>'[2]EB2'!O23</f>
         <v>0</v>
       </c>
       <c r="P12" s="46">
-        <f>[2]EB2!P23</f>
+        <f>'[2]EB2'!P23</f>
         <v>0</v>
       </c>
       <c r="Q12" s="46">
-        <f>[2]EB2!Q23</f>
+        <f>'[2]EB2'!Q23</f>
         <v>0</v>
       </c>
       <c r="R12" s="46">
-        <f>[2]EB2!R23</f>
+        <f>'[2]EB2'!R23</f>
         <v>0</v>
       </c>
       <c r="S12" s="81">
-        <f>[2]EB2!S23</f>
+        <f>'[2]EB2'!S23</f>
         <v>0</v>
       </c>
       <c r="T12" s="81">
-        <f>[2]EB2!T23</f>
+        <f>'[2]EB2'!T23</f>
         <v>0</v>
       </c>
       <c r="U12" s="81">
-        <f>[2]EB2!U23</f>
+        <f>'[2]EB2'!U23</f>
         <v>0</v>
       </c>
       <c r="V12" s="83">
-        <f t="shared" si="0"/>
+        <f>SUM(D12:U12)</f>
         <v>1055.546</v>
       </c>
     </row>
-    <row r="13" spans="2:27" ht="15" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:22" ht="15">
       <c r="B13" s="78" t="s">
-        <v>89</v>
+        <v>170</v>
       </c>
       <c r="C13" s="50" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="D13" s="48">
-        <f t="shared" ref="D13:V13" si="1">SUM(D5:D12)</f>
-        <v>1258.8820999999991</v>
+        <f>SUM(D5:D12)</f>
+        <v>1258.8820999999989</v>
       </c>
       <c r="E13" s="48">
-        <f t="shared" si="1"/>
+        <f>SUM(E5:E12)</f>
         <v>7322.9772000000003</v>
       </c>
       <c r="F13" s="48">
-        <f t="shared" si="1"/>
+        <f>SUM(F5:F12)</f>
         <v>0</v>
       </c>
       <c r="G13" s="48">
-        <f t="shared" si="1"/>
+        <f>SUM(G5:G12)</f>
         <v>5975.8215</v>
       </c>
       <c r="H13" s="48">
-        <f t="shared" si="1"/>
+        <f>SUM(H5:H12)</f>
         <v>1163.9024999999999</v>
       </c>
       <c r="I13" s="48">
-        <f t="shared" si="1"/>
+        <f>SUM(I5:I12)</f>
         <v>675.02300000000002</v>
       </c>
       <c r="J13" s="48">
-        <f t="shared" si="1"/>
+        <f>SUM(J5:J12)</f>
         <v>2415.732</v>
       </c>
       <c r="K13" s="48">
-        <f t="shared" si="1"/>
+        <f>SUM(K5:K12)</f>
         <v>943.27200000000005</v>
       </c>
       <c r="L13" s="48">
-        <f t="shared" si="1"/>
+        <f>SUM(L5:L12)</f>
         <v>1321.9105</v>
       </c>
       <c r="M13" s="48">
-        <f t="shared" si="1"/>
+        <f>SUM(M5:M12)</f>
         <v>999.96400000000006</v>
       </c>
       <c r="N13" s="48">
-        <f t="shared" si="1"/>
+        <f>SUM(N5:N12)</f>
         <v>0</v>
       </c>
       <c r="O13" s="48">
-        <f t="shared" si="1"/>
+        <f>SUM(O5:O12)</f>
         <v>547.92100000000005</v>
       </c>
       <c r="P13" s="48"/>
       <c r="Q13" s="48"/>
       <c r="R13" s="48"/>
       <c r="S13" s="48">
-        <f t="shared" si="1"/>
-        <v>59.204999999999998</v>
+        <f>SUM(S5:S12)</f>
+        <v>59.205</v>
       </c>
       <c r="T13" s="48">
-        <f t="shared" si="1"/>
+        <f>SUM(T5:T12)</f>
         <v>1198.163</v>
       </c>
       <c r="U13" s="48">
@@ -5831,11 +5833,11 @@
         <v>5211.4674999999997</v>
       </c>
       <c r="V13" s="49">
-        <f t="shared" si="1"/>
+        <f>SUM(V5:V12)</f>
         <v>29151.741299999998</v>
       </c>
     </row>
-    <row r="14" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="14" spans="4:13" ht="12.75">
       <c r="D14" s="7"/>
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
@@ -5846,7 +5848,7 @@
       <c r="L14" s="7"/>
       <c r="M14" s="7"/>
     </row>
-    <row r="15" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="15" spans="4:13" ht="12.75">
       <c r="D15" s="7"/>
       <c r="F15" s="7"/>
       <c r="G15" s="7"/>
@@ -5857,9 +5859,9 @@
       <c r="L15" s="7"/>
       <c r="M15" s="7"/>
     </row>
-    <row r="16" spans="2:27" ht="15" x14ac:dyDescent="0.25">
+    <row r="16" spans="3:13" ht="15">
       <c r="C16" s="47" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="D16" s="47"/>
       <c r="E16" s="47"/>
@@ -5872,7 +5874,7 @@
       <c r="L16" s="7"/>
       <c r="M16" s="7"/>
     </row>
-    <row r="17" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="17" spans="4:13" ht="12.75">
       <c r="D17" s="7"/>
       <c r="F17" s="7"/>
       <c r="G17" s="7"/>
@@ -5883,7 +5885,7 @@
       <c r="L17" s="7"/>
       <c r="M17" s="7"/>
     </row>
-    <row r="18" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="18" spans="4:13" ht="12.75">
       <c r="D18" s="7"/>
       <c r="F18" s="7"/>
       <c r="G18" s="7"/>
@@ -5894,7 +5896,7 @@
       <c r="L18" s="7"/>
       <c r="M18" s="7"/>
     </row>
-    <row r="19" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="19" spans="4:13" ht="12.75">
       <c r="D19" s="7"/>
       <c r="F19" s="7"/>
       <c r="G19" s="7"/>
@@ -5905,7 +5907,7 @@
       <c r="L19" s="7"/>
       <c r="M19" s="7"/>
     </row>
-    <row r="20" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="20" spans="4:13" ht="12.75">
       <c r="D20" s="7"/>
       <c r="F20" s="7"/>
       <c r="G20" s="7"/>
@@ -5916,7 +5918,7 @@
       <c r="L20" s="7"/>
       <c r="M20" s="7"/>
     </row>
-    <row r="21" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="21" spans="4:13" ht="12.75">
       <c r="D21" s="7"/>
       <c r="F21" s="7"/>
       <c r="G21" s="7"/>
@@ -5927,7 +5929,7 @@
       <c r="L21" s="7"/>
       <c r="M21" s="7"/>
     </row>
-    <row r="22" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="22" spans="4:13" ht="12.75">
       <c r="D22" s="7"/>
       <c r="F22" s="7"/>
       <c r="G22" s="7"/>
@@ -5938,7 +5940,7 @@
       <c r="L22" s="7"/>
       <c r="M22" s="7"/>
     </row>
-    <row r="23" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:18" ht="12.75">
       <c r="C23" s="1"/>
       <c r="D23" s="21"/>
       <c r="O23" s="6"/>
@@ -5946,77 +5948,77 @@
       <c r="Q23" s="6"/>
       <c r="R23" s="6"/>
     </row>
-    <row r="24" spans="2:24" ht="38.25" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:22" ht="38.25">
       <c r="B24" s="22" t="s">
-        <v>102</v>
+        <v>47</v>
       </c>
       <c r="C24" s="57" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="D24" s="103" t="s">
-        <v>51</v>
+        <v>138</v>
       </c>
       <c r="E24" s="104" t="s">
-        <v>52</v>
+        <v>141</v>
       </c>
       <c r="F24" s="104" t="s">
         <v>128</v>
       </c>
       <c r="G24" s="104" t="s">
-        <v>141</v>
+        <v>52</v>
       </c>
       <c r="H24" s="104" t="s">
-        <v>138</v>
+        <v>51</v>
       </c>
       <c r="I24" s="104" t="s">
-        <v>131</v>
+        <v>165</v>
       </c>
       <c r="J24" s="104" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="K24" s="104" t="s">
-        <v>140</v>
+        <v>102</v>
       </c>
       <c r="L24" s="104" t="s">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="M24" s="104" t="s">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="N24" s="104" t="s">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="O24" s="42" t="s">
-        <v>172</v>
+        <v>134</v>
       </c>
       <c r="P24" s="42" t="s">
-        <v>173</v>
+        <v>87</v>
       </c>
       <c r="Q24" s="42" t="s">
-        <v>174</v>
+        <v>70</v>
       </c>
       <c r="R24" s="42" t="s">
-        <v>175</v>
+        <v>86</v>
       </c>
       <c r="S24" s="104" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="T24" s="104" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="U24" s="105" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="V24" s="42" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="25" spans="2:24" ht="15" x14ac:dyDescent="0.25">
-      <c r="B25" s="43" t="s">
-        <v>66</v>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="2:24" ht="15">
+      <c r="B25" s="128" t="s">
+        <v>126</v>
       </c>
       <c r="C25" s="54" t="s">
-        <v>164</v>
+        <v>133</v>
       </c>
       <c r="D25" s="88"/>
       <c r="E25" s="92">
@@ -6024,7 +6026,7 @@
       </c>
       <c r="F25" s="89"/>
       <c r="G25" s="92">
-        <v>0.9</v>
+        <v>0.90</v>
       </c>
       <c r="H25" s="89"/>
       <c r="I25" s="92">
@@ -6038,7 +6040,7 @@
       <c r="M25" s="89"/>
       <c r="N25" s="89"/>
       <c r="O25" s="92">
-        <v>0.5</v>
+        <v>0.50</v>
       </c>
       <c r="P25" s="89"/>
       <c r="Q25" s="89"/>
@@ -6050,15 +6052,15 @@
       </c>
       <c r="V25" s="55"/>
       <c r="X25" s="51" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="26" spans="2:24" ht="15" x14ac:dyDescent="0.25">
-      <c r="B26" s="43" t="s">
-        <v>66</v>
+        <v>132</v>
+      </c>
+    </row>
+    <row r="26" spans="2:24" ht="15">
+      <c r="B26" s="128" t="s">
+        <v>126</v>
       </c>
       <c r="C26" s="56" t="s">
-        <v>165</v>
+        <v>130</v>
       </c>
       <c r="D26" s="90"/>
       <c r="E26" s="93">
@@ -6068,7 +6070,7 @@
       <c r="F26" s="91"/>
       <c r="G26" s="93">
         <f>1-G25</f>
-        <v>9.9999999999999978E-2</v>
+        <v>0.099999999999999978</v>
       </c>
       <c r="H26" s="91"/>
       <c r="I26" s="93">
@@ -6085,7 +6087,7 @@
       <c r="N26" s="91"/>
       <c r="O26" s="93">
         <f>1-O25</f>
-        <v>0.5</v>
+        <v>0.50</v>
       </c>
       <c r="P26" s="91"/>
       <c r="Q26" s="91"/>
@@ -6098,37 +6100,37 @@
       </c>
       <c r="V26" s="45"/>
       <c r="X26" s="53" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="29" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="C29" s="58" t="s">
-        <v>106</v>
-      </c>
-      <c r="D29" s="60" t="s">
-        <v>107</v>
-      </c>
-      <c r="E29" s="59" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="30" spans="2:24" x14ac:dyDescent="0.2">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="29" spans="3:5" ht="12.75">
+      <c r="C29" s="129" t="s">
+        <v>46</v>
+      </c>
+      <c r="D29" s="130" t="s">
+        <v>45</v>
+      </c>
+      <c r="E29" s="131" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" ht="12.75">
       <c r="B30" s="20" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="C30" s="86" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="D30" s="86" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="E30" s="87" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="31" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B31" s="43" t="s">
-        <v>66</v>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" ht="12.75">
+      <c r="B31" s="128" t="s">
+        <v>126</v>
       </c>
       <c r="C31" s="110">
         <v>1</v>
@@ -6138,30 +6140,54 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B3:G5"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="1.85546875" style="23" customWidth="1"/>
-    <col min="2" max="2" width="7.7109375" style="23" customWidth="1"/>
-    <col min="3" max="3" width="6.85546875" style="23" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="23"/>
+    <col min="1" max="1" width="1.85714285714286" style="23" customWidth="1"/>
+    <col min="2" max="2" width="7.71428571428571" style="23" customWidth="1"/>
+    <col min="3" max="3" width="6.85714285714286" style="23" customWidth="1"/>
+    <col min="4" max="16384" width="9.14285714285714" style="23"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="12.75">
+      <c r="A1" s="23"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+    </row>
+    <row r="2" spans="1:4" ht="12.75">
+      <c r="A2" s="23"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+    </row>
+    <row r="3" spans="1:4" ht="18">
+      <c r="A3" s="23"/>
       <c r="B3" s="106" t="s">
+        <v>167</v>
+      </c>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+    </row>
+    <row r="4" spans="1:4" ht="12.75">
+      <c r="A4" s="23"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+    </row>
+    <row r="5" spans="1:7" ht="12.75">
+      <c r="A5" s="23"/>
+      <c r="B5" s="23"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="107" t="s">
         <v>161</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="D5" s="107" t="s">
-        <v>167</v>
       </c>
       <c r="E5" s="107"/>
       <c r="F5" s="107"/>
@@ -6169,37 +6195,37 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
-  <drawing r:id="rId2"/>
+  <pageSetup orientation="portrait" paperSize="9" r:id="rId2"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:R36"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5714285714286" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.1428571428571" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.8571428571429" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5714285714286" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.28571428571429" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9" customWidth="1"/>
-    <col min="9" max="9" width="2.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.42578125" customWidth="1"/>
-    <col min="11" max="11" width="7.140625" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="2.14285714285714" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.4285714285714" customWidth="1"/>
+    <col min="11" max="11" width="7.14285714285714" customWidth="1"/>
+    <col min="12" max="12" width="14.5714285714286" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="63" customWidth="1"/>
-    <col min="14" max="14" width="6.140625" customWidth="1"/>
-    <col min="15" max="15" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.140625" customWidth="1"/>
+    <col min="14" max="14" width="6.14285714285714" customWidth="1"/>
+    <col min="15" max="15" width="10.4285714285714" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.8571428571429" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.1428571428571" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.14285714285714" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:18" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:8" ht="15">
       <c r="B1" s="8" t="s">
         <v>73</v>
       </c>
@@ -6210,7 +6236,7 @@
         <v>75</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="F1" s="8" t="s">
         <v>94</v>
@@ -6220,7 +6246,7 @@
       </c>
       <c r="H1" s="30"/>
     </row>
-    <row r="2" spans="2:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:18" ht="15.75">
       <c r="B2" s="10" t="str">
         <f>'EB2'!B9</f>
         <v>TRA</v>
@@ -6230,7 +6256,7 @@
         <v>Transport</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E2" s="10" t="str">
         <f>'EB2'!Z2</f>
@@ -6256,7 +6282,7 @@
       <c r="Q2" s="116"/>
       <c r="R2" s="116"/>
     </row>
-    <row r="3" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="3" spans="10:18" ht="12.75">
       <c r="J3" s="117" t="s">
         <v>7</v>
       </c>
@@ -6285,7 +6311,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:18" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:18" ht="24" thickBot="1">
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
@@ -6319,13 +6345,13 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="5:18" ht="12.75">
       <c r="E5" s="12"/>
       <c r="F5" s="12"/>
       <c r="G5" s="70"/>
       <c r="H5" s="11"/>
       <c r="J5" s="120" t="s">
-        <v>72</v>
+        <v>154</v>
       </c>
       <c r="K5" s="120"/>
       <c r="L5" s="120" t="str">
@@ -6337,7 +6363,7 @@
         <v>Transport Natural Gas</v>
       </c>
       <c r="N5" s="120" t="str">
-        <f t="shared" ref="N5:N10" si="0">$E$2</f>
+        <f>$E$2</f>
         <v>PJ</v>
       </c>
       <c r="O5" s="120"/>
@@ -6345,7 +6371,7 @@
       <c r="Q5" s="120"/>
       <c r="R5" s="120"/>
     </row>
-    <row r="6" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="5:18" ht="12.75">
       <c r="E6" s="12"/>
       <c r="F6" s="12"/>
       <c r="G6" s="70"/>
@@ -6361,7 +6387,7 @@
         <v>Transport Diesel oil</v>
       </c>
       <c r="N6" s="120" t="str">
-        <f t="shared" si="0"/>
+        <f>$E$2</f>
         <v>PJ</v>
       </c>
       <c r="O6" s="120"/>
@@ -6369,7 +6395,7 @@
       <c r="Q6" s="120"/>
       <c r="R6" s="120"/>
     </row>
-    <row r="7" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="5:18" ht="12.75">
       <c r="E7" s="12"/>
       <c r="F7" s="12"/>
       <c r="G7" s="70"/>
@@ -6385,7 +6411,7 @@
         <v>Transport LPG</v>
       </c>
       <c r="N7" s="120" t="str">
-        <f t="shared" si="0"/>
+        <f>$E$2</f>
         <v>PJ</v>
       </c>
       <c r="O7" s="120"/>
@@ -6393,7 +6419,7 @@
       <c r="Q7" s="120"/>
       <c r="R7" s="120"/>
     </row>
-    <row r="8" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="5:18" ht="12.75">
       <c r="E8" s="12"/>
       <c r="F8" s="12"/>
       <c r="G8" s="70"/>
@@ -6409,7 +6435,7 @@
         <v>Transport Motor spirit</v>
       </c>
       <c r="N8" s="120" t="str">
-        <f t="shared" si="0"/>
+        <f>$E$2</f>
         <v>PJ</v>
       </c>
       <c r="O8" s="120"/>
@@ -6417,7 +6443,7 @@
       <c r="Q8" s="120"/>
       <c r="R8" s="120"/>
     </row>
-    <row r="9" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="5:18" ht="12.75">
       <c r="E9" s="12"/>
       <c r="F9" s="12"/>
       <c r="G9" s="70"/>
@@ -6433,7 +6459,7 @@
         <v>Transport Biofuels</v>
       </c>
       <c r="N9" s="120" t="str">
-        <f t="shared" si="0"/>
+        <f>$E$2</f>
         <v>PJ</v>
       </c>
       <c r="O9" s="120"/>
@@ -6441,7 +6467,7 @@
       <c r="Q9" s="120"/>
       <c r="R9" s="120"/>
     </row>
-    <row r="10" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="5:18" ht="12.75">
       <c r="E10" s="12"/>
       <c r="F10" s="12"/>
       <c r="G10" s="70"/>
@@ -6457,23 +6483,23 @@
         <v>Transport Electricity</v>
       </c>
       <c r="N10" s="120" t="str">
-        <f t="shared" si="0"/>
+        <f>$E$2</f>
         <v>PJ</v>
       </c>
       <c r="O10" s="120"/>
       <c r="P10" s="120" t="s">
-        <v>125</v>
+        <v>155</v>
       </c>
       <c r="Q10" s="120"/>
       <c r="R10" s="120" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="12:13" ht="12.75">
       <c r="L11" s="23"/>
       <c r="M11" s="24"/>
     </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="12" spans="4:18" ht="12.75">
       <c r="D12" s="5" t="s">
         <v>13</v>
       </c>
@@ -6491,7 +6517,7 @@
       <c r="Q12" s="120"/>
       <c r="R12" s="120"/>
     </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:18" ht="12.75">
       <c r="B13" s="17" t="s">
         <v>1</v>
       </c>
@@ -6502,7 +6528,7 @@
         <v>6</v>
       </c>
       <c r="E13" s="74" t="s">
-        <v>155</v>
+        <v>72</v>
       </c>
       <c r="F13" s="71" t="s">
         <v>127</v>
@@ -6541,7 +6567,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="2:18" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:18" ht="23.25" thickBot="1">
       <c r="B14" s="16" t="s">
         <v>39</v>
       </c>
@@ -6552,7 +6578,7 @@
         <v>33</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>154</v>
+        <v>111</v>
       </c>
       <c r="F14" s="16" t="s">
         <v>34</v>
@@ -6591,7 +6617,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="2:18" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:18" ht="13.5" thickBot="1">
       <c r="B15" s="15" t="s">
         <v>91</v>
       </c>
@@ -6618,17 +6644,17 @@
       <c r="Q15" s="122"/>
       <c r="R15" s="122"/>
     </row>
-    <row r="16" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:18" ht="12.75">
       <c r="B16" t="str">
-        <f t="shared" ref="B16:B21" si="1">L16</f>
+        <f>L16</f>
         <v>FTE-TRAGAS</v>
       </c>
       <c r="C16" t="str">
-        <f t="shared" ref="C16:C21" si="2">RIGHT(D16,3)</f>
+        <f>RIGHT(D16,3)</f>
         <v>GAS</v>
       </c>
       <c r="D16" t="str">
-        <f t="shared" ref="D16:D21" si="3">L5</f>
+        <f>L5</f>
         <v>TRAGAS</v>
       </c>
       <c r="E16" s="12"/>
@@ -6640,40 +6666,40 @@
         <v>50</v>
       </c>
       <c r="J16" s="116" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K16" s="120"/>
       <c r="L16" s="120" t="str">
-        <f t="shared" ref="L16:L21" si="4">"FT"&amp;$G$2&amp;"-"&amp;L5</f>
+        <f>"FT"&amp;$G$2&amp;"-"&amp;L5</f>
         <v>FTE-TRAGAS</v>
       </c>
       <c r="M16" s="121" t="str">
-        <f t="shared" ref="M16:M21" si="5">$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M5</f>
+        <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M5</f>
         <v>Sector Fuel Technology Existing Transport Natural Gas</v>
       </c>
       <c r="N16" s="120" t="str">
-        <f t="shared" ref="N16:N21" si="6">$E$2</f>
+        <f>$E$2</f>
         <v>PJ</v>
       </c>
       <c r="O16" s="120" t="str">
-        <f t="shared" ref="O16:O21" si="7">$E$2&amp;"a"</f>
+        <f>$E$2&amp;"a"</f>
         <v>PJa</v>
       </c>
       <c r="P16" s="120"/>
       <c r="Q16" s="120"/>
       <c r="R16" s="120"/>
     </row>
-    <row r="17" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:18" ht="12.75">
       <c r="B17" t="str">
-        <f t="shared" si="1"/>
+        <f>L17</f>
         <v>FTE-TRADSL</v>
       </c>
       <c r="C17" t="str">
-        <f t="shared" si="2"/>
+        <f>RIGHT(D17,3)</f>
         <v>DSL</v>
       </c>
       <c r="D17" t="str">
-        <f t="shared" si="3"/>
+        <f>L6</f>
         <v>TRADSL</v>
       </c>
       <c r="E17" s="12"/>
@@ -6687,36 +6713,36 @@
       <c r="J17" s="116"/>
       <c r="K17" s="120"/>
       <c r="L17" s="120" t="str">
-        <f t="shared" si="4"/>
+        <f>"FT"&amp;$G$2&amp;"-"&amp;L6</f>
         <v>FTE-TRADSL</v>
       </c>
       <c r="M17" s="121" t="str">
-        <f t="shared" si="5"/>
+        <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M6</f>
         <v>Sector Fuel Technology Existing Transport Diesel oil</v>
       </c>
       <c r="N17" s="120" t="str">
-        <f t="shared" si="6"/>
+        <f>$E$2</f>
         <v>PJ</v>
       </c>
       <c r="O17" s="120" t="str">
-        <f t="shared" si="7"/>
+        <f>$E$2&amp;"a"</f>
         <v>PJa</v>
       </c>
       <c r="P17" s="120"/>
       <c r="Q17" s="120"/>
       <c r="R17" s="120"/>
     </row>
-    <row r="18" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:18" ht="12.75">
       <c r="B18" t="str">
-        <f t="shared" si="1"/>
+        <f>L18</f>
         <v>FTE-TRALPG</v>
       </c>
       <c r="C18" t="str">
-        <f t="shared" si="2"/>
+        <f>RIGHT(D18,3)</f>
         <v>LPG</v>
       </c>
       <c r="D18" t="str">
-        <f t="shared" si="3"/>
+        <f>L7</f>
         <v>TRALPG</v>
       </c>
       <c r="E18" s="12"/>
@@ -6730,36 +6756,36 @@
       <c r="J18" s="120"/>
       <c r="K18" s="120"/>
       <c r="L18" s="120" t="str">
-        <f t="shared" si="4"/>
+        <f>"FT"&amp;$G$2&amp;"-"&amp;L7</f>
         <v>FTE-TRALPG</v>
       </c>
       <c r="M18" s="121" t="str">
-        <f t="shared" si="5"/>
+        <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M7</f>
         <v>Sector Fuel Technology Existing Transport LPG</v>
       </c>
       <c r="N18" s="120" t="str">
-        <f t="shared" si="6"/>
+        <f>$E$2</f>
         <v>PJ</v>
       </c>
       <c r="O18" s="120" t="str">
-        <f t="shared" si="7"/>
+        <f>$E$2&amp;"a"</f>
         <v>PJa</v>
       </c>
       <c r="P18" s="120"/>
       <c r="Q18" s="120"/>
       <c r="R18" s="120"/>
     </row>
-    <row r="19" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:18" ht="12.75">
       <c r="B19" t="str">
-        <f t="shared" si="1"/>
+        <f>L19</f>
         <v>FTE-TRAGSL</v>
       </c>
       <c r="C19" t="str">
-        <f t="shared" si="2"/>
+        <f>RIGHT(D19,3)</f>
         <v>GSL</v>
       </c>
       <c r="D19" t="str">
-        <f t="shared" si="3"/>
+        <f>L8</f>
         <v>TRAGSL</v>
       </c>
       <c r="E19" s="12"/>
@@ -6773,36 +6799,36 @@
       <c r="J19" s="120"/>
       <c r="K19" s="120"/>
       <c r="L19" s="120" t="str">
-        <f t="shared" si="4"/>
+        <f>"FT"&amp;$G$2&amp;"-"&amp;L8</f>
         <v>FTE-TRAGSL</v>
       </c>
       <c r="M19" s="121" t="str">
-        <f t="shared" si="5"/>
+        <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M8</f>
         <v>Sector Fuel Technology Existing Transport Motor spirit</v>
       </c>
       <c r="N19" s="120" t="str">
-        <f t="shared" si="6"/>
+        <f>$E$2</f>
         <v>PJ</v>
       </c>
       <c r="O19" s="120" t="str">
-        <f t="shared" si="7"/>
+        <f>$E$2&amp;"a"</f>
         <v>PJa</v>
       </c>
       <c r="P19" s="120"/>
       <c r="Q19" s="120"/>
       <c r="R19" s="120"/>
     </row>
-    <row r="20" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:18" ht="12.75">
       <c r="B20" t="str">
-        <f t="shared" si="1"/>
+        <f>L20</f>
         <v>FTE-TRABIO</v>
       </c>
       <c r="C20" t="str">
-        <f t="shared" si="2"/>
+        <f>RIGHT(D20,3)</f>
         <v>BIO</v>
       </c>
       <c r="D20" t="str">
-        <f t="shared" si="3"/>
+        <f>L9</f>
         <v>TRABIO</v>
       </c>
       <c r="E20" s="12"/>
@@ -6816,36 +6842,36 @@
       <c r="J20" s="120"/>
       <c r="K20" s="120"/>
       <c r="L20" s="120" t="str">
-        <f t="shared" si="4"/>
+        <f>"FT"&amp;$G$2&amp;"-"&amp;L9</f>
         <v>FTE-TRABIO</v>
       </c>
       <c r="M20" s="121" t="str">
-        <f t="shared" si="5"/>
+        <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M9</f>
         <v>Sector Fuel Technology Existing Transport Biofuels</v>
       </c>
       <c r="N20" s="120" t="str">
-        <f t="shared" si="6"/>
+        <f>$E$2</f>
         <v>PJ</v>
       </c>
       <c r="O20" s="120" t="str">
-        <f t="shared" si="7"/>
+        <f>$E$2&amp;"a"</f>
         <v>PJa</v>
       </c>
       <c r="P20" s="120"/>
       <c r="Q20" s="120"/>
       <c r="R20" s="120"/>
     </row>
-    <row r="21" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:18" ht="12.75">
       <c r="B21" t="str">
-        <f t="shared" si="1"/>
+        <f>L21</f>
         <v>FTE-TRAELC</v>
       </c>
       <c r="C21" t="str">
-        <f t="shared" si="2"/>
+        <f>RIGHT(D21,3)</f>
         <v>ELC</v>
       </c>
       <c r="D21" t="str">
-        <f t="shared" si="3"/>
+        <f>L10</f>
         <v>TRAELC</v>
       </c>
       <c r="E21" s="12"/>
@@ -6859,42 +6885,42 @@
       <c r="J21" s="120"/>
       <c r="K21" s="120"/>
       <c r="L21" s="120" t="str">
-        <f t="shared" si="4"/>
+        <f>"FT"&amp;$G$2&amp;"-"&amp;L10</f>
         <v>FTE-TRAELC</v>
       </c>
       <c r="M21" s="121" t="str">
-        <f t="shared" si="5"/>
+        <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M10</f>
         <v>Sector Fuel Technology Existing Transport Electricity</v>
       </c>
       <c r="N21" s="120" t="str">
-        <f t="shared" si="6"/>
+        <f>$E$2</f>
         <v>PJ</v>
       </c>
       <c r="O21" s="120" t="str">
-        <f t="shared" si="7"/>
+        <f>$E$2&amp;"a"</f>
         <v>PJa</v>
       </c>
       <c r="P21" s="120" t="s">
-        <v>125</v>
+        <v>155</v>
       </c>
       <c r="Q21" s="120"/>
       <c r="R21" s="120"/>
     </row>
-    <row r="22" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="22" spans="5:13" ht="12.75">
       <c r="E22" s="12"/>
       <c r="F22" s="12"/>
       <c r="G22" s="70"/>
       <c r="H22" s="11"/>
       <c r="M22" s="19"/>
     </row>
-    <row r="23" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="23" spans="5:13" ht="12.75">
       <c r="E23" s="12"/>
       <c r="F23" s="12"/>
       <c r="G23" s="70"/>
       <c r="H23" s="11"/>
       <c r="M23" s="19"/>
     </row>
-    <row r="24" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:13" ht="12.75">
       <c r="B24" s="23"/>
       <c r="D24" s="23"/>
       <c r="E24" s="12"/>
@@ -6903,7 +6929,7 @@
       <c r="H24" s="11"/>
       <c r="M24" s="19"/>
     </row>
-    <row r="25" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:13" ht="12.75">
       <c r="B25" s="23"/>
       <c r="D25" s="23"/>
       <c r="E25" s="12"/>
@@ -6914,7 +6940,7 @@
       <c r="K25" s="23"/>
       <c r="M25" s="19"/>
     </row>
-    <row r="26" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:13" ht="12.75">
       <c r="B26" s="23"/>
       <c r="D26" s="23"/>
       <c r="E26" s="94"/>
@@ -6925,7 +6951,7 @@
       <c r="K26" s="23"/>
       <c r="M26" s="19"/>
     </row>
-    <row r="27" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:13" ht="12.75">
       <c r="B27" s="23"/>
       <c r="D27" s="23"/>
       <c r="E27" s="94"/>
@@ -6936,7 +6962,7 @@
       <c r="K27" s="23"/>
       <c r="M27" s="19"/>
     </row>
-    <row r="28" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:13" ht="12.75">
       <c r="B28" s="23"/>
       <c r="D28" s="23"/>
       <c r="E28" s="94"/>
@@ -6945,7 +6971,7 @@
       <c r="H28" s="11"/>
       <c r="M28" s="19"/>
     </row>
-    <row r="29" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:8" ht="12.75">
       <c r="B29" s="23"/>
       <c r="D29" s="23"/>
       <c r="E29" s="94"/>
@@ -6953,7 +6979,7 @@
       <c r="G29" s="70"/>
       <c r="H29" s="11"/>
     </row>
-    <row r="30" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:8" ht="12.75">
       <c r="B30" s="23"/>
       <c r="D30" s="23"/>
       <c r="E30" s="12"/>
@@ -6961,7 +6987,7 @@
       <c r="G30" s="70"/>
       <c r="H30" s="11"/>
     </row>
-    <row r="31" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:8" ht="12.75">
       <c r="B31" s="23"/>
       <c r="D31" s="23"/>
       <c r="E31" s="12"/>
@@ -6969,13 +6995,13 @@
       <c r="G31" s="70"/>
       <c r="H31" s="11"/>
     </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:3" ht="12.75">
       <c r="B35" s="44"/>
       <c r="C35" s="1" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:3" ht="12.75">
       <c r="B36" s="64"/>
       <c r="C36" s="1" t="s">
         <v>160</v>
@@ -6983,43 +7009,43 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9" r:id="rId4"/>
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B1:W32"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1428571428571" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" customWidth="1"/>
-    <col min="5" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.85546875" customWidth="1"/>
-    <col min="11" max="11" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.8571428571429" customWidth="1"/>
+    <col min="5" max="5" width="12.2857142857143" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.1428571428571" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.5714285714286" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.1428571428571" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.5714285714286" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.85714285714286" customWidth="1"/>
+    <col min="11" max="11" width="13.5714285714286" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" customWidth="1"/>
+    <col min="13" max="13" width="13.8571428571429" customWidth="1"/>
     <col min="14" max="14" width="2" customWidth="1"/>
-    <col min="15" max="15" width="12.42578125" customWidth="1"/>
-    <col min="16" max="16" width="7.140625" customWidth="1"/>
+    <col min="15" max="15" width="12.4285714285714" customWidth="1"/>
+    <col min="16" max="16" width="7.14285714285714" customWidth="1"/>
     <col min="17" max="17" width="11" customWidth="1"/>
-    <col min="18" max="18" width="63.42578125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="7.7109375" customWidth="1"/>
+    <col min="18" max="18" width="63.4285714285714" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.71428571428571" customWidth="1"/>
     <col min="20" max="20" width="12" customWidth="1"/>
-    <col min="21" max="21" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.28515625" customWidth="1"/>
+    <col min="21" max="21" width="12.8571428571429" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.2857142857143" customWidth="1"/>
     <col min="23" max="23" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:23" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:9" ht="15">
       <c r="B1" s="8" t="s">
         <v>73</v>
       </c>
@@ -7027,7 +7053,7 @@
         <v>75</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>114</v>
+        <v>145</v>
       </c>
       <c r="E1" s="8" t="s">
         <v>77</v>
@@ -7036,14 +7062,14 @@
         <v>78</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>143</v>
+        <v>183</v>
       </c>
       <c r="H1" s="8" t="s">
         <v>100</v>
       </c>
       <c r="I1" s="30"/>
     </row>
-    <row r="2" spans="2:23" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:23" ht="31.5">
       <c r="B2" s="10" t="str">
         <f>'EB2'!B9</f>
         <v>TRA</v>
@@ -7053,7 +7079,7 @@
         <v>Transport</v>
       </c>
       <c r="D2" s="18" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="E2" s="10" t="str">
         <f>'EB2'!Z2</f>
@@ -7064,7 +7090,7 @@
         <v>M€2005</v>
       </c>
       <c r="G2" s="31" t="s">
-        <v>144</v>
+        <v>182</v>
       </c>
       <c r="H2" s="10" t="s">
         <v>101</v>
@@ -7082,7 +7108,7 @@
       <c r="V2" s="116"/>
       <c r="W2" s="116"/>
     </row>
-    <row r="3" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="3" spans="15:23" ht="12.75">
       <c r="O3" s="117" t="s">
         <v>7</v>
       </c>
@@ -7111,7 +7137,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:23" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:23" ht="24" thickBot="1">
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
@@ -7145,7 +7171,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="2:23" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:23" ht="15.75">
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
@@ -7160,18 +7186,18 @@
         <v>DTCAR</v>
       </c>
       <c r="R5" s="116" t="str">
-        <f>LEFT($D$2,6)&amp;" "&amp;$C$2&amp; " Sector - "&amp;'EB2'!$X$25</f>
+        <f>LEFT($D$2,6)&amp;" "&amp;$C$2&amp;" Sector - "&amp;'EB2'!$X$25</f>
         <v>Demand Transport Sector - Cars</v>
       </c>
       <c r="S5" s="116" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="T5" s="116"/>
       <c r="U5" s="116"/>
       <c r="V5" s="116"/>
       <c r="W5" s="116"/>
     </row>
-    <row r="6" spans="2:23" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:23" ht="15.75">
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
@@ -7184,20 +7210,20 @@
         <v>DTPUB</v>
       </c>
       <c r="R6" s="116" t="str">
-        <f>LEFT($D$2,6)&amp;" "&amp;$C$2&amp; " Sector - "&amp;'EB2'!$X$26</f>
+        <f>LEFT($D$2,6)&amp;" "&amp;$C$2&amp;" Sector - "&amp;'EB2'!$X$26</f>
         <v>Demand Transport Sector - Pub</v>
       </c>
       <c r="S6" s="116" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="T6" s="116"/>
       <c r="U6" s="116"/>
       <c r="V6" s="116"/>
       <c r="W6" s="116"/>
     </row>
-    <row r="7" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="15:23" ht="12.75">
       <c r="O7" s="120" t="s">
-        <v>105</v>
+        <v>147</v>
       </c>
       <c r="P7" s="120"/>
       <c r="Q7" s="120" t="str">
@@ -7217,7 +7243,7 @@
       <c r="V7" s="120"/>
       <c r="W7" s="120"/>
     </row>
-    <row r="9" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="4:23" ht="12.75">
       <c r="D9" s="5" t="s">
         <v>13</v>
       </c>
@@ -7237,7 +7263,7 @@
       <c r="V9" s="120"/>
       <c r="W9" s="120"/>
     </row>
-    <row r="10" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:23" ht="12.75">
       <c r="B10" s="17" t="s">
         <v>1</v>
       </c>
@@ -7254,23 +7280,23 @@
         <v>85</v>
       </c>
       <c r="G10" s="71" t="s">
-        <v>98</v>
+        <v>151</v>
       </c>
       <c r="H10" s="71" t="s">
-        <v>146</v>
+        <v>180</v>
       </c>
       <c r="I10" s="71" t="s">
-        <v>84</v>
+        <v>179</v>
       </c>
       <c r="J10" s="71" t="s">
         <v>79</v>
       </c>
       <c r="K10" s="71" t="s">
-        <v>178</v>
+        <v>96</v>
       </c>
       <c r="L10" s="25"/>
       <c r="M10" s="29" t="s">
-        <v>118</v>
+        <v>148</v>
       </c>
       <c r="O10" s="117" t="s">
         <v>11</v>
@@ -7300,7 +7326,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="2:23" ht="23.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:23" ht="23.25" thickBot="1">
       <c r="B11" s="16" t="s">
         <v>39</v>
       </c>
@@ -7320,16 +7346,16 @@
         <v>99</v>
       </c>
       <c r="H11" s="85" t="s">
-        <v>148</v>
+        <v>118</v>
       </c>
       <c r="I11" s="16" t="s">
-        <v>96</v>
+        <v>178</v>
       </c>
       <c r="J11" s="16" t="s">
         <v>177</v>
       </c>
       <c r="K11" s="16" t="s">
-        <v>179</v>
+        <v>84</v>
       </c>
       <c r="L11" s="32"/>
       <c r="M11" s="113" t="s">
@@ -7363,7 +7389,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="2:23" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:23" ht="13.5" thickBot="1">
       <c r="B12" s="15" t="s">
         <v>91</v>
       </c>
@@ -7374,13 +7400,13 @@
         <v>000_Units</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>180</v>
+        <v>146</v>
       </c>
       <c r="G12" s="75" t="s">
-        <v>151</v>
+        <v>98</v>
       </c>
       <c r="H12" s="73" t="s">
-        <v>147</v>
+        <v>105</v>
       </c>
       <c r="I12" s="13" t="str">
         <f>$F$2&amp;"/"&amp;G2&amp;"a"</f>
@@ -7390,11 +7416,11 @@
         <v>92</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>181</v>
+        <v>144</v>
       </c>
       <c r="L12" s="32"/>
       <c r="M12" s="114" t="s">
-        <v>182</v>
+        <v>115</v>
       </c>
       <c r="O12" s="119" t="s">
         <v>81</v>
@@ -7408,17 +7434,17 @@
       <c r="V12" s="119"/>
       <c r="W12" s="119"/>
     </row>
-    <row r="13" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:23" ht="12.75">
       <c r="B13" t="str">
-        <f t="shared" ref="B13:B24" si="0">Q13</f>
+        <f>Q13</f>
         <v>TCAREGAS</v>
       </c>
       <c r="C13" t="str">
-        <f t="shared" ref="C13:C24" si="1">$B$2&amp;RIGHT(B13,3)</f>
+        <f>$B$2&amp;RIGHT(B13,3)</f>
         <v>TRAGAS</v>
       </c>
       <c r="D13" t="str">
-        <f t="shared" ref="D13:D18" si="2">$Q$5</f>
+        <f>$Q$5</f>
         <v>DTCAR</v>
       </c>
       <c r="E13" s="63">
@@ -7441,14 +7467,14 @@
         <v>10</v>
       </c>
       <c r="K13" s="69">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="M13" s="29">
         <f>E13*G13*K13*H13</f>
         <v>6.1165246499999988</v>
       </c>
       <c r="O13" s="116" t="s">
-        <v>97</v>
+        <v>143</v>
       </c>
       <c r="P13" s="120"/>
       <c r="Q13" s="120" t="str">
@@ -7456,33 +7482,33 @@
         <v>TCAREGAS</v>
       </c>
       <c r="R13" s="121" t="str">
-        <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB2'!$X$25&amp;" - "&amp;'EB2'!$E$3</f>
+        <f>$D$2&amp;" "&amp;$C$2&amp;" Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB2'!$X$25&amp;" - "&amp;'EB2'!$E$3</f>
         <v>Demand Technologies Transport Sector - Existing Cars - Natural Gas</v>
       </c>
       <c r="S13" s="116" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="T13" s="116" t="str">
-        <f t="shared" ref="T13:T24" si="3">$G$2</f>
+        <f>$G$2</f>
         <v>000_Units</v>
       </c>
       <c r="U13" s="120"/>
       <c r="V13" s="116" t="s">
-        <v>145</v>
+        <v>114</v>
       </c>
       <c r="W13" s="120"/>
     </row>
-    <row r="14" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:23" ht="12.75">
       <c r="B14" t="str">
-        <f t="shared" si="0"/>
+        <f>Q14</f>
         <v>TCAREDSL</v>
       </c>
       <c r="C14" t="str">
-        <f t="shared" si="1"/>
+        <f>$B$2&amp;RIGHT(B14,3)</f>
         <v>TRADSL</v>
       </c>
       <c r="D14" t="str">
-        <f t="shared" si="2"/>
+        <f>$Q$5</f>
         <v>DTCAR</v>
       </c>
       <c r="E14" s="63">
@@ -7493,7 +7519,7 @@
         <v>0.41</v>
       </c>
       <c r="G14" s="62">
-        <v>16.5</v>
+        <v>16.50</v>
       </c>
       <c r="H14" s="67">
         <v>1.25</v>
@@ -7505,10 +7531,10 @@
         <v>10</v>
       </c>
       <c r="K14" s="69">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="M14" s="29">
-        <f t="shared" ref="M14:M22" si="4">E14*G14*K14*H14</f>
+        <f>E14*G14*K14*H14</f>
         <v>1796.4988037437502</v>
       </c>
       <c r="O14" s="120"/>
@@ -7518,33 +7544,33 @@
         <v>TCAREDSL</v>
       </c>
       <c r="R14" s="121" t="str">
-        <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB2'!$X$25&amp;" - "&amp;'EB2'!$G$3</f>
+        <f>$D$2&amp;" "&amp;$C$2&amp;" Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB2'!$X$25&amp;" - "&amp;'EB2'!$G$3</f>
         <v>Demand Technologies Transport Sector - Existing Cars - Diesel oil</v>
       </c>
       <c r="S14" s="116" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="T14" s="116" t="str">
-        <f t="shared" si="3"/>
+        <f>$G$2</f>
         <v>000_Units</v>
       </c>
       <c r="U14" s="120"/>
       <c r="V14" s="116" t="s">
-        <v>145</v>
+        <v>114</v>
       </c>
       <c r="W14" s="120"/>
     </row>
-    <row r="15" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:23" ht="12.75">
       <c r="B15" t="str">
-        <f t="shared" si="0"/>
+        <f>Q15</f>
         <v>TCARELPG</v>
       </c>
       <c r="C15" t="str">
-        <f t="shared" si="1"/>
+        <f>$B$2&amp;RIGHT(B15,3)</f>
         <v>TRALPG</v>
       </c>
       <c r="D15" t="str">
-        <f t="shared" si="2"/>
+        <f>$Q$5</f>
         <v>DTCAR</v>
       </c>
       <c r="E15" s="63">
@@ -7567,10 +7593,10 @@
         <v>10</v>
       </c>
       <c r="K15" s="69">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="M15" s="29">
-        <f t="shared" si="4"/>
+        <f>E15*G15*K15*H15</f>
         <v>45.207322250000004</v>
       </c>
       <c r="O15" s="120"/>
@@ -7580,33 +7606,33 @@
         <v>TCARELPG</v>
       </c>
       <c r="R15" s="121" t="str">
-        <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB2'!$X$25&amp;" - "&amp;'EB2'!$I$3</f>
+        <f>$D$2&amp;" "&amp;$C$2&amp;" Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB2'!$X$25&amp;" - "&amp;'EB2'!$I$3</f>
         <v>Demand Technologies Transport Sector - Existing Cars - LPG</v>
       </c>
       <c r="S15" s="116" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="T15" s="116" t="str">
-        <f t="shared" si="3"/>
+        <f>$G$2</f>
         <v>000_Units</v>
       </c>
       <c r="U15" s="120"/>
       <c r="V15" s="116" t="s">
-        <v>145</v>
+        <v>114</v>
       </c>
       <c r="W15" s="120"/>
     </row>
-    <row r="16" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:23" ht="12.75">
       <c r="B16" t="str">
-        <f t="shared" si="0"/>
+        <f>Q16</f>
         <v>TCAREGSL</v>
       </c>
       <c r="C16" t="str">
-        <f t="shared" si="1"/>
+        <f>$B$2&amp;RIGHT(B16,3)</f>
         <v>TRAGSL</v>
       </c>
       <c r="D16" t="str">
-        <f t="shared" si="2"/>
+        <f>$Q$5</f>
         <v>DTCAR</v>
       </c>
       <c r="E16" s="63">
@@ -7614,10 +7640,10 @@
         <v>84109.849043478273</v>
       </c>
       <c r="F16" s="68">
-        <v>0.4</v>
+        <v>0.40</v>
       </c>
       <c r="G16" s="62">
-        <v>11.5</v>
+        <v>11.50</v>
       </c>
       <c r="H16" s="67">
         <v>1.25</v>
@@ -7629,10 +7655,10 @@
         <v>10</v>
       </c>
       <c r="K16" s="69">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="M16" s="29">
-        <f t="shared" si="4"/>
+        <f>E16*G16*K16*H16</f>
         <v>1209.07908</v>
       </c>
       <c r="O16" s="120"/>
@@ -7642,23 +7668,23 @@
         <v>TCAREGSL</v>
       </c>
       <c r="R16" s="120" t="str">
-        <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB2'!$X$25&amp;" - "&amp;'EB2'!$J$3</f>
+        <f>$D$2&amp;" "&amp;$C$2&amp;" Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB2'!$X$25&amp;" - "&amp;'EB2'!$J$3</f>
         <v>Demand Technologies Transport Sector - Existing Cars - Motor spirit</v>
       </c>
       <c r="S16" s="116" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="T16" s="116" t="str">
-        <f t="shared" si="3"/>
+        <f>$G$2</f>
         <v>000_Units</v>
       </c>
       <c r="U16" s="120"/>
       <c r="V16" s="116" t="s">
-        <v>145</v>
+        <v>114</v>
       </c>
       <c r="W16" s="120"/>
     </row>
-    <row r="17" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:23" ht="12.75">
       <c r="B17" t="str">
         <f>Q17</f>
         <v>TCAREBIO</v>
@@ -7668,7 +7694,7 @@
         <v>TRABIO</v>
       </c>
       <c r="D17" t="str">
-        <f t="shared" si="2"/>
+        <f>$Q$5</f>
         <v>DTCAR</v>
       </c>
       <c r="E17" s="63">
@@ -7676,10 +7702,10 @@
         <v>707.00000000000011</v>
       </c>
       <c r="F17" s="68">
-        <v>0.4</v>
+        <v>0.40</v>
       </c>
       <c r="G17" s="62">
-        <v>11.5</v>
+        <v>11.50</v>
       </c>
       <c r="H17" s="67">
         <v>1.25</v>
@@ -7691,7 +7717,7 @@
         <v>10</v>
       </c>
       <c r="K17" s="69">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="M17" s="29">
         <f>E17*G17*K17*H17</f>
@@ -7704,33 +7730,33 @@
         <v>TCAREBIO</v>
       </c>
       <c r="R17" s="120" t="str">
-        <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB2'!$X$25&amp;" - "&amp;'EB2'!$O$3</f>
+        <f>$D$2&amp;" "&amp;$C$2&amp;" Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB2'!$X$25&amp;" - "&amp;'EB2'!$O$3</f>
         <v>Demand Technologies Transport Sector - Existing Cars - Biofuels</v>
       </c>
       <c r="S17" s="116" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="T17" s="116" t="str">
-        <f t="shared" si="3"/>
+        <f>$G$2</f>
         <v>000_Units</v>
       </c>
       <c r="U17" s="120"/>
       <c r="V17" s="116" t="s">
-        <v>145</v>
+        <v>114</v>
       </c>
       <c r="W17" s="120"/>
     </row>
-    <row r="18" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:23" ht="12.75">
       <c r="B18" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>Q18</f>
         <v>TCAREELC</v>
       </c>
       <c r="C18" s="6" t="str">
-        <f t="shared" si="1"/>
+        <f>$B$2&amp;RIGHT(B18,3)</f>
         <v>TRAELC</v>
       </c>
       <c r="D18" s="6" t="str">
-        <f t="shared" si="2"/>
+        <f>$Q$5</f>
         <v>DTCAR</v>
       </c>
       <c r="E18" s="77">
@@ -7738,10 +7764,10 @@
         <v>0</v>
       </c>
       <c r="F18" s="95">
-        <v>0.4</v>
+        <v>0.40</v>
       </c>
       <c r="G18" s="96">
-        <v>11.5</v>
+        <v>11.50</v>
       </c>
       <c r="H18" s="97">
         <v>1.25</v>
@@ -7753,11 +7779,11 @@
         <v>10</v>
       </c>
       <c r="K18" s="99">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="L18" s="6"/>
       <c r="M18" s="100">
-        <f t="shared" si="4"/>
+        <f>E18*G18*K18*H18</f>
         <v>0</v>
       </c>
       <c r="O18" s="123"/>
@@ -7767,33 +7793,33 @@
         <v>TCAREELC</v>
       </c>
       <c r="R18" s="123" t="str">
-        <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB2'!$X$25&amp;" - "&amp;'EB2'!$U$3</f>
+        <f>$D$2&amp;" "&amp;$C$2&amp;" Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB2'!$X$25&amp;" - "&amp;'EB2'!$U$3</f>
         <v>Demand Technologies Transport Sector - Existing Cars - Electricity</v>
       </c>
       <c r="S18" s="124" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="T18" s="124" t="str">
-        <f t="shared" si="3"/>
+        <f>$G$2</f>
         <v>000_Units</v>
       </c>
       <c r="U18" s="123"/>
       <c r="V18" s="124" t="s">
-        <v>145</v>
+        <v>114</v>
       </c>
       <c r="W18" s="123"/>
     </row>
-    <row r="19" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:23" ht="12.75">
       <c r="B19" t="str">
-        <f t="shared" si="0"/>
+        <f>Q19</f>
         <v>TPUBEGAS</v>
       </c>
       <c r="C19" t="str">
-        <f t="shared" si="1"/>
+        <f>$B$2&amp;RIGHT(B19,3)</f>
         <v>TRAGAS</v>
       </c>
       <c r="D19" t="str">
-        <f t="shared" ref="D19:D24" si="5">$Q$6</f>
+        <f>$Q$6</f>
         <v>DTPUB</v>
       </c>
       <c r="E19" s="63">
@@ -7801,7 +7827,7 @@
         <v>0</v>
       </c>
       <c r="F19" s="67">
-        <v>0.1</v>
+        <v>0.10</v>
       </c>
       <c r="G19" s="44">
         <v>50</v>
@@ -7816,7 +7842,7 @@
         <v>30</v>
       </c>
       <c r="K19" s="69">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="M19" s="29">
         <f>E19*G19*K19*H19</f>
@@ -7829,33 +7855,33 @@
         <v>TPUBEGAS</v>
       </c>
       <c r="R19" s="121" t="str">
-        <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB2'!$X$26&amp;" - "&amp;'EB2'!$E$3</f>
+        <f>$D$2&amp;" "&amp;$C$2&amp;" Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB2'!$X$26&amp;" - "&amp;'EB2'!$E$3</f>
         <v>Demand Technologies Transport Sector - Existing Pub - Natural Gas</v>
       </c>
       <c r="S19" s="116" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="T19" s="116" t="str">
-        <f t="shared" si="3"/>
+        <f>$G$2</f>
         <v>000_Units</v>
       </c>
       <c r="U19" s="120"/>
       <c r="V19" s="116" t="s">
-        <v>145</v>
+        <v>114</v>
       </c>
       <c r="W19" s="120"/>
     </row>
-    <row r="20" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:23" ht="12.75">
       <c r="B20" t="str">
-        <f t="shared" si="0"/>
+        <f>Q20</f>
         <v>TPUBEDSL</v>
       </c>
       <c r="C20" t="str">
-        <f t="shared" si="1"/>
+        <f>$B$2&amp;RIGHT(B20,3)</f>
         <v>TRADSL</v>
       </c>
       <c r="D20" t="str">
-        <f t="shared" si="5"/>
+        <f>$Q$6</f>
         <v>DTPUB</v>
       </c>
       <c r="E20" s="63">
@@ -7878,7 +7904,7 @@
         <v>30</v>
       </c>
       <c r="K20" s="69">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="M20" s="29">
         <f>E20*G20*K20*H20</f>
@@ -7891,33 +7917,33 @@
         <v>TPUBEDSL</v>
       </c>
       <c r="R20" s="121" t="str">
-        <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB2'!$X$26&amp;" - "&amp;'EB2'!$G$3</f>
+        <f>$D$2&amp;" "&amp;$C$2&amp;" Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB2'!$X$26&amp;" - "&amp;'EB2'!$G$3</f>
         <v>Demand Technologies Transport Sector - Existing Pub - Diesel oil</v>
       </c>
       <c r="S20" s="116" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="T20" s="116" t="str">
-        <f t="shared" si="3"/>
+        <f>$G$2</f>
         <v>000_Units</v>
       </c>
       <c r="U20" s="120"/>
       <c r="V20" s="116" t="s">
-        <v>145</v>
+        <v>114</v>
       </c>
       <c r="W20" s="120"/>
     </row>
-    <row r="21" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:23" ht="12.75">
       <c r="B21" t="str">
-        <f t="shared" si="0"/>
+        <f>Q21</f>
         <v>TPUBELPG</v>
       </c>
       <c r="C21" t="str">
-        <f t="shared" si="1"/>
+        <f>$B$2&amp;RIGHT(B21,3)</f>
         <v>TRALPG</v>
       </c>
       <c r="D21" t="str">
-        <f t="shared" si="5"/>
+        <f>$Q$6</f>
         <v>DTPUB</v>
       </c>
       <c r="E21" s="63">
@@ -7925,7 +7951,7 @@
         <v>0</v>
       </c>
       <c r="F21" s="67">
-        <v>0.1</v>
+        <v>0.10</v>
       </c>
       <c r="G21" s="62">
         <v>50</v>
@@ -7940,7 +7966,7 @@
         <v>30</v>
       </c>
       <c r="K21" s="69">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="M21" s="29">
         <f>E21*G21*K21*H21</f>
@@ -7953,33 +7979,33 @@
         <v>TPUBELPG</v>
       </c>
       <c r="R21" s="121" t="str">
-        <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB2'!$X$26&amp;" - "&amp;'EB2'!$I$3</f>
+        <f>$D$2&amp;" "&amp;$C$2&amp;" Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB2'!$X$26&amp;" - "&amp;'EB2'!$I$3</f>
         <v>Demand Technologies Transport Sector - Existing Pub - LPG</v>
       </c>
       <c r="S21" s="116" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="T21" s="116" t="str">
-        <f t="shared" si="3"/>
+        <f>$G$2</f>
         <v>000_Units</v>
       </c>
       <c r="U21" s="120"/>
       <c r="V21" s="116" t="s">
-        <v>145</v>
+        <v>114</v>
       </c>
       <c r="W21" s="120"/>
     </row>
-    <row r="22" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:23" ht="12.75">
       <c r="B22" t="str">
-        <f t="shared" si="0"/>
+        <f>Q22</f>
         <v>TPUBEGSL</v>
       </c>
       <c r="C22" t="str">
-        <f t="shared" si="1"/>
+        <f>$B$2&amp;RIGHT(B22,3)</f>
         <v>TRAGSL</v>
       </c>
       <c r="D22" t="str">
-        <f t="shared" si="5"/>
+        <f>$Q$6</f>
         <v>DTPUB</v>
       </c>
       <c r="E22" s="63">
@@ -8002,10 +8028,10 @@
         <v>30</v>
       </c>
       <c r="K22" s="69">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="M22" s="29">
-        <f t="shared" si="4"/>
+        <f>E22*G22*K22*H22</f>
         <v>0</v>
       </c>
       <c r="O22" s="120"/>
@@ -8015,23 +8041,23 @@
         <v>TPUBEGSL</v>
       </c>
       <c r="R22" s="120" t="str">
-        <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB2'!$X$26&amp;" - "&amp;'EB2'!$J$3</f>
+        <f>$D$2&amp;" "&amp;$C$2&amp;" Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB2'!$X$26&amp;" - "&amp;'EB2'!$J$3</f>
         <v>Demand Technologies Transport Sector - Existing Pub - Motor spirit</v>
       </c>
       <c r="S22" s="116" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="T22" s="116" t="str">
-        <f t="shared" si="3"/>
+        <f>$G$2</f>
         <v>000_Units</v>
       </c>
       <c r="U22" s="120"/>
       <c r="V22" s="116" t="s">
-        <v>145</v>
+        <v>114</v>
       </c>
       <c r="W22" s="120"/>
     </row>
-    <row r="23" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:23" ht="12.75">
       <c r="B23" t="str">
         <f>Q23</f>
         <v>TPUBEBIO</v>
@@ -8041,7 +8067,7 @@
         <v>TRABIO</v>
       </c>
       <c r="D23" t="str">
-        <f t="shared" si="5"/>
+        <f>$Q$6</f>
         <v>DTPUB</v>
       </c>
       <c r="E23" s="63">
@@ -8064,7 +8090,7 @@
         <v>30</v>
       </c>
       <c r="K23" s="69">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="M23" s="29">
         <f>E23*G23*K23*H23</f>
@@ -8077,33 +8103,33 @@
         <v>TPUBEBIO</v>
       </c>
       <c r="R23" s="120" t="str">
-        <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB2'!$X$26&amp;" - "&amp;'EB2'!$O$3</f>
+        <f>$D$2&amp;" "&amp;$C$2&amp;" Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB2'!$X$26&amp;" - "&amp;'EB2'!$O$3</f>
         <v>Demand Technologies Transport Sector - Existing Pub - Biofuels</v>
       </c>
       <c r="S23" s="116" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="T23" s="116" t="str">
-        <f t="shared" si="3"/>
+        <f>$G$2</f>
         <v>000_Units</v>
       </c>
       <c r="U23" s="120"/>
       <c r="V23" s="116" t="s">
-        <v>145</v>
+        <v>114</v>
       </c>
       <c r="W23" s="120"/>
     </row>
-    <row r="24" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:23" ht="12.75">
       <c r="B24" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>Q24</f>
         <v>TPUBEELC</v>
       </c>
       <c r="C24" s="6" t="str">
-        <f t="shared" si="1"/>
+        <f>$B$2&amp;RIGHT(B24,3)</f>
         <v>TRAELC</v>
       </c>
       <c r="D24" s="6" t="str">
-        <f t="shared" si="5"/>
+        <f>$Q$6</f>
         <v>DTPUB</v>
       </c>
       <c r="E24" s="77">
@@ -8126,7 +8152,7 @@
         <v>30</v>
       </c>
       <c r="K24" s="99">
-        <v>1E-3</v>
+        <v>0.001</v>
       </c>
       <c r="M24" s="100">
         <f>E24*G24*K24*H24</f>
@@ -8139,23 +8165,23 @@
         <v>TPUBEELC</v>
       </c>
       <c r="R24" s="123" t="str">
-        <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB2'!$X$26&amp;" - "&amp;'EB2'!$U$3</f>
+        <f>$D$2&amp;" "&amp;$C$2&amp;" Sector - "&amp;""&amp;$H$1&amp;" "&amp;'EB2'!$X$26&amp;" - "&amp;'EB2'!$U$3</f>
         <v>Demand Technologies Transport Sector - Existing Pub - Electricity</v>
       </c>
       <c r="S24" s="124" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="T24" s="124" t="str">
-        <f t="shared" si="3"/>
+        <f>$G$2</f>
         <v>000_Units</v>
       </c>
       <c r="U24" s="123"/>
       <c r="V24" s="124" t="s">
-        <v>145</v>
+        <v>114</v>
       </c>
       <c r="W24" s="123"/>
     </row>
-    <row r="27" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:13" ht="12.75">
       <c r="B27" s="44"/>
       <c r="C27" s="1" t="s">
         <v>159</v>
@@ -8164,7 +8190,7 @@
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
     </row>
-    <row r="28" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:14" ht="12.75">
       <c r="B28" s="64"/>
       <c r="C28" s="1" t="s">
         <v>160</v>
@@ -8174,49 +8200,49 @@
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
     </row>
-    <row r="29" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="29" spans="11:14" ht="12.75">
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
       <c r="N29" s="1"/>
     </row>
-    <row r="30" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="30" spans="11:14" ht="12.75">
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
       <c r="N30" s="1"/>
     </row>
-    <row r="31" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="31" spans="5:14" ht="12.75">
       <c r="E31" s="1"/>
       <c r="N31" s="1"/>
     </row>
-    <row r="32" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="32" spans="5:5" ht="12.75">
       <c r="E32" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B1:J24"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5703125" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" customWidth="1"/>
-    <col min="4" max="4" width="11.5703125" customWidth="1"/>
-    <col min="5" max="5" width="11.28515625" customWidth="1"/>
+    <col min="2" max="2" width="12.5714285714286" customWidth="1"/>
+    <col min="3" max="3" width="13.1428571428571" customWidth="1"/>
+    <col min="4" max="4" width="11.5714285714286" customWidth="1"/>
+    <col min="5" max="5" width="11.2857142857143" customWidth="1"/>
     <col min="6" max="6" width="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.5703125" customWidth="1"/>
+    <col min="7" max="7" width="13.1428571428571" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.5714285714286" customWidth="1"/>
     <col min="9" max="9" width="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:7" ht="15">
       <c r="B1" s="8" t="s">
         <v>73</v>
       </c>
@@ -8233,7 +8259,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:7" ht="15.75">
       <c r="B2" s="10" t="s">
         <v>83</v>
       </c>
@@ -8248,7 +8274,7 @@
         <v>M€2005</v>
       </c>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="3:10" ht="12.75">
       <c r="C5" s="3" t="s">
         <v>13</v>
       </c>
@@ -8259,55 +8285,55 @@
       </c>
       <c r="J5" s="1"/>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:10" ht="12.75">
       <c r="B6" s="2" t="s">
-        <v>80</v>
+        <v>124</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>152</v>
+        <v>120</v>
       </c>
       <c r="E6" s="76">
         <v>2005</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>80</v>
+        <v>124</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>0</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="J6" s="2">
         <v>2005</v>
       </c>
     </row>
-    <row r="7" spans="2:10" ht="22.5" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:10" ht="22.5">
       <c r="B7" s="16" t="s">
         <v>81</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>153</v>
+        <v>121</v>
       </c>
       <c r="E7" s="72" t="s">
-        <v>36</v>
+        <v>184</v>
       </c>
       <c r="G7" s="16" t="s">
         <v>81</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="I7" s="16"/>
       <c r="J7" s="16"/>
     </row>
-    <row r="8" spans="2:10" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:10" ht="13.5" thickBot="1">
       <c r="B8" s="15" t="s">
         <v>91</v>
       </c>
@@ -8324,7 +8350,7 @@
       <c r="I8" s="15"/>
       <c r="J8" s="15"/>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:10" ht="12.75">
       <c r="B9" t="s">
         <v>35</v>
       </c>
@@ -8333,27 +8359,27 @@
         <v>DTCAR</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>184</v>
+        <v>82</v>
       </c>
       <c r="E9" s="62">
         <f>SUM(DemTechs_TRA!M13:M18)</f>
         <v>3067.06485564375</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>120</v>
+        <v>36</v>
       </c>
       <c r="H9" t="str">
         <f>DemTechs_TRA!$Q$5</f>
         <v>DTCAR</v>
       </c>
       <c r="I9" s="23" t="s">
-        <v>121</v>
+        <v>153</v>
       </c>
       <c r="J9" s="67">
         <v>0.25</v>
       </c>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:10" ht="12.75">
       <c r="B10" t="s">
         <v>35</v>
       </c>
@@ -8362,126 +8388,126 @@
         <v>DTPUB</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>184</v>
+        <v>82</v>
       </c>
       <c r="E10" s="62">
         <f>SUM(DemTechs_TRA!M19:M24)</f>
         <v>1727.9701023749997</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>120</v>
+        <v>36</v>
       </c>
       <c r="H10" t="str">
         <f>DemTechs_TRA!$Q$5</f>
         <v>DTCAR</v>
       </c>
       <c r="I10" s="23" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J10" s="67">
         <v>0.25</v>
       </c>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="7:10" ht="12.75">
       <c r="G11" s="1" t="s">
-        <v>120</v>
+        <v>36</v>
       </c>
       <c r="H11" t="str">
         <f>DemTechs_TRA!$Q$5</f>
         <v>DTCAR</v>
       </c>
       <c r="I11" s="23" t="s">
-        <v>123</v>
+        <v>80</v>
       </c>
       <c r="J11" s="67">
         <v>0.25</v>
       </c>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="5:10" ht="12.75">
       <c r="E12" s="26"/>
       <c r="G12" s="27" t="s">
-        <v>120</v>
+        <v>36</v>
       </c>
       <c r="H12" s="6" t="str">
         <f>DemTechs_TRA!$Q$5</f>
         <v>DTCAR</v>
       </c>
       <c r="I12" s="28" t="s">
-        <v>124</v>
+        <v>152</v>
       </c>
       <c r="J12" s="97">
         <v>0.25</v>
       </c>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="5:10" ht="12.75">
       <c r="E13" s="7"/>
       <c r="G13" s="1" t="s">
-        <v>120</v>
+        <v>36</v>
       </c>
       <c r="H13" t="str">
         <f>DemTechs_TRA!$Q$6</f>
         <v>DTPUB</v>
       </c>
       <c r="I13" s="23" t="s">
-        <v>121</v>
+        <v>153</v>
       </c>
       <c r="J13" s="67">
         <v>0.25</v>
       </c>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="7:10" ht="12.75">
       <c r="G14" s="1" t="s">
-        <v>120</v>
+        <v>36</v>
       </c>
       <c r="H14" t="str">
         <f>DemTechs_TRA!$Q$6</f>
         <v>DTPUB</v>
       </c>
       <c r="I14" s="23" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="J14" s="67">
         <v>0.25</v>
       </c>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="5:10" ht="12.75">
       <c r="E15" s="7"/>
       <c r="G15" s="1" t="s">
-        <v>120</v>
+        <v>36</v>
       </c>
       <c r="H15" t="str">
         <f>DemTechs_TRA!$Q$6</f>
         <v>DTPUB</v>
       </c>
       <c r="I15" s="23" t="s">
-        <v>123</v>
+        <v>80</v>
       </c>
       <c r="J15" s="67">
         <v>0.25</v>
       </c>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="7:10" ht="12.75">
       <c r="G16" s="1" t="s">
-        <v>120</v>
+        <v>36</v>
       </c>
       <c r="H16" t="str">
         <f>DemTechs_TRA!$Q$6</f>
         <v>DTPUB</v>
       </c>
       <c r="I16" s="23" t="s">
-        <v>124</v>
+        <v>152</v>
       </c>
       <c r="J16" s="67">
         <v>0.25</v>
       </c>
     </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:3" ht="12.75">
       <c r="B23" s="44"/>
       <c r="C23" s="1" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:3" ht="12.75">
       <c r="B24" s="64"/>
       <c r="C24" s="1" t="s">
         <v>160</v>
@@ -8494,21 +8520,21 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="B2:V35"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="2" max="2" width="14.42578125" customWidth="1"/>
+    <col min="2" max="2" width="14.4285714285714" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="2" spans="19:19" ht="12.75">
       <c r="S2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="3" spans="2:22" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="3" spans="2:13" ht="17.45" customHeight="1">
       <c r="B3" s="35" t="s">
-        <v>149</v>
+        <v>194</v>
       </c>
       <c r="C3" s="35"/>
       <c r="D3" s="35"/>
@@ -8517,13 +8543,13 @@
       <c r="G3" s="35"/>
       <c r="H3" s="35"/>
       <c r="J3" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="M3" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="4" spans="2:22" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="4" spans="2:16" ht="17.45" customHeight="1">
       <c r="B4" s="36"/>
       <c r="C4" s="36"/>
       <c r="D4" s="36"/>
@@ -8531,28 +8557,28 @@
       <c r="F4" s="36"/>
       <c r="G4" s="36"/>
       <c r="L4" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="N4" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="P4" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="5" spans="2:22" ht="18" x14ac:dyDescent="0.25">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="5" spans="2:22" ht="18">
       <c r="B5" s="33" t="s">
-        <v>150</v>
+        <v>198</v>
       </c>
       <c r="C5" s="34"/>
       <c r="Q5" t="s">
-        <v>210</v>
+        <v>189</v>
       </c>
       <c r="V5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="6" spans="2:22" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13" ht="13.5" thickBot="1">
       <c r="B6" s="38" t="s">
         <v>0</v>
       </c>
@@ -8575,39 +8601,39 @@
       <c r="G6" s="37"/>
       <c r="H6" s="37"/>
       <c r="I6" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="M6" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="7" spans="2:22" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" ht="13.5" thickBot="1">
       <c r="B7" s="15" t="s">
         <v>91</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>158</v>
+        <v>200</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>158</v>
+        <v>200</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>158</v>
+        <v>200</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>158</v>
+        <v>200</v>
       </c>
       <c r="G7" s="101"/>
       <c r="H7" s="101"/>
       <c r="I7" s="1"/>
     </row>
-    <row r="8" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:19" ht="12.75">
       <c r="B8" s="37" t="str">
         <f>DemTechs_TRA!Q7</f>
         <v>TRACO2</v>
       </c>
       <c r="C8" s="67">
-        <v>56.1</v>
+        <v>56.10</v>
       </c>
       <c r="D8" s="67">
         <v>75</v>
@@ -8620,140 +8646,148 @@
       </c>
       <c r="G8" s="102"/>
       <c r="H8" s="102" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I8" s="1"/>
       <c r="S8" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="9" spans="2:22" x14ac:dyDescent="0.2">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="9" spans="9:13" ht="12.75">
       <c r="I9" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="L9" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="M9" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="11" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="11" spans="9:15" ht="12.75">
       <c r="I11" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="K11" t="s">
         <v>187</v>
       </c>
       <c r="O11" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="14" spans="2:22" x14ac:dyDescent="0.2">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="13" spans="16:16" ht="12.75">
+      <c r="P13" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="14" spans="13:14" ht="12.75">
       <c r="M14" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="17" spans="2:17" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+      <c r="N14" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="17" spans="9:16" ht="12.75">
       <c r="I17" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O17" s="125" t="s">
-        <v>189</v>
+        <v>158</v>
       </c>
       <c r="P17" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="18" spans="2:17" x14ac:dyDescent="0.2">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="18" spans="11:11" ht="12.75">
       <c r="K18" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="21" spans="2:17" x14ac:dyDescent="0.2">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="21" spans="9:10" ht="12.75">
       <c r="I21" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="J21" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.2">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="22" spans="11:14" ht="12.75">
       <c r="K22" t="s">
-        <v>189</v>
+        <v>158</v>
       </c>
       <c r="N22" s="125" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.2">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14" ht="12.75">
       <c r="B23" s="44"/>
       <c r="C23" s="1" t="s">
         <v>159</v>
       </c>
       <c r="N23" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="24" spans="2:17" x14ac:dyDescent="0.2">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" ht="12.75">
       <c r="B24" s="64"/>
       <c r="C24" s="1" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="25" spans="8:16" ht="12.75">
       <c r="H25" t="s">
+        <v>210</v>
+      </c>
+      <c r="P25" s="125" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="26" spans="7:12" ht="12.75">
+      <c r="G26" t="s">
         <v>196</v>
       </c>
-      <c r="P25" s="125" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="26" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="G26" t="s">
-        <v>199</v>
-      </c>
       <c r="K26" s="125" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="L26" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.2">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="27" spans="5:5" ht="12.75">
       <c r="E27" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="29" spans="2:17" x14ac:dyDescent="0.2">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" ht="12.75">
       <c r="C29" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="Q29" s="125" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="30" spans="2:17" x14ac:dyDescent="0.2">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="30" spans="17:17" ht="12.75">
       <c r="Q30" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" ht="12.75">
       <c r="B33" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="34" spans="6:12" ht="12.75">
       <c r="F34" t="s">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="L34" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="35" spans="10:10" ht="12.75">
       <c r="J35" s="125" t="s">
-        <v>192</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>
